--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1321,6 +1321,238 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126488322</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>464536</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6785232</v>
+      </c>
+      <c r="S8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Miljöbilder! Fantastisk naturskönt område geologiskt! Inlandsisen har skapat ett flertal rullstensåsar i området varav den övre norra delen har formen av en cirkel runt myren här, vackert! Rullstensåsarna fortsätter sen i sydlig riktning som två parallella åsar.  Måttligt till rikligt med garnlav i en radie av ca 100 meter</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126488280</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>464538</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6785094</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Miljöbilder! Rikligt med garnlav i en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1553,6 +1553,3577 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126602970</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>464508</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6785019</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126603689</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>464528</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6785096</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126603549</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>464516</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6785072</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126603022</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>464494</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6785014</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126605806</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>464558</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6785175</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126604254</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>464509</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6785154</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Miljöbild på knotig torraka med bohål</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126604230</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79598</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>464519</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6785138</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126602944</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78739</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>464508</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6785019</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Miljöbild med kolad stubbe, bandad</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126605726</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>464549</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6785157</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126603818</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>464519</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6785128</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126604122</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>464519</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6785138</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Miljöbild med två tallar med garnlav samt kolad stubbe. Rullstensås i bakgrund</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126606459</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>464607</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6785225</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126606381</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79598</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>464583</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6785194</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126602948</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78738</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>464508</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6785019</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126603112</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>464493</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6785036</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126603275</v>
+      </c>
+      <c r="B25" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>464503</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6785048</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126605890</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>464574</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6785187</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126604065</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>464522</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6785128</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Miljöbild på hög torraka med bohål</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126606333</v>
+      </c>
+      <c r="B28" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>464583</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6785194</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126604580</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>464536</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6785152</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126604224</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78738</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>464519</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6785138</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126604216</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78739</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>464519</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6785138</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Miljöbild med kolad stubbe och rullstensås i bakgrund</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126606215</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>464581</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6785191</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126603485</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>464538</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6785057</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Miljöbild med två tallar, garnlav samt torrakor</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126603375</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>464503</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6785048</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126606412</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>464595</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6785208</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126606320</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>464583</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6785194</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Miljöbild, högstubbe med hackhål/bohål</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126602950</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79598</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>464508</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6785019</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126603440</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>464529</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6785062</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Miljöbild på två lågor</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126604232</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79569</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>464519</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6785138</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126603247</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>464498</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6785040</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126605752</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79598</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>464549</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6785157</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126603569</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>464521</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6785078</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -1555,7 +1555,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126602970</v>
+        <v>126603689</v>
       </c>
       <c r="B10" t="n">
         <v>78980</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464508</v>
+        <v>464528</v>
       </c>
       <c r="R10" t="n">
-        <v>6785019</v>
+        <v>6785096</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1662,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126603689</v>
+        <v>126602970</v>
       </c>
       <c r="B11" t="n">
         <v>78980</v>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464528</v>
+        <v>464508</v>
       </c>
       <c r="R11" t="n">
-        <v>6785096</v>
+        <v>6785019</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,7 +1769,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126603549</v>
+        <v>126603022</v>
       </c>
       <c r="B12" t="n">
         <v>78980</v>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464516</v>
+        <v>464494</v>
       </c>
       <c r="R12" t="n">
-        <v>6785072</v>
+        <v>6785014</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126603022</v>
+        <v>126603549</v>
       </c>
       <c r="B13" t="n">
         <v>78980</v>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464494</v>
+        <v>464516</v>
       </c>
       <c r="R13" t="n">
-        <v>6785014</v>
+        <v>6785072</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126605806</v>
+        <v>126604254</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,21 +1994,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464558</v>
+        <v>464509</v>
       </c>
       <c r="R14" t="n">
-        <v>6785175</v>
+        <v>6785154</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,6 +2064,11 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Miljöbild på knotig torraka med bohål</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126604254</v>
+        <v>126604230</v>
       </c>
       <c r="B15" t="n">
-        <v>57654</v>
+        <v>79598</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,21 +2106,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2125,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464509</v>
+        <v>464519</v>
       </c>
       <c r="R15" t="n">
-        <v>6785154</v>
+        <v>6785138</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,11 +2176,6 @@
       <c r="AB15" t="inlineStr">
         <is>
           <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Miljöbild på knotig torraka med bohål</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126604230</v>
+        <v>126605806</v>
       </c>
       <c r="B16" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464519</v>
+        <v>464558</v>
       </c>
       <c r="R16" t="n">
-        <v>6785138</v>
+        <v>6785175</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2421,7 +2421,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126605726</v>
+        <v>126603818</v>
       </c>
       <c r="B18" t="n">
         <v>78980</v>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464549</v>
+        <v>464519</v>
       </c>
       <c r="R18" t="n">
-        <v>6785157</v>
+        <v>6785128</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,7 +2528,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126603818</v>
+        <v>126604122</v>
       </c>
       <c r="B19" t="n">
         <v>78980</v>
@@ -2566,7 +2566,7 @@
         <v>464519</v>
       </c>
       <c r="R19" t="n">
-        <v>6785128</v>
+        <v>6785138</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2608,7 +2608,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Miljöbild med två tallar med garnlav samt kolad stubbe. Rullstensås i bakgrund</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,7 +2640,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126604122</v>
+        <v>126605726</v>
       </c>
       <c r="B20" t="n">
         <v>78980</v>
@@ -2670,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464519</v>
+        <v>464549</v>
       </c>
       <c r="R20" t="n">
-        <v>6785138</v>
+        <v>6785157</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2716,11 +2721,6 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Miljöbild med två tallar med garnlav samt kolad stubbe. Rullstensås i bakgrund</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2961,32 +2961,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126602948</v>
+        <v>126603275</v>
       </c>
       <c r="B23" t="n">
-        <v>78738</v>
+        <v>8447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464508</v>
+        <v>464503</v>
       </c>
       <c r="R23" t="n">
-        <v>6785019</v>
+        <v>6785048</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126603112</v>
+        <v>126602948</v>
       </c>
       <c r="B24" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3079,21 +3079,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464493</v>
+        <v>464508</v>
       </c>
       <c r="R24" t="n">
-        <v>6785036</v>
+        <v>6785019</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3175,32 +3175,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126603275</v>
+        <v>126603112</v>
       </c>
       <c r="B25" t="n">
-        <v>8447</v>
+        <v>78980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3210,10 +3210,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464503</v>
+        <v>464493</v>
       </c>
       <c r="R25" t="n">
-        <v>6785048</v>
+        <v>6785036</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3282,10 +3282,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126605890</v>
+        <v>126604065</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3293,21 +3293,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464574</v>
+        <v>464522</v>
       </c>
       <c r="R26" t="n">
-        <v>6785187</v>
+        <v>6785128</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3363,6 +3363,11 @@
       <c r="AB26" t="inlineStr">
         <is>
           <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Miljöbild på hög torraka med bohål</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3389,10 +3394,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126604065</v>
+        <v>126605890</v>
       </c>
       <c r="B27" t="n">
-        <v>57654</v>
+        <v>78980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3400,21 +3405,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3424,10 +3429,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464522</v>
+        <v>464574</v>
       </c>
       <c r="R27" t="n">
-        <v>6785128</v>
+        <v>6785187</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3470,11 +3475,6 @@
       <c r="AB27" t="inlineStr">
         <is>
           <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Miljöbild på hög torraka med bohål</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4586,32 +4586,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126603440</v>
+        <v>126604232</v>
       </c>
       <c r="B38" t="n">
-        <v>8447</v>
+        <v>79569</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464529</v>
+        <v>464519</v>
       </c>
       <c r="R38" t="n">
-        <v>6785062</v>
+        <v>6785138</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4666,12 +4666,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Miljöbild på två lågor</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4698,32 +4693,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126604232</v>
+        <v>126603440</v>
       </c>
       <c r="B39" t="n">
-        <v>79569</v>
+        <v>8447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4733,10 +4728,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464519</v>
+        <v>464529</v>
       </c>
       <c r="R39" t="n">
-        <v>6785138</v>
+        <v>6785062</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4768,7 +4763,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4778,7 +4773,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Miljöbild på två lågor</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>126602970</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>126603689</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1769,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126603022</v>
+        <v>126604254</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,21 +1780,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464494</v>
+        <v>464509</v>
       </c>
       <c r="R12" t="n">
-        <v>6785014</v>
+        <v>6785154</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1849,7 +1849,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Miljöbild på knotig torraka med bohål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126604254</v>
+        <v>126604230</v>
       </c>
       <c r="B13" t="n">
-        <v>57654</v>
+        <v>79629</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,21 +1892,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1911,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464509</v>
+        <v>464519</v>
       </c>
       <c r="R13" t="n">
-        <v>6785154</v>
+        <v>6785138</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,11 +1962,6 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Miljöbild på knotig torraka med bohål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126605806</v>
+        <v>126602823</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464558</v>
+        <v>464494</v>
       </c>
       <c r="R14" t="n">
-        <v>6785175</v>
+        <v>6785014</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,7 +2098,7 @@
         <v>126603549</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126604230</v>
+        <v>126605806</v>
       </c>
       <c r="B16" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464519</v>
+        <v>464558</v>
       </c>
       <c r="R16" t="n">
-        <v>6785138</v>
+        <v>6785175</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2312,7 +2312,7 @@
         <v>126602944</v>
       </c>
       <c r="B17" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>126606381</v>
       </c>
       <c r="B18" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,10 +2528,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126603818</v>
+        <v>126605726</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464519</v>
+        <v>464549</v>
       </c>
       <c r="R19" t="n">
-        <v>6785128</v>
+        <v>6785157</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,10 +2635,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126605726</v>
+        <v>126603818</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464549</v>
+        <v>464519</v>
       </c>
       <c r="R20" t="n">
-        <v>6785157</v>
+        <v>6785128</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2742,32 +2742,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126606459</v>
+        <v>126604122</v>
       </c>
       <c r="B21" t="n">
-        <v>8447</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464607</v>
+        <v>464519</v>
       </c>
       <c r="R21" t="n">
-        <v>6785225</v>
+        <v>6785138</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2823,6 +2823,11 @@
       <c r="AB21" t="inlineStr">
         <is>
           <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Miljöbild med två tallar med garnlav samt kolad stubbe. Rullstensås i bakgrund</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2849,32 +2854,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126604122</v>
+        <v>126606459</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2884,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464519</v>
+        <v>464607</v>
       </c>
       <c r="R22" t="n">
-        <v>6785138</v>
+        <v>6785225</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,11 +2935,6 @@
       <c r="AB22" t="inlineStr">
         <is>
           <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Miljöbild med två tallar med garnlav samt kolad stubbe. Rullstensås i bakgrund</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2961,10 +2961,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126602948</v>
+        <v>126603112</v>
       </c>
       <c r="B23" t="n">
-        <v>78738</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2972,21 +2972,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464508</v>
+        <v>464493</v>
       </c>
       <c r="R23" t="n">
-        <v>6785019</v>
+        <v>6785036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3068,32 +3068,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126603275</v>
+        <v>126602948</v>
       </c>
       <c r="B24" t="n">
-        <v>8447</v>
+        <v>78769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464503</v>
+        <v>464508</v>
       </c>
       <c r="R24" t="n">
-        <v>6785048</v>
+        <v>6785019</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3175,32 +3175,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126603112</v>
+        <v>126603275</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3210,10 +3210,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464493</v>
+        <v>464503</v>
       </c>
       <c r="R25" t="n">
-        <v>6785036</v>
+        <v>6785048</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3285,7 +3285,7 @@
         <v>126605890</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3608,10 +3608,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126604224</v>
+        <v>126604216</v>
       </c>
       <c r="B29" t="n">
-        <v>78738</v>
+        <v>78770</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3619,21 +3619,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3689,6 +3689,11 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Miljöbild med kolad stubbe och rullstensås i bakgrund</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3718,7 +3723,7 @@
         <v>126606215</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3822,10 +3827,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126604580</v>
+        <v>126604224</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>78769</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3833,21 +3838,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3857,10 +3862,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464536</v>
+        <v>464519</v>
       </c>
       <c r="R31" t="n">
-        <v>6785152</v>
+        <v>6785138</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3929,10 +3934,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126604216</v>
+        <v>126604580</v>
       </c>
       <c r="B32" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3940,21 +3945,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3964,10 +3969,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464519</v>
+        <v>464536</v>
       </c>
       <c r="R32" t="n">
-        <v>6785138</v>
+        <v>6785152</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4010,11 +4015,6 @@
       <c r="AB32" t="inlineStr">
         <is>
           <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Miljöbild med kolad stubbe och rullstensås i bakgrund</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4044,7 +4044,7 @@
         <v>126603375</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>126603485</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>126606412</v>
       </c>
       <c r="B35" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>126602950</v>
       </c>
       <c r="B37" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>126604232</v>
       </c>
       <c r="B39" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4805,10 +4805,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126605687</v>
+        <v>126603247</v>
       </c>
       <c r="B40" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4816,21 +4816,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464549</v>
+        <v>464498</v>
       </c>
       <c r="R40" t="n">
-        <v>6785157</v>
+        <v>6785040</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4875,7 +4875,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4912,10 +4912,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126603247</v>
+        <v>126605687</v>
       </c>
       <c r="B41" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4923,21 +4923,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464498</v>
+        <v>464549</v>
       </c>
       <c r="R41" t="n">
-        <v>6785040</v>
+        <v>6785157</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5022,7 +5022,7 @@
         <v>126603569</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>126673899</v>
       </c>
       <c r="B43" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5227,27 +5227,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126671166</v>
+        <v>126673354</v>
       </c>
       <c r="B44" t="n">
-        <v>56613</v>
+        <v>57654</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>208260</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5255,17 +5255,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5275,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464570</v>
+        <v>464578</v>
       </c>
       <c r="R44" t="n">
-        <v>6785148</v>
+        <v>6785262</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5319,7 +5314,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5338,27 +5332,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126673354</v>
+        <v>126671166</v>
       </c>
       <c r="B45" t="n">
-        <v>57654</v>
+        <v>56613</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>208260</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5366,12 +5360,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5381,10 +5380,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464578</v>
+        <v>464570</v>
       </c>
       <c r="R45" t="n">
-        <v>6785262</v>
+        <v>6785148</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5425,6 +5424,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126673693</v>
+        <v>126671598</v>
       </c>
       <c r="B46" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,26 +5454,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5481,10 +5486,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464560</v>
+        <v>464615</v>
       </c>
       <c r="R46" t="n">
-        <v>6785286</v>
+        <v>6785215</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5525,7 +5530,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5547,7 +5551,7 @@
         <v>126673612</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5645,39 +5649,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126673409</v>
+        <v>126674062</v>
       </c>
       <c r="B48" t="n">
-        <v>8447</v>
+        <v>79629</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5685,10 +5687,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464578</v>
+        <v>464476</v>
       </c>
       <c r="R48" t="n">
-        <v>6785262</v>
+        <v>6785273</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5748,39 +5750,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126674080</v>
+        <v>126673693</v>
       </c>
       <c r="B49" t="n">
-        <v>8447</v>
+        <v>79011</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464476</v>
+        <v>464560</v>
       </c>
       <c r="R49" t="n">
-        <v>6785273</v>
+        <v>6785286</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5851,37 +5851,39 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126674062</v>
+        <v>126674080</v>
       </c>
       <c r="B50" t="n">
-        <v>79598</v>
+        <v>8447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5952,42 +5954,39 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126671598</v>
+        <v>126673409</v>
       </c>
       <c r="B51" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5995,10 +5994,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464615</v>
+        <v>464578</v>
       </c>
       <c r="R51" t="n">
-        <v>6785215</v>
+        <v>6785262</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6039,6 +6038,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6060,7 +6060,7 @@
         <v>126674709</v>
       </c>
       <c r="B52" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>126674647</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>126673865</v>
       </c>
       <c r="B54" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6360,37 +6360,39 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126673908</v>
+        <v>126673604</v>
       </c>
       <c r="B55" t="n">
-        <v>79598</v>
+        <v>8447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6398,10 +6400,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464493</v>
+        <v>464577</v>
       </c>
       <c r="R55" t="n">
-        <v>6785289</v>
+        <v>6785269</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6464,7 +6466,7 @@
         <v>126673857</v>
       </c>
       <c r="B56" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6562,39 +6564,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126673604</v>
+        <v>126673908</v>
       </c>
       <c r="B57" t="n">
-        <v>8447</v>
+        <v>79629</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464577</v>
+        <v>464493</v>
       </c>
       <c r="R57" t="n">
-        <v>6785269</v>
+        <v>6785289</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6665,39 +6665,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126674305</v>
+        <v>126673637</v>
       </c>
       <c r="B58" t="n">
-        <v>8447</v>
+        <v>79629</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6705,10 +6703,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464493</v>
+        <v>464561</v>
       </c>
       <c r="R58" t="n">
-        <v>6785242</v>
+        <v>6785279</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6768,37 +6766,39 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126673637</v>
+        <v>126674305</v>
       </c>
       <c r="B59" t="n">
-        <v>79598</v>
+        <v>8447</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464561</v>
+        <v>464493</v>
       </c>
       <c r="R59" t="n">
-        <v>6785279</v>
+        <v>6785242</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6869,10 +6869,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126671230</v>
+        <v>126671531</v>
       </c>
       <c r="B60" t="n">
-        <v>57654</v>
+        <v>91337</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6880,31 +6880,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6912,10 +6907,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464649</v>
+        <v>464639</v>
       </c>
       <c r="R60" t="n">
-        <v>6785183</v>
+        <v>6785224</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6956,6 +6951,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6974,10 +6970,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126671531</v>
+        <v>126671230</v>
       </c>
       <c r="B61" t="n">
-        <v>91263</v>
+        <v>57654</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6985,26 +6981,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7012,10 +7013,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464639</v>
+        <v>464649</v>
       </c>
       <c r="R61" t="n">
-        <v>6785224</v>
+        <v>6785183</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7056,7 +7057,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7183,7 +7183,7 @@
         <v>126674692</v>
       </c>
       <c r="B63" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>126673290</v>
       </c>
       <c r="B64" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>126673628</v>
       </c>
       <c r="B66" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>126674472</v>
       </c>
       <c r="B67" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>126673925</v>
       </c>
       <c r="B68" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>126674463</v>
       </c>
       <c r="B69" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7894,10 +7894,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126674521</v>
+        <v>126673529</v>
       </c>
       <c r="B70" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464473</v>
+        <v>464596</v>
       </c>
       <c r="R70" t="n">
-        <v>6785254</v>
+        <v>6785247</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7995,10 +7995,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126673529</v>
+        <v>126674521</v>
       </c>
       <c r="B71" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464596</v>
+        <v>464473</v>
       </c>
       <c r="R71" t="n">
-        <v>6785247</v>
+        <v>6785254</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8096,37 +8096,39 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126673816</v>
+        <v>126674542</v>
       </c>
       <c r="B72" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8134,10 +8136,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464526</v>
+        <v>464460</v>
       </c>
       <c r="R72" t="n">
-        <v>6785298</v>
+        <v>6785250</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8197,39 +8199,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126674542</v>
+        <v>126673816</v>
       </c>
       <c r="B73" t="n">
-        <v>8447</v>
+        <v>79011</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8237,10 +8237,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464460</v>
+        <v>464526</v>
       </c>
       <c r="R73" t="n">
-        <v>6785250</v>
+        <v>6785298</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8303,7 +8303,7 @@
         <v>126674606</v>
       </c>
       <c r="B74" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8401,10 +8401,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126673961</v>
+        <v>126672268</v>
       </c>
       <c r="B75" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8412,21 +8412,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464480</v>
+        <v>464577</v>
       </c>
       <c r="R75" t="n">
-        <v>6785279</v>
+        <v>6785208</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8502,10 +8502,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126672268</v>
+        <v>126673961</v>
       </c>
       <c r="B76" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8513,21 +8513,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8540,10 +8540,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464577</v>
+        <v>464480</v>
       </c>
       <c r="R76" t="n">
-        <v>6785208</v>
+        <v>6785279</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8606,7 +8606,7 @@
         <v>126674688</v>
       </c>
       <c r="B77" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8809,10 +8809,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126673585</v>
+        <v>126673713</v>
       </c>
       <c r="B79" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8847,10 +8847,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464577</v>
+        <v>464541</v>
       </c>
       <c r="R79" t="n">
-        <v>6785269</v>
+        <v>6785290</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8910,10 +8910,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126673713</v>
+        <v>126673585</v>
       </c>
       <c r="B80" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464541</v>
+        <v>464577</v>
       </c>
       <c r="R80" t="n">
-        <v>6785290</v>
+        <v>6785269</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9014,7 +9014,7 @@
         <v>126674073</v>
       </c>
       <c r="B81" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>126672703</v>
       </c>
       <c r="B82" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9318,10 +9318,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126691497</v>
+        <v>126691457</v>
       </c>
       <c r="B84" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9356,10 +9356,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464498</v>
+        <v>464489</v>
       </c>
       <c r="R84" t="n">
-        <v>6785170</v>
+        <v>6785179</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9419,10 +9419,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126691457</v>
+        <v>126691497</v>
       </c>
       <c r="B85" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9457,10 +9457,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464489</v>
+        <v>464498</v>
       </c>
       <c r="R85" t="n">
-        <v>6785179</v>
+        <v>6785170</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9626,7 +9626,7 @@
         <v>126691510</v>
       </c>
       <c r="B87" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>126691032</v>
       </c>
       <c r="B88" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>126690655</v>
       </c>
       <c r="B89" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9926,39 +9926,37 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126691398</v>
+        <v>126691473</v>
       </c>
       <c r="B90" t="n">
-        <v>8447</v>
+        <v>79011</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -9966,10 +9964,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464479</v>
+        <v>464493</v>
       </c>
       <c r="R90" t="n">
-        <v>6785190</v>
+        <v>6785173</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10029,37 +10027,39 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126691473</v>
+        <v>126691398</v>
       </c>
       <c r="B91" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464493</v>
+        <v>464479</v>
       </c>
       <c r="R91" t="n">
-        <v>6785173</v>
+        <v>6785190</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10133,7 +10133,7 @@
         <v>126690643</v>
       </c>
       <c r="B92" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10231,10 +10231,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126691436</v>
+        <v>126690666</v>
       </c>
       <c r="B93" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10269,10 +10269,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464487</v>
+        <v>464470</v>
       </c>
       <c r="R93" t="n">
-        <v>6785181</v>
+        <v>6785218</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10332,10 +10332,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126690666</v>
+        <v>126691436</v>
       </c>
       <c r="B94" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10370,10 +10370,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464470</v>
+        <v>464487</v>
       </c>
       <c r="R94" t="n">
-        <v>6785218</v>
+        <v>6785181</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10436,7 +10436,7 @@
         <v>126690932</v>
       </c>
       <c r="B95" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>126691491</v>
       </c>
       <c r="B96" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>126691386</v>
       </c>
       <c r="B97" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10736,10 +10736,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126690958</v>
+        <v>126690787</v>
       </c>
       <c r="B98" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10774,10 +10774,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464476</v>
+        <v>464471</v>
       </c>
       <c r="R98" t="n">
-        <v>6785202</v>
+        <v>6785211</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10837,10 +10837,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126690787</v>
+        <v>126690958</v>
       </c>
       <c r="B99" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10875,10 +10875,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464471</v>
+        <v>464476</v>
       </c>
       <c r="R99" t="n">
-        <v>6785211</v>
+        <v>6785202</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10941,7 +10941,7 @@
         <v>126691009</v>
       </c>
       <c r="B100" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>126691382</v>
       </c>
       <c r="B101" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>126690680</v>
       </c>
       <c r="B102" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11241,32 +11241,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127020226</v>
+        <v>127156818</v>
       </c>
       <c r="B103" t="n">
-        <v>91718</v>
+        <v>91773</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5467</v>
+        <v>1209</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11279,13 +11279,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464537</v>
+        <v>464550</v>
       </c>
       <c r="R103" t="n">
-        <v>6785309</v>
+        <v>6785289</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11309,12 +11309,17 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11330,44 +11335,44 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127156818</v>
+        <v>127020226</v>
       </c>
       <c r="B104" t="n">
-        <v>91699</v>
+        <v>91780</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knölgrynna</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phlebia femsjoeensis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Litsch. &amp; S. Lundell) J. Erikss. &amp; Hjortstam</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11380,13 +11385,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>464550</v>
+        <v>464537</v>
       </c>
       <c r="R104" t="n">
-        <v>6785289</v>
+        <v>6785309</v>
       </c>
       <c r="S104" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11410,17 +11415,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11436,12 +11436,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -1558,7 +1558,7 @@
         <v>126602970</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>126603689</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1769,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126604254</v>
+        <v>126604230</v>
       </c>
       <c r="B12" t="n">
-        <v>57654</v>
+        <v>79632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,21 +1780,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464509</v>
+        <v>464519</v>
       </c>
       <c r="R12" t="n">
-        <v>6785154</v>
+        <v>6785138</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,11 +1850,6 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Miljöbild på knotig torraka med bohål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126604230</v>
+        <v>126602823</v>
       </c>
       <c r="B13" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,21 +1887,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1916,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464519</v>
+        <v>464494</v>
       </c>
       <c r="R13" t="n">
-        <v>6785138</v>
+        <v>6785014</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,7 +1946,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1961,7 +1956,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126602823</v>
+        <v>126603549</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464494</v>
+        <v>464516</v>
       </c>
       <c r="R14" t="n">
-        <v>6785014</v>
+        <v>6785072</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2095,10 +2090,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126603549</v>
+        <v>126605806</v>
       </c>
       <c r="B15" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,10 +2125,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464516</v>
+        <v>464558</v>
       </c>
       <c r="R15" t="n">
-        <v>6785072</v>
+        <v>6785175</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,7 +2160,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,7 +2170,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126605806</v>
+        <v>126604254</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,21 +2208,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2237,10 +2232,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464558</v>
+        <v>464509</v>
       </c>
       <c r="R16" t="n">
-        <v>6785175</v>
+        <v>6785154</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2283,6 +2278,11 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Miljöbild på knotig torraka med bohål</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2312,7 +2312,7 @@
         <v>126602944</v>
       </c>
       <c r="B17" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>126606381</v>
       </c>
       <c r="B18" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>126605726</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>126603818</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>126604122</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>126603112</v>
       </c>
       <c r="B23" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>126602948</v>
       </c>
       <c r="B24" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>126605890</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>126604216</v>
       </c>
       <c r="B29" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>126606215</v>
       </c>
       <c r="B30" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>126604224</v>
       </c>
       <c r="B31" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>126604580</v>
       </c>
       <c r="B32" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>126603375</v>
       </c>
       <c r="B33" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>126603485</v>
       </c>
       <c r="B34" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>126606412</v>
       </c>
       <c r="B35" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>126602950</v>
       </c>
       <c r="B37" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>126604232</v>
       </c>
       <c r="B39" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>126603247</v>
       </c>
       <c r="B40" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>126605687</v>
       </c>
       <c r="B41" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>126603569</v>
       </c>
       <c r="B42" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5126,10 +5126,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126673899</v>
+        <v>126673354</v>
       </c>
       <c r="B43" t="n">
-        <v>79600</v>
+        <v>57654</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,26 +5137,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5164,10 +5169,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464493</v>
+        <v>464578</v>
       </c>
       <c r="R43" t="n">
-        <v>6785289</v>
+        <v>6785262</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5208,7 +5213,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5227,27 +5231,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126673354</v>
+        <v>126671166</v>
       </c>
       <c r="B44" t="n">
-        <v>57654</v>
+        <v>56613</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>208260</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5255,12 +5259,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5270,10 +5279,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464578</v>
+        <v>464570</v>
       </c>
       <c r="R44" t="n">
-        <v>6785262</v>
+        <v>6785148</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5314,6 +5323,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5332,47 +5342,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126671166</v>
+        <v>126673899</v>
       </c>
       <c r="B45" t="n">
-        <v>56613</v>
+        <v>79603</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>208260</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464570</v>
+        <v>464493</v>
       </c>
       <c r="R45" t="n">
-        <v>6785148</v>
+        <v>6785289</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5548,37 +5548,39 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126673612</v>
+        <v>126674080</v>
       </c>
       <c r="B47" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5586,10 +5588,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464579</v>
+        <v>464476</v>
       </c>
       <c r="R47" t="n">
-        <v>6785276</v>
+        <v>6785273</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5649,37 +5651,39 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126674062</v>
+        <v>126673409</v>
       </c>
       <c r="B48" t="n">
-        <v>79629</v>
+        <v>8447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5687,10 +5691,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464476</v>
+        <v>464578</v>
       </c>
       <c r="R48" t="n">
-        <v>6785273</v>
+        <v>6785262</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5750,10 +5754,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126673693</v>
+        <v>126673612</v>
       </c>
       <c r="B49" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5788,10 +5792,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464560</v>
+        <v>464579</v>
       </c>
       <c r="R49" t="n">
-        <v>6785286</v>
+        <v>6785276</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5851,39 +5855,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126674080</v>
+        <v>126673693</v>
       </c>
       <c r="B50" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5891,10 +5893,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464476</v>
+        <v>464560</v>
       </c>
       <c r="R50" t="n">
-        <v>6785273</v>
+        <v>6785286</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5954,39 +5956,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126673409</v>
+        <v>126674062</v>
       </c>
       <c r="B51" t="n">
-        <v>8447</v>
+        <v>79632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464578</v>
+        <v>464476</v>
       </c>
       <c r="R51" t="n">
-        <v>6785262</v>
+        <v>6785273</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6060,7 +6060,7 @@
         <v>126674709</v>
       </c>
       <c r="B52" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>126674647</v>
       </c>
       <c r="B53" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>126673865</v>
       </c>
       <c r="B54" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6360,39 +6360,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126673604</v>
+        <v>126673857</v>
       </c>
       <c r="B55" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6400,10 +6398,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464577</v>
+        <v>464502</v>
       </c>
       <c r="R55" t="n">
-        <v>6785269</v>
+        <v>6785289</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6463,10 +6461,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126673857</v>
+        <v>126673908</v>
       </c>
       <c r="B56" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6474,21 +6472,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6501,7 +6499,7 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464502</v>
+        <v>464493</v>
       </c>
       <c r="R56" t="n">
         <v>6785289</v>
@@ -6564,37 +6562,39 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126673908</v>
+        <v>126673604</v>
       </c>
       <c r="B57" t="n">
-        <v>79629</v>
+        <v>8447</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464493</v>
+        <v>464577</v>
       </c>
       <c r="R57" t="n">
-        <v>6785289</v>
+        <v>6785269</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6665,37 +6665,39 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126673637</v>
+        <v>126674305</v>
       </c>
       <c r="B58" t="n">
-        <v>79629</v>
+        <v>8447</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6703,10 +6705,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464561</v>
+        <v>464493</v>
       </c>
       <c r="R58" t="n">
-        <v>6785279</v>
+        <v>6785242</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6766,39 +6768,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126674305</v>
+        <v>126673637</v>
       </c>
       <c r="B59" t="n">
-        <v>8447</v>
+        <v>79632</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464493</v>
+        <v>464561</v>
       </c>
       <c r="R59" t="n">
-        <v>6785242</v>
+        <v>6785279</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6872,7 +6872,7 @@
         <v>126671531</v>
       </c>
       <c r="B60" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>126674692</v>
       </c>
       <c r="B63" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>126673290</v>
       </c>
       <c r="B64" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7490,10 +7490,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126673628</v>
+        <v>126674472</v>
       </c>
       <c r="B66" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7528,10 +7528,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464561</v>
+        <v>464473</v>
       </c>
       <c r="R66" t="n">
-        <v>6785279</v>
+        <v>6785249</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7591,10 +7591,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126674472</v>
+        <v>126673628</v>
       </c>
       <c r="B67" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464473</v>
+        <v>464561</v>
       </c>
       <c r="R67" t="n">
-        <v>6785249</v>
+        <v>6785279</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7695,7 +7695,7 @@
         <v>126673925</v>
       </c>
       <c r="B68" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>126674463</v>
       </c>
       <c r="B69" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>126673529</v>
       </c>
       <c r="B70" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>126674521</v>
       </c>
       <c r="B71" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>126673816</v>
       </c>
       <c r="B73" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>126674606</v>
       </c>
       <c r="B74" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8401,10 +8401,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126672268</v>
+        <v>126673961</v>
       </c>
       <c r="B75" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8412,21 +8412,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464577</v>
+        <v>464480</v>
       </c>
       <c r="R75" t="n">
-        <v>6785208</v>
+        <v>6785279</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8502,10 +8502,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126673961</v>
+        <v>126672268</v>
       </c>
       <c r="B76" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8513,21 +8513,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8540,10 +8540,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464480</v>
+        <v>464577</v>
       </c>
       <c r="R76" t="n">
-        <v>6785279</v>
+        <v>6785208</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8606,7 +8606,7 @@
         <v>126674688</v>
       </c>
       <c r="B77" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8704,10 +8704,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126674229</v>
+        <v>126673713</v>
       </c>
       <c r="B78" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8715,31 +8715,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8747,10 +8742,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464503</v>
+        <v>464541</v>
       </c>
       <c r="R78" t="n">
-        <v>6785245</v>
+        <v>6785290</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8791,6 +8786,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8809,10 +8805,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126673713</v>
+        <v>126673585</v>
       </c>
       <c r="B79" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8847,10 +8843,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464541</v>
+        <v>464577</v>
       </c>
       <c r="R79" t="n">
-        <v>6785290</v>
+        <v>6785269</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8910,10 +8906,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126673585</v>
+        <v>126674229</v>
       </c>
       <c r="B80" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8921,26 +8917,31 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -8948,10 +8949,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464577</v>
+        <v>464503</v>
       </c>
       <c r="R80" t="n">
-        <v>6785269</v>
+        <v>6785245</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8992,7 +8993,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9014,7 +9014,7 @@
         <v>126674073</v>
       </c>
       <c r="B81" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9112,10 +9112,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126672703</v>
+        <v>126671991</v>
       </c>
       <c r="B82" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9123,26 +9123,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9150,10 +9155,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464597</v>
+        <v>464571</v>
       </c>
       <c r="R82" t="n">
-        <v>6785229</v>
+        <v>6785206</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9194,7 +9199,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9213,10 +9217,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126671991</v>
+        <v>126672703</v>
       </c>
       <c r="B83" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9224,31 +9228,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9256,10 +9255,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464571</v>
+        <v>464597</v>
       </c>
       <c r="R83" t="n">
-        <v>6785206</v>
+        <v>6785229</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9300,6 +9299,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9318,37 +9318,39 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126691457</v>
+        <v>126691440</v>
       </c>
       <c r="B84" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9356,10 +9358,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464489</v>
+        <v>464487</v>
       </c>
       <c r="R84" t="n">
-        <v>6785179</v>
+        <v>6785181</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9419,10 +9421,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126691497</v>
+        <v>126691457</v>
       </c>
       <c r="B85" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9457,10 +9459,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464498</v>
+        <v>464489</v>
       </c>
       <c r="R85" t="n">
-        <v>6785170</v>
+        <v>6785179</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9520,39 +9522,37 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126691440</v>
+        <v>126691497</v>
       </c>
       <c r="B86" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464487</v>
+        <v>464498</v>
       </c>
       <c r="R86" t="n">
-        <v>6785181</v>
+        <v>6785170</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9626,7 +9626,7 @@
         <v>126691510</v>
       </c>
       <c r="B87" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>126691032</v>
       </c>
       <c r="B88" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>126690655</v>
       </c>
       <c r="B89" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9926,37 +9926,39 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126691473</v>
+        <v>126691398</v>
       </c>
       <c r="B90" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -9964,10 +9966,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464493</v>
+        <v>464479</v>
       </c>
       <c r="R90" t="n">
-        <v>6785173</v>
+        <v>6785190</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10027,39 +10029,37 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126691398</v>
+        <v>126691473</v>
       </c>
       <c r="B91" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464479</v>
+        <v>464493</v>
       </c>
       <c r="R91" t="n">
-        <v>6785190</v>
+        <v>6785173</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10133,7 +10133,7 @@
         <v>126690643</v>
       </c>
       <c r="B92" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>126690666</v>
       </c>
       <c r="B93" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>126691436</v>
       </c>
       <c r="B94" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>126690932</v>
       </c>
       <c r="B95" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>126691491</v>
       </c>
       <c r="B96" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>126691386</v>
       </c>
       <c r="B97" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>126690787</v>
       </c>
       <c r="B98" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>126690958</v>
       </c>
       <c r="B99" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>126691009</v>
       </c>
       <c r="B100" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>126691382</v>
       </c>
       <c r="B101" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>126690680</v>
       </c>
       <c r="B102" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>127156818</v>
       </c>
       <c r="B103" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>127020226</v>
       </c>
       <c r="B104" t="n">
-        <v>91780</v>
+        <v>91786</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -1876,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126602823</v>
+        <v>126604254</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,21 +1887,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464494</v>
+        <v>464509</v>
       </c>
       <c r="R13" t="n">
-        <v>6785014</v>
+        <v>6785154</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1956,7 +1956,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Miljöbild på knotig torraka med bohål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,7 +1988,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126603549</v>
+        <v>126602823</v>
       </c>
       <c r="B14" t="n">
         <v>79014</v>
@@ -2018,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464516</v>
+        <v>464494</v>
       </c>
       <c r="R14" t="n">
-        <v>6785072</v>
+        <v>6785014</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2090,7 +2095,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126605806</v>
+        <v>126603549</v>
       </c>
       <c r="B15" t="n">
         <v>79014</v>
@@ -2125,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464558</v>
+        <v>464516</v>
       </c>
       <c r="R15" t="n">
-        <v>6785175</v>
+        <v>6785072</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2170,7 +2175,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126604254</v>
+        <v>126605806</v>
       </c>
       <c r="B16" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2232,10 +2237,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464509</v>
+        <v>464558</v>
       </c>
       <c r="R16" t="n">
-        <v>6785154</v>
+        <v>6785175</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2278,11 +2283,6 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Miljöbild på knotig torraka med bohål</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2421,32 +2421,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126606381</v>
+        <v>126606459</v>
       </c>
       <c r="B18" t="n">
-        <v>79632</v>
+        <v>8447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464583</v>
+        <v>464607</v>
       </c>
       <c r="R18" t="n">
-        <v>6785194</v>
+        <v>6785225</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2854,32 +2854,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126606459</v>
+        <v>126606381</v>
       </c>
       <c r="B22" t="n">
-        <v>8447</v>
+        <v>79632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464607</v>
+        <v>464583</v>
       </c>
       <c r="R22" t="n">
-        <v>6785225</v>
+        <v>6785194</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3608,10 +3608,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126604216</v>
+        <v>126604224</v>
       </c>
       <c r="B29" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3619,21 +3619,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3689,11 +3689,6 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Miljöbild med kolad stubbe och rullstensås i bakgrund</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3720,10 +3715,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126606215</v>
+        <v>126604216</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3731,21 +3726,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3755,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464581</v>
+        <v>464519</v>
       </c>
       <c r="R30" t="n">
-        <v>6785191</v>
+        <v>6785138</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3801,6 +3796,11 @@
       <c r="AB30" t="inlineStr">
         <is>
           <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Miljöbild med kolad stubbe och rullstensås i bakgrund</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3827,10 +3827,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126604224</v>
+        <v>126606215</v>
       </c>
       <c r="B31" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3838,21 +3838,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3862,10 +3862,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464519</v>
+        <v>464581</v>
       </c>
       <c r="R31" t="n">
-        <v>6785138</v>
+        <v>6785191</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4805,10 +4805,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126603247</v>
+        <v>126605687</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4816,21 +4816,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464498</v>
+        <v>464549</v>
       </c>
       <c r="R40" t="n">
-        <v>6785040</v>
+        <v>6785157</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4875,7 +4875,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4912,10 +4912,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126605687</v>
+        <v>126603247</v>
       </c>
       <c r="B41" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4923,21 +4923,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464549</v>
+        <v>464498</v>
       </c>
       <c r="R41" t="n">
-        <v>6785157</v>
+        <v>6785040</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5855,10 +5855,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126673693</v>
+        <v>126674062</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5866,21 +5866,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464560</v>
+        <v>464476</v>
       </c>
       <c r="R50" t="n">
-        <v>6785286</v>
+        <v>6785273</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5956,10 +5956,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126674062</v>
+        <v>126673693</v>
       </c>
       <c r="B51" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5967,21 +5967,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464476</v>
+        <v>464560</v>
       </c>
       <c r="R51" t="n">
-        <v>6785273</v>
+        <v>6785286</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6665,39 +6665,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126674305</v>
+        <v>126673637</v>
       </c>
       <c r="B58" t="n">
-        <v>8447</v>
+        <v>79632</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6705,10 +6703,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464493</v>
+        <v>464561</v>
       </c>
       <c r="R58" t="n">
-        <v>6785242</v>
+        <v>6785279</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6768,37 +6766,39 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126673637</v>
+        <v>126674305</v>
       </c>
       <c r="B59" t="n">
-        <v>79632</v>
+        <v>8447</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464561</v>
+        <v>464493</v>
       </c>
       <c r="R59" t="n">
-        <v>6785279</v>
+        <v>6785242</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7793,10 +7793,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126674463</v>
+        <v>126673529</v>
       </c>
       <c r="B69" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7804,21 +7804,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464473</v>
+        <v>464596</v>
       </c>
       <c r="R69" t="n">
-        <v>6785249</v>
+        <v>6785247</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7894,7 +7894,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126673529</v>
+        <v>126674521</v>
       </c>
       <c r="B70" t="n">
         <v>79014</v>
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464596</v>
+        <v>464473</v>
       </c>
       <c r="R70" t="n">
-        <v>6785247</v>
+        <v>6785254</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7995,10 +7995,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126674521</v>
+        <v>126674463</v>
       </c>
       <c r="B71" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8006,21 +8006,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8036,7 +8036,7 @@
         <v>464473</v>
       </c>
       <c r="R71" t="n">
-        <v>6785254</v>
+        <v>6785249</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8401,10 +8401,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126673961</v>
+        <v>126672268</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8412,21 +8412,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464480</v>
+        <v>464577</v>
       </c>
       <c r="R75" t="n">
-        <v>6785279</v>
+        <v>6785208</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8502,10 +8502,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126672268</v>
+        <v>126673961</v>
       </c>
       <c r="B76" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8513,21 +8513,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8540,10 +8540,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464577</v>
+        <v>464480</v>
       </c>
       <c r="R76" t="n">
-        <v>6785208</v>
+        <v>6785279</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8704,10 +8704,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126673713</v>
+        <v>126674229</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8715,26 +8715,31 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8742,10 +8747,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464541</v>
+        <v>464503</v>
       </c>
       <c r="R78" t="n">
-        <v>6785290</v>
+        <v>6785245</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8786,7 +8791,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8805,7 +8809,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126673585</v>
+        <v>126673713</v>
       </c>
       <c r="B79" t="n">
         <v>79014</v>
@@ -8843,10 +8847,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464577</v>
+        <v>464541</v>
       </c>
       <c r="R79" t="n">
-        <v>6785269</v>
+        <v>6785290</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8906,10 +8910,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126674229</v>
+        <v>126673585</v>
       </c>
       <c r="B80" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8917,31 +8921,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -8949,10 +8948,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464503</v>
+        <v>464577</v>
       </c>
       <c r="R80" t="n">
-        <v>6785245</v>
+        <v>6785269</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8993,6 +8992,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9112,10 +9112,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126671991</v>
+        <v>126672703</v>
       </c>
       <c r="B82" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9123,31 +9123,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9155,10 +9150,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464571</v>
+        <v>464597</v>
       </c>
       <c r="R82" t="n">
-        <v>6785206</v>
+        <v>6785229</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9199,6 +9194,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9217,10 +9213,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126672703</v>
+        <v>126671991</v>
       </c>
       <c r="B83" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9228,26 +9224,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9255,10 +9256,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464597</v>
+        <v>464571</v>
       </c>
       <c r="R83" t="n">
-        <v>6785229</v>
+        <v>6785206</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9299,7 +9300,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9318,39 +9318,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126691440</v>
+        <v>126691457</v>
       </c>
       <c r="B84" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9358,10 +9356,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464487</v>
+        <v>464489</v>
       </c>
       <c r="R84" t="n">
-        <v>6785181</v>
+        <v>6785179</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9421,7 +9419,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126691457</v>
+        <v>126691497</v>
       </c>
       <c r="B85" t="n">
         <v>79014</v>
@@ -9459,10 +9457,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464489</v>
+        <v>464498</v>
       </c>
       <c r="R85" t="n">
-        <v>6785179</v>
+        <v>6785170</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9522,37 +9520,39 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126691497</v>
+        <v>126691440</v>
       </c>
       <c r="B86" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464498</v>
+        <v>464487</v>
       </c>
       <c r="R86" t="n">
-        <v>6785170</v>
+        <v>6785181</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9926,39 +9926,37 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126691398</v>
+        <v>126691473</v>
       </c>
       <c r="B90" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -9966,10 +9964,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464479</v>
+        <v>464493</v>
       </c>
       <c r="R90" t="n">
-        <v>6785190</v>
+        <v>6785173</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10029,37 +10027,39 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126691473</v>
+        <v>126691398</v>
       </c>
       <c r="B91" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464493</v>
+        <v>464479</v>
       </c>
       <c r="R91" t="n">
-        <v>6785173</v>
+        <v>6785190</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -2421,32 +2421,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126606459</v>
+        <v>126605726</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464607</v>
+        <v>464549</v>
       </c>
       <c r="R18" t="n">
-        <v>6785225</v>
+        <v>6785157</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2528,7 +2528,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126605726</v>
+        <v>126603818</v>
       </c>
       <c r="B19" t="n">
         <v>79014</v>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464549</v>
+        <v>464519</v>
       </c>
       <c r="R19" t="n">
-        <v>6785157</v>
+        <v>6785128</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,7 +2635,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126603818</v>
+        <v>126604122</v>
       </c>
       <c r="B20" t="n">
         <v>79014</v>
@@ -2673,7 +2673,7 @@
         <v>464519</v>
       </c>
       <c r="R20" t="n">
-        <v>6785128</v>
+        <v>6785138</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2715,7 +2715,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Miljöbild med två tallar med garnlav samt kolad stubbe. Rullstensås i bakgrund</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2742,10 +2747,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126604122</v>
+        <v>126606381</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2753,21 +2758,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2777,10 +2782,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464519</v>
+        <v>464583</v>
       </c>
       <c r="R21" t="n">
-        <v>6785138</v>
+        <v>6785194</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2823,11 +2828,6 @@
       <c r="AB21" t="inlineStr">
         <is>
           <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Miljöbild med två tallar med garnlav samt kolad stubbe. Rullstensås i bakgrund</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2854,32 +2854,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126606381</v>
+        <v>126606459</v>
       </c>
       <c r="B22" t="n">
-        <v>79632</v>
+        <v>8447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464583</v>
+        <v>464607</v>
       </c>
       <c r="R22" t="n">
-        <v>6785194</v>
+        <v>6785225</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2961,10 +2961,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126603112</v>
+        <v>126602948</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2972,21 +2972,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464493</v>
+        <v>464508</v>
       </c>
       <c r="R23" t="n">
-        <v>6785036</v>
+        <v>6785019</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126602948</v>
+        <v>126603112</v>
       </c>
       <c r="B24" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3079,21 +3079,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464508</v>
+        <v>464493</v>
       </c>
       <c r="R24" t="n">
-        <v>6785019</v>
+        <v>6785036</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126604216</v>
+        <v>126606215</v>
       </c>
       <c r="B30" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,21 +3726,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464519</v>
+        <v>464581</v>
       </c>
       <c r="R30" t="n">
-        <v>6785138</v>
+        <v>6785191</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3796,11 +3796,6 @@
       <c r="AB30" t="inlineStr">
         <is>
           <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Miljöbild med kolad stubbe och rullstensås i bakgrund</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3827,7 +3822,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126606215</v>
+        <v>126604580</v>
       </c>
       <c r="B31" t="n">
         <v>79014</v>
@@ -3862,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464581</v>
+        <v>464536</v>
       </c>
       <c r="R31" t="n">
-        <v>6785191</v>
+        <v>6785152</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3934,10 +3929,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126604580</v>
+        <v>126604216</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3945,21 +3940,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3969,10 +3964,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464536</v>
+        <v>464519</v>
       </c>
       <c r="R32" t="n">
-        <v>6785152</v>
+        <v>6785138</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4015,6 +4010,11 @@
       <c r="AB32" t="inlineStr">
         <is>
           <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Miljöbild med kolad stubbe och rullstensås i bakgrund</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -7894,10 +7894,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126674521</v>
+        <v>126674463</v>
       </c>
       <c r="B70" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7905,21 +7905,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7935,7 +7935,7 @@
         <v>464473</v>
       </c>
       <c r="R70" t="n">
-        <v>6785254</v>
+        <v>6785249</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7995,10 +7995,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126674463</v>
+        <v>126674521</v>
       </c>
       <c r="B71" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8006,21 +8006,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8036,7 +8036,7 @@
         <v>464473</v>
       </c>
       <c r="R71" t="n">
-        <v>6785249</v>
+        <v>6785254</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8096,39 +8096,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126674542</v>
+        <v>126673816</v>
       </c>
       <c r="B72" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8136,10 +8134,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464460</v>
+        <v>464526</v>
       </c>
       <c r="R72" t="n">
-        <v>6785250</v>
+        <v>6785298</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8199,7 +8197,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126673816</v>
+        <v>126674606</v>
       </c>
       <c r="B73" t="n">
         <v>79014</v>
@@ -8237,10 +8235,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464526</v>
+        <v>464462</v>
       </c>
       <c r="R73" t="n">
-        <v>6785298</v>
+        <v>6785243</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8300,37 +8298,39 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126674606</v>
+        <v>126674542</v>
       </c>
       <c r="B74" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8338,10 +8338,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464462</v>
+        <v>464460</v>
       </c>
       <c r="R74" t="n">
-        <v>6785243</v>
+        <v>6785250</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126671598</v>
+        <v>126673612</v>
       </c>
       <c r="B46" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,31 +5454,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5486,10 +5481,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464615</v>
+        <v>464579</v>
       </c>
       <c r="R46" t="n">
-        <v>6785215</v>
+        <v>6785276</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5530,6 +5525,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5548,39 +5544,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126674080</v>
+        <v>126674062</v>
       </c>
       <c r="B47" t="n">
-        <v>8447</v>
+        <v>79632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5651,39 +5645,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126673409</v>
+        <v>126673693</v>
       </c>
       <c r="B48" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5691,10 +5683,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464578</v>
+        <v>464560</v>
       </c>
       <c r="R48" t="n">
-        <v>6785262</v>
+        <v>6785286</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5754,10 +5746,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126673612</v>
+        <v>126671598</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5765,26 +5757,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5792,10 +5789,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464579</v>
+        <v>464615</v>
       </c>
       <c r="R49" t="n">
-        <v>6785276</v>
+        <v>6785215</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5836,7 +5833,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5855,37 +5851,39 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126674062</v>
+        <v>126674080</v>
       </c>
       <c r="B50" t="n">
-        <v>79632</v>
+        <v>8447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5956,37 +5954,39 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126673693</v>
+        <v>126673409</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464560</v>
+        <v>464578</v>
       </c>
       <c r="R51" t="n">
-        <v>6785286</v>
+        <v>6785262</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6872,7 +6872,7 @@
         <v>126671531</v>
       </c>
       <c r="B60" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126674472</v>
+        <v>126673628</v>
       </c>
       <c r="B66" t="n">
         <v>79603</v>
@@ -7528,10 +7528,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464473</v>
+        <v>464561</v>
       </c>
       <c r="R66" t="n">
-        <v>6785249</v>
+        <v>6785279</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7591,7 +7591,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126673628</v>
+        <v>126674472</v>
       </c>
       <c r="B67" t="n">
         <v>79603</v>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464561</v>
+        <v>464473</v>
       </c>
       <c r="R67" t="n">
-        <v>6785279</v>
+        <v>6785249</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7793,10 +7793,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126673529</v>
+        <v>126674463</v>
       </c>
       <c r="B69" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7804,21 +7804,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464596</v>
+        <v>464473</v>
       </c>
       <c r="R69" t="n">
-        <v>6785247</v>
+        <v>6785249</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7894,10 +7894,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126674463</v>
+        <v>126673529</v>
       </c>
       <c r="B70" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7905,21 +7905,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464473</v>
+        <v>464596</v>
       </c>
       <c r="R70" t="n">
-        <v>6785249</v>
+        <v>6785247</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -11244,7 +11244,7 @@
         <v>127156818</v>
       </c>
       <c r="B103" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>127020226</v>
       </c>
       <c r="B104" t="n">
-        <v>91786</v>
+        <v>91787</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY104"/>
+  <dimension ref="A1:AY152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5126,10 +5126,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126673354</v>
+        <v>126673899</v>
       </c>
       <c r="B43" t="n">
-        <v>57654</v>
+        <v>79603</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,31 +5137,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5169,10 +5164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464578</v>
+        <v>464493</v>
       </c>
       <c r="R43" t="n">
-        <v>6785262</v>
+        <v>6785289</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5213,6 +5208,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5342,10 +5338,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126673899</v>
+        <v>126673354</v>
       </c>
       <c r="B45" t="n">
-        <v>79603</v>
+        <v>57654</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5353,26 +5349,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5380,10 +5381,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464493</v>
+        <v>464578</v>
       </c>
       <c r="R45" t="n">
-        <v>6785289</v>
+        <v>6785262</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5424,7 +5425,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -9318,37 +9318,39 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126691457</v>
+        <v>126691440</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9356,10 +9358,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464489</v>
+        <v>464487</v>
       </c>
       <c r="R84" t="n">
-        <v>6785179</v>
+        <v>6785181</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9419,7 +9421,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126691497</v>
+        <v>126691457</v>
       </c>
       <c r="B85" t="n">
         <v>79014</v>
@@ -9457,10 +9459,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464498</v>
+        <v>464489</v>
       </c>
       <c r="R85" t="n">
-        <v>6785170</v>
+        <v>6785179</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9520,39 +9522,37 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126691440</v>
+        <v>126691497</v>
       </c>
       <c r="B86" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464487</v>
+        <v>464498</v>
       </c>
       <c r="R86" t="n">
-        <v>6785181</v>
+        <v>6785170</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11446,6 +11446,5187 @@
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>127422560</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>464493</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6785289</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>127422249</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>464471</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6785300</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>127423331</v>
+      </c>
+      <c r="B107" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>464480</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6785322</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>127422104</v>
+      </c>
+      <c r="B108" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>464454</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6785288</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>127423519</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>464487</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6785354</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>127423611</v>
+      </c>
+      <c r="B110" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>464488</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6785340</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>127427354</v>
+      </c>
+      <c r="B111" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>464643</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6785243</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>127421762</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>464429</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6785317</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>127421683</v>
+      </c>
+      <c r="B113" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>464444</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6785295</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>127421835</v>
+      </c>
+      <c r="B114" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>464456</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6785336</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>127423850</v>
+      </c>
+      <c r="B115" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>464502</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6785318</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>127425834</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>464558</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6785308</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>127423223</v>
+      </c>
+      <c r="B117" t="n">
+        <v>79603</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>464502</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6785318</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>127422036</v>
+      </c>
+      <c r="B118" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>464445</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6785311</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>127422304</v>
+      </c>
+      <c r="B119" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>464471</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6785300</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>127424788</v>
+      </c>
+      <c r="B120" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>464526</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6785298</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>127423326</v>
+      </c>
+      <c r="B121" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>464480</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6785322</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>127423422</v>
+      </c>
+      <c r="B122" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>464465</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6785344</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>127427379</v>
+      </c>
+      <c r="B123" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>464643</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6785243</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>127425909</v>
+      </c>
+      <c r="B124" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>464566</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6785301</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>127426763</v>
+      </c>
+      <c r="B125" t="n">
+        <v>58027</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>464578</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6785262</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>127421841</v>
+      </c>
+      <c r="B126" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>464456</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6785336</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>127423221</v>
+      </c>
+      <c r="B127" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>464502</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6785318</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127421737</v>
+      </c>
+      <c r="B128" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>464429</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6785317</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>127423538</v>
+      </c>
+      <c r="B129" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>464487</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6785354</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>127423379</v>
+      </c>
+      <c r="B130" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>464477</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6785333</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>127422760</v>
+      </c>
+      <c r="B131" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>464479</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6785300</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>127422589</v>
+      </c>
+      <c r="B132" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>464502</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6785289</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>127422151</v>
+      </c>
+      <c r="B133" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>464471</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6785300</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>127421996</v>
+      </c>
+      <c r="B134" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>464445</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6785311</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>127423972</v>
+      </c>
+      <c r="B135" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>464506</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6785318</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>127423454</v>
+      </c>
+      <c r="B136" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>464472</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6785351</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>127422954</v>
+      </c>
+      <c r="B137" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>464492</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6785316</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>127423216</v>
+      </c>
+      <c r="B138" t="n">
+        <v>78773</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>464502</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6785318</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>127423983</v>
+      </c>
+      <c r="B139" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>464506</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6785318</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>127425810</v>
+      </c>
+      <c r="B140" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>464558</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6785308</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>127424901</v>
+      </c>
+      <c r="B141" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>464544</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6785309</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>127423228</v>
+      </c>
+      <c r="B142" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>464502</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6785318</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>127424838</v>
+      </c>
+      <c r="B143" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>464537</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6785309</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>127425011</v>
+      </c>
+      <c r="B144" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>464526</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6785325</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>127423546</v>
+      </c>
+      <c r="B145" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>464487</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6785354</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>127424833</v>
+      </c>
+      <c r="B146" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>464537</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6785309</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>127423429</v>
+      </c>
+      <c r="B147" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>464465</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6785344</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>127423346</v>
+      </c>
+      <c r="B148" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>464480</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6785322</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>127422085</v>
+      </c>
+      <c r="B149" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>464454</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6785288</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>127421885</v>
+      </c>
+      <c r="B150" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>464445</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6785311</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>127422583</v>
+      </c>
+      <c r="B151" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>464502</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6785289</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>127421603</v>
+      </c>
+      <c r="B152" t="n">
+        <v>79603</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>464439</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6785262</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -5126,10 +5126,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126673899</v>
+        <v>126673354</v>
       </c>
       <c r="B43" t="n">
-        <v>79603</v>
+        <v>57654</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5137,26 +5137,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5164,10 +5169,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464493</v>
+        <v>464578</v>
       </c>
       <c r="R43" t="n">
-        <v>6785289</v>
+        <v>6785262</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5208,7 +5213,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5338,10 +5342,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126673354</v>
+        <v>126673899</v>
       </c>
       <c r="B45" t="n">
-        <v>57654</v>
+        <v>79603</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5349,31 +5353,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5381,10 +5380,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464578</v>
+        <v>464493</v>
       </c>
       <c r="R45" t="n">
-        <v>6785262</v>
+        <v>6785289</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5425,6 +5424,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126673612</v>
+        <v>126671598</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,26 +5454,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5481,10 +5486,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464579</v>
+        <v>464615</v>
       </c>
       <c r="R46" t="n">
-        <v>6785276</v>
+        <v>6785215</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5525,7 +5530,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5544,10 +5548,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126674062</v>
+        <v>126673612</v>
       </c>
       <c r="B47" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5555,21 +5559,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5582,10 +5586,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464476</v>
+        <v>464579</v>
       </c>
       <c r="R47" t="n">
-        <v>6785273</v>
+        <v>6785276</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5746,10 +5750,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126671598</v>
+        <v>126674062</v>
       </c>
       <c r="B49" t="n">
-        <v>57654</v>
+        <v>79632</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5757,31 +5761,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5789,10 +5788,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464615</v>
+        <v>464476</v>
       </c>
       <c r="R49" t="n">
-        <v>6785215</v>
+        <v>6785273</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5833,6 +5832,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6869,10 +6869,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126671531</v>
+        <v>126671230</v>
       </c>
       <c r="B60" t="n">
-        <v>91344</v>
+        <v>57654</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6880,26 +6880,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6907,10 +6912,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464639</v>
+        <v>464649</v>
       </c>
       <c r="R60" t="n">
-        <v>6785224</v>
+        <v>6785183</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6951,7 +6956,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6970,10 +6974,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126671230</v>
+        <v>126671531</v>
       </c>
       <c r="B61" t="n">
-        <v>57654</v>
+        <v>91344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6981,31 +6985,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7013,10 +7012,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464649</v>
+        <v>464639</v>
       </c>
       <c r="R61" t="n">
-        <v>6785183</v>
+        <v>6785224</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7057,6 +7056,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7793,10 +7793,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126674463</v>
+        <v>126674521</v>
       </c>
       <c r="B69" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7804,21 +7804,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7834,7 +7834,7 @@
         <v>464473</v>
       </c>
       <c r="R69" t="n">
-        <v>6785249</v>
+        <v>6785254</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7995,10 +7995,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126674521</v>
+        <v>126674463</v>
       </c>
       <c r="B71" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8006,21 +8006,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8036,7 +8036,7 @@
         <v>464473</v>
       </c>
       <c r="R71" t="n">
-        <v>6785254</v>
+        <v>6785249</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8809,7 +8809,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126673713</v>
+        <v>126673585</v>
       </c>
       <c r="B79" t="n">
         <v>79014</v>
@@ -8847,10 +8847,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464541</v>
+        <v>464577</v>
       </c>
       <c r="R79" t="n">
-        <v>6785290</v>
+        <v>6785269</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8910,7 +8910,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126673585</v>
+        <v>126673713</v>
       </c>
       <c r="B80" t="n">
         <v>79014</v>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464577</v>
+        <v>464541</v>
       </c>
       <c r="R80" t="n">
-        <v>6785269</v>
+        <v>6785290</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9112,10 +9112,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126672703</v>
+        <v>126671991</v>
       </c>
       <c r="B82" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9123,26 +9123,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9150,10 +9155,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464597</v>
+        <v>464571</v>
       </c>
       <c r="R82" t="n">
-        <v>6785229</v>
+        <v>6785206</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9194,7 +9199,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9213,10 +9217,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126671991</v>
+        <v>126672703</v>
       </c>
       <c r="B83" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9224,31 +9228,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9256,10 +9255,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464571</v>
+        <v>464597</v>
       </c>
       <c r="R83" t="n">
-        <v>6785206</v>
+        <v>6785229</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9300,6 +9299,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9318,39 +9318,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126691440</v>
+        <v>126691497</v>
       </c>
       <c r="B84" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9358,10 +9356,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464487</v>
+        <v>464498</v>
       </c>
       <c r="R84" t="n">
-        <v>6785181</v>
+        <v>6785170</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9522,37 +9520,39 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126691497</v>
+        <v>126691440</v>
       </c>
       <c r="B86" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464498</v>
+        <v>464487</v>
       </c>
       <c r="R86" t="n">
-        <v>6785170</v>
+        <v>6785181</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9724,7 +9724,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126691032</v>
+        <v>126690655</v>
       </c>
       <c r="B88" t="n">
         <v>79014</v>
@@ -9762,10 +9762,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464477</v>
+        <v>464462</v>
       </c>
       <c r="R88" t="n">
-        <v>6785195</v>
+        <v>6785217</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9825,7 +9825,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126690655</v>
+        <v>126691032</v>
       </c>
       <c r="B89" t="n">
         <v>79014</v>
@@ -9863,10 +9863,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464462</v>
+        <v>464477</v>
       </c>
       <c r="R89" t="n">
-        <v>6785217</v>
+        <v>6785195</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10130,7 +10130,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126690643</v>
+        <v>126691436</v>
       </c>
       <c r="B92" t="n">
         <v>79014</v>
@@ -10168,10 +10168,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464465</v>
+        <v>464487</v>
       </c>
       <c r="R92" t="n">
-        <v>6785221</v>
+        <v>6785181</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10332,7 +10332,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126691436</v>
+        <v>126690643</v>
       </c>
       <c r="B94" t="n">
         <v>79014</v>
@@ -10370,10 +10370,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464487</v>
+        <v>464465</v>
       </c>
       <c r="R94" t="n">
-        <v>6785181</v>
+        <v>6785221</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11448,7 +11448,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127422560</v>
+        <v>127422249</v>
       </c>
       <c r="B105" t="n">
         <v>79014</v>
@@ -11483,10 +11483,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464493</v>
+        <v>464471</v>
       </c>
       <c r="R105" t="n">
-        <v>6785289</v>
+        <v>6785300</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11555,7 +11555,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127422249</v>
+        <v>127422560</v>
       </c>
       <c r="B106" t="n">
         <v>79014</v>
@@ -11590,10 +11590,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464471</v>
+        <v>464493</v>
       </c>
       <c r="R106" t="n">
-        <v>6785300</v>
+        <v>6785289</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11662,45 +11662,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127423331</v>
+        <v>127427354</v>
       </c>
       <c r="B107" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464480</v>
+        <v>464643</v>
       </c>
       <c r="R107" t="n">
-        <v>6785322</v>
+        <v>6785243</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11732,7 +11737,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11742,7 +11747,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11769,32 +11774,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127422104</v>
+        <v>127423519</v>
       </c>
       <c r="B108" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11804,10 +11809,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464454</v>
+        <v>464487</v>
       </c>
       <c r="R108" t="n">
-        <v>6785288</v>
+        <v>6785354</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11876,7 +11881,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127423519</v>
+        <v>127423611</v>
       </c>
       <c r="B109" t="n">
         <v>79014</v>
@@ -11911,10 +11916,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>464487</v>
+        <v>464488</v>
       </c>
       <c r="R109" t="n">
-        <v>6785354</v>
+        <v>6785340</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11983,32 +11988,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127423611</v>
+        <v>127423331</v>
       </c>
       <c r="B110" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12018,10 +12023,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>464488</v>
+        <v>464480</v>
       </c>
       <c r="R110" t="n">
-        <v>6785340</v>
+        <v>6785322</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12090,50 +12095,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127427354</v>
+        <v>127422104</v>
       </c>
       <c r="B111" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464643</v>
+        <v>464454</v>
       </c>
       <c r="R111" t="n">
-        <v>6785243</v>
+        <v>6785288</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12165,7 +12165,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12202,7 +12202,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127421762</v>
+        <v>127421835</v>
       </c>
       <c r="B112" t="n">
         <v>79014</v>
@@ -12237,10 +12237,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464429</v>
+        <v>464456</v>
       </c>
       <c r="R112" t="n">
-        <v>6785317</v>
+        <v>6785336</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12309,10 +12309,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127421683</v>
+        <v>127421762</v>
       </c>
       <c r="B113" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12320,21 +12320,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12344,10 +12344,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464444</v>
+        <v>464429</v>
       </c>
       <c r="R113" t="n">
-        <v>6785295</v>
+        <v>6785317</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12416,10 +12416,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127421835</v>
+        <v>127421683</v>
       </c>
       <c r="B114" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12427,21 +12427,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12451,10 +12451,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464456</v>
+        <v>464444</v>
       </c>
       <c r="R114" t="n">
-        <v>6785336</v>
+        <v>6785295</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12737,32 +12737,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127423223</v>
+        <v>127422036</v>
       </c>
       <c r="B117" t="n">
-        <v>79603</v>
+        <v>8447</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12772,10 +12772,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464502</v>
+        <v>464445</v>
       </c>
       <c r="R117" t="n">
-        <v>6785318</v>
+        <v>6785311</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12844,7 +12844,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127422036</v>
+        <v>127422304</v>
       </c>
       <c r="B118" t="n">
         <v>8447</v>
@@ -12879,10 +12879,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464445</v>
+        <v>464471</v>
       </c>
       <c r="R118" t="n">
-        <v>6785311</v>
+        <v>6785300</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12951,32 +12951,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127422304</v>
+        <v>127423223</v>
       </c>
       <c r="B119" t="n">
-        <v>8447</v>
+        <v>79603</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12986,10 +12986,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464471</v>
+        <v>464502</v>
       </c>
       <c r="R119" t="n">
-        <v>6785300</v>
+        <v>6785318</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13282,45 +13282,50 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127423422</v>
+        <v>127425909</v>
       </c>
       <c r="B122" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464465</v>
+        <v>464566</v>
       </c>
       <c r="R122" t="n">
-        <v>6785344</v>
+        <v>6785301</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13352,7 +13357,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13362,7 +13367,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13389,7 +13394,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127427379</v>
+        <v>127421841</v>
       </c>
       <c r="B123" t="n">
         <v>8447</v>
@@ -13424,10 +13429,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>464643</v>
+        <v>464456</v>
       </c>
       <c r="R123" t="n">
-        <v>6785243</v>
+        <v>6785336</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13459,7 +13464,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13469,7 +13474,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13496,50 +13501,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127425909</v>
+        <v>127423422</v>
       </c>
       <c r="B124" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464566</v>
+        <v>464465</v>
       </c>
       <c r="R124" t="n">
-        <v>6785301</v>
+        <v>6785344</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13571,7 +13571,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13581,7 +13581,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13608,10 +13608,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127426763</v>
+        <v>127427379</v>
       </c>
       <c r="B125" t="n">
-        <v>58027</v>
+        <v>8447</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13619,39 +13619,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>464578</v>
+        <v>464643</v>
       </c>
       <c r="R125" t="n">
-        <v>6785262</v>
+        <v>6785243</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13720,10 +13715,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127421841</v>
+        <v>127426763</v>
       </c>
       <c r="B126" t="n">
-        <v>8447</v>
+        <v>58027</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13731,34 +13726,39 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464456</v>
+        <v>464578</v>
       </c>
       <c r="R126" t="n">
-        <v>6785336</v>
+        <v>6785262</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14041,50 +14041,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127423538</v>
+        <v>127423379</v>
       </c>
       <c r="B129" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>464487</v>
+        <v>464477</v>
       </c>
       <c r="R129" t="n">
-        <v>6785354</v>
+        <v>6785333</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14153,45 +14148,50 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127423379</v>
+        <v>127423538</v>
       </c>
       <c r="B130" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>464477</v>
+        <v>464487</v>
       </c>
       <c r="R130" t="n">
-        <v>6785333</v>
+        <v>6785354</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14367,32 +14367,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127422589</v>
+        <v>127423972</v>
       </c>
       <c r="B132" t="n">
-        <v>8447</v>
+        <v>79632</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14402,10 +14402,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464502</v>
+        <v>464506</v>
       </c>
       <c r="R132" t="n">
-        <v>6785289</v>
+        <v>6785318</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14474,10 +14474,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127422151</v>
+        <v>127423454</v>
       </c>
       <c r="B133" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14485,39 +14485,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464471</v>
+        <v>464472</v>
       </c>
       <c r="R133" t="n">
-        <v>6785300</v>
+        <v>6785351</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14698,10 +14693,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127423972</v>
+        <v>127422151</v>
       </c>
       <c r="B135" t="n">
-        <v>79632</v>
+        <v>57654</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14709,34 +14704,39 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464506</v>
+        <v>464471</v>
       </c>
       <c r="R135" t="n">
-        <v>6785318</v>
+        <v>6785300</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14805,32 +14805,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127423454</v>
+        <v>127422589</v>
       </c>
       <c r="B136" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14840,10 +14840,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>464472</v>
+        <v>464502</v>
       </c>
       <c r="R136" t="n">
-        <v>6785351</v>
+        <v>6785289</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14912,10 +14912,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127422954</v>
+        <v>127423216</v>
       </c>
       <c r="B137" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14923,21 +14923,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14947,10 +14947,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464492</v>
+        <v>464502</v>
       </c>
       <c r="R137" t="n">
-        <v>6785316</v>
+        <v>6785318</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15019,10 +15019,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127423216</v>
+        <v>127422954</v>
       </c>
       <c r="B138" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15030,21 +15030,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15054,10 +15054,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>464502</v>
+        <v>464492</v>
       </c>
       <c r="R138" t="n">
-        <v>6785318</v>
+        <v>6785316</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15233,32 +15233,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127425810</v>
+        <v>127424838</v>
       </c>
       <c r="B140" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15268,10 +15268,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464558</v>
+        <v>464537</v>
       </c>
       <c r="R140" t="n">
-        <v>6785308</v>
+        <v>6785309</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15313,7 +15313,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15340,32 +15340,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127424901</v>
+        <v>127423228</v>
       </c>
       <c r="B141" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>464544</v>
+        <v>464502</v>
       </c>
       <c r="R141" t="n">
-        <v>6785309</v>
+        <v>6785318</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15447,32 +15447,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127423228</v>
+        <v>127425011</v>
       </c>
       <c r="B142" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15482,10 +15482,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464502</v>
+        <v>464526</v>
       </c>
       <c r="R142" t="n">
-        <v>6785318</v>
+        <v>6785325</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15554,32 +15554,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127424838</v>
+        <v>127425810</v>
       </c>
       <c r="B143" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15589,10 +15589,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>464537</v>
+        <v>464558</v>
       </c>
       <c r="R143" t="n">
-        <v>6785309</v>
+        <v>6785308</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15661,7 +15661,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127425011</v>
+        <v>127424901</v>
       </c>
       <c r="B144" t="n">
         <v>79014</v>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464526</v>
+        <v>464544</v>
       </c>
       <c r="R144" t="n">
-        <v>6785325</v>
+        <v>6785309</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16196,10 +16196,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127422085</v>
+        <v>127422583</v>
       </c>
       <c r="B149" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16207,34 +16207,39 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464454</v>
+        <v>464502</v>
       </c>
       <c r="R149" t="n">
-        <v>6785288</v>
+        <v>6785289</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16410,10 +16415,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127422583</v>
+        <v>127422085</v>
       </c>
       <c r="B151" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16421,39 +16426,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>464502</v>
+        <v>464454</v>
       </c>
       <c r="R151" t="n">
-        <v>6785289</v>
+        <v>6785288</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY152"/>
+  <dimension ref="A1:AY161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12737,45 +12737,50 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127422036</v>
+        <v>127424788</v>
       </c>
       <c r="B117" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464445</v>
+        <v>464526</v>
       </c>
       <c r="R117" t="n">
-        <v>6785311</v>
+        <v>6785298</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12844,7 +12849,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127422304</v>
+        <v>127422036</v>
       </c>
       <c r="B118" t="n">
         <v>8447</v>
@@ -12879,10 +12884,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464471</v>
+        <v>464445</v>
       </c>
       <c r="R118" t="n">
-        <v>6785300</v>
+        <v>6785311</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12951,32 +12956,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127423223</v>
+        <v>127422304</v>
       </c>
       <c r="B119" t="n">
-        <v>79603</v>
+        <v>8447</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12986,10 +12991,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464502</v>
+        <v>464471</v>
       </c>
       <c r="R119" t="n">
-        <v>6785318</v>
+        <v>6785300</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13058,10 +13063,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127424788</v>
+        <v>127423223</v>
       </c>
       <c r="B120" t="n">
-        <v>57654</v>
+        <v>79603</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13069,39 +13074,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464526</v>
+        <v>464502</v>
       </c>
       <c r="R120" t="n">
-        <v>6785298</v>
+        <v>6785318</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -16627,6 +16627,923 @@
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>127465306</v>
+      </c>
+      <c r="B153" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>464656</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6785173</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>127465699</v>
+      </c>
+      <c r="B154" t="n">
+        <v>75138</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>464622</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6785219</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>127465669</v>
+      </c>
+      <c r="B155" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>464621</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6785225</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>127466199</v>
+      </c>
+      <c r="B156" t="n">
+        <v>91780</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>464572</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6785297</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF156" t="inlineStr"/>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>127470562</v>
+      </c>
+      <c r="B157" t="n">
+        <v>91780</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>464476</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6785297</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>127465578</v>
+      </c>
+      <c r="B158" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>464659</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6785196</v>
+      </c>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>127465540</v>
+      </c>
+      <c r="B159" t="n">
+        <v>75138</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>464659</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6785196</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF159" t="inlineStr"/>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>127469037</v>
+      </c>
+      <c r="B160" t="n">
+        <v>91780</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>464491</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6785311</v>
+      </c>
+      <c r="S160" t="n">
+        <v>10</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF160" t="inlineStr"/>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>127465918</v>
+      </c>
+      <c r="B161" t="n">
+        <v>75138</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Kölbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>464578</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6785294</v>
+      </c>
+      <c r="S161" t="n">
+        <v>10</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -12737,50 +12737,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127424788</v>
+        <v>127422036</v>
       </c>
       <c r="B117" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464526</v>
+        <v>464445</v>
       </c>
       <c r="R117" t="n">
-        <v>6785298</v>
+        <v>6785311</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12849,7 +12844,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127422036</v>
+        <v>127422304</v>
       </c>
       <c r="B118" t="n">
         <v>8447</v>
@@ -12884,10 +12879,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464445</v>
+        <v>464471</v>
       </c>
       <c r="R118" t="n">
-        <v>6785311</v>
+        <v>6785300</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12956,32 +12951,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127422304</v>
+        <v>127423223</v>
       </c>
       <c r="B119" t="n">
-        <v>8447</v>
+        <v>79603</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12991,10 +12986,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464471</v>
+        <v>464502</v>
       </c>
       <c r="R119" t="n">
-        <v>6785300</v>
+        <v>6785318</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13063,10 +13058,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127423223</v>
+        <v>127424788</v>
       </c>
       <c r="B120" t="n">
-        <v>79603</v>
+        <v>57654</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13074,34 +13069,39 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464502</v>
+        <v>464526</v>
       </c>
       <c r="R120" t="n">
-        <v>6785318</v>
+        <v>6785298</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13501,10 +13501,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127423422</v>
+        <v>127426763</v>
       </c>
       <c r="B124" t="n">
-        <v>8447</v>
+        <v>58027</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13512,34 +13512,39 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464465</v>
+        <v>464578</v>
       </c>
       <c r="R124" t="n">
-        <v>6785344</v>
+        <v>6785262</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13571,7 +13576,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13581,7 +13586,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13608,7 +13613,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127427379</v>
+        <v>127423422</v>
       </c>
       <c r="B125" t="n">
         <v>8447</v>
@@ -13643,10 +13648,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>464643</v>
+        <v>464465</v>
       </c>
       <c r="R125" t="n">
-        <v>6785243</v>
+        <v>6785344</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13678,7 +13683,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13688,7 +13693,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13715,10 +13720,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127426763</v>
+        <v>127427379</v>
       </c>
       <c r="B126" t="n">
-        <v>58027</v>
+        <v>8447</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13726,39 +13731,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464578</v>
+        <v>464643</v>
       </c>
       <c r="R126" t="n">
-        <v>6785262</v>
+        <v>6785243</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14912,10 +14912,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127423216</v>
+        <v>127422954</v>
       </c>
       <c r="B137" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14923,21 +14923,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14947,10 +14947,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464502</v>
+        <v>464492</v>
       </c>
       <c r="R137" t="n">
-        <v>6785318</v>
+        <v>6785316</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15019,7 +15019,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127422954</v>
+        <v>127423983</v>
       </c>
       <c r="B138" t="n">
         <v>79014</v>
@@ -15054,10 +15054,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>464492</v>
+        <v>464506</v>
       </c>
       <c r="R138" t="n">
-        <v>6785316</v>
+        <v>6785318</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15126,10 +15126,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127423983</v>
+        <v>127423216</v>
       </c>
       <c r="B139" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15137,21 +15137,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15161,7 +15161,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464506</v>
+        <v>464502</v>
       </c>
       <c r="R139" t="n">
         <v>6785318</v>
@@ -15233,32 +15233,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127424838</v>
+        <v>127425011</v>
       </c>
       <c r="B140" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15268,10 +15268,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464537</v>
+        <v>464526</v>
       </c>
       <c r="R140" t="n">
-        <v>6785309</v>
+        <v>6785325</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15340,32 +15340,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127423228</v>
+        <v>127425810</v>
       </c>
       <c r="B141" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>464502</v>
+        <v>464558</v>
       </c>
       <c r="R141" t="n">
-        <v>6785318</v>
+        <v>6785308</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15447,7 +15447,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127425011</v>
+        <v>127424901</v>
       </c>
       <c r="B142" t="n">
         <v>79014</v>
@@ -15482,10 +15482,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464526</v>
+        <v>464544</v>
       </c>
       <c r="R142" t="n">
-        <v>6785325</v>
+        <v>6785309</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15554,32 +15554,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127425810</v>
+        <v>127424838</v>
       </c>
       <c r="B143" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15589,10 +15589,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>464558</v>
+        <v>464537</v>
       </c>
       <c r="R143" t="n">
-        <v>6785308</v>
+        <v>6785309</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15661,32 +15661,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127424901</v>
+        <v>127423228</v>
       </c>
       <c r="B144" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464544</v>
+        <v>464502</v>
       </c>
       <c r="R144" t="n">
-        <v>6785309</v>
+        <v>6785318</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16196,10 +16196,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127422583</v>
+        <v>127422085</v>
       </c>
       <c r="B149" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16207,39 +16207,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464502</v>
+        <v>464454</v>
       </c>
       <c r="R149" t="n">
-        <v>6785289</v>
+        <v>6785288</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16415,10 +16410,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127422085</v>
+        <v>127422583</v>
       </c>
       <c r="B151" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16426,34 +16421,39 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>464454</v>
+        <v>464502</v>
       </c>
       <c r="R151" t="n">
-        <v>6785288</v>
+        <v>6785289</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -11244,7 +11244,7 @@
         <v>127156818</v>
       </c>
       <c r="B103" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>127020226</v>
       </c>
       <c r="B104" t="n">
-        <v>91787</v>
+        <v>91791</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>127422249</v>
       </c>
       <c r="B105" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>127422560</v>
       </c>
       <c r="B106" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11662,10 +11662,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127427354</v>
+        <v>127423519</v>
       </c>
       <c r="B107" t="n">
-        <v>57654</v>
+        <v>79018</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11673,39 +11673,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464643</v>
+        <v>464487</v>
       </c>
       <c r="R107" t="n">
-        <v>6785243</v>
+        <v>6785354</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11737,7 +11732,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11747,7 +11742,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11774,10 +11769,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127423519</v>
+        <v>127423611</v>
       </c>
       <c r="B108" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11809,10 +11804,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464487</v>
+        <v>464488</v>
       </c>
       <c r="R108" t="n">
-        <v>6785354</v>
+        <v>6785340</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11881,32 +11876,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127423611</v>
+        <v>127423331</v>
       </c>
       <c r="B109" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11916,10 +11911,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>464488</v>
+        <v>464480</v>
       </c>
       <c r="R109" t="n">
-        <v>6785340</v>
+        <v>6785322</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11988,10 +11983,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127423331</v>
+        <v>127422104</v>
       </c>
       <c r="B110" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12023,10 +12018,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>464480</v>
+        <v>464454</v>
       </c>
       <c r="R110" t="n">
-        <v>6785322</v>
+        <v>6785288</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12095,45 +12090,50 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127422104</v>
+        <v>127427354</v>
       </c>
       <c r="B111" t="n">
-        <v>8447</v>
+        <v>57658</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464454</v>
+        <v>464643</v>
       </c>
       <c r="R111" t="n">
-        <v>6785288</v>
+        <v>6785243</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12165,7 +12165,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12205,7 +12205,7 @@
         <v>127421835</v>
       </c>
       <c r="B112" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>127421762</v>
       </c>
       <c r="B113" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12416,10 +12416,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127421683</v>
+        <v>127423850</v>
       </c>
       <c r="B114" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12427,21 +12427,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12451,10 +12451,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464444</v>
+        <v>464502</v>
       </c>
       <c r="R114" t="n">
-        <v>6785295</v>
+        <v>6785318</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12523,10 +12523,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127423850</v>
+        <v>127421683</v>
       </c>
       <c r="B115" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12534,21 +12534,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12558,10 +12558,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464502</v>
+        <v>464444</v>
       </c>
       <c r="R115" t="n">
-        <v>6785318</v>
+        <v>6785295</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12633,7 +12633,7 @@
         <v>127425834</v>
       </c>
       <c r="B116" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>127422036</v>
       </c>
       <c r="B117" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>127422304</v>
       </c>
       <c r="B118" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12951,10 +12951,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127423223</v>
+        <v>127424788</v>
       </c>
       <c r="B119" t="n">
-        <v>79603</v>
+        <v>57658</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12962,34 +12962,39 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464502</v>
+        <v>464526</v>
       </c>
       <c r="R119" t="n">
-        <v>6785318</v>
+        <v>6785298</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13058,10 +13063,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127424788</v>
+        <v>127423223</v>
       </c>
       <c r="B120" t="n">
-        <v>57654</v>
+        <v>79607</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13069,39 +13074,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464526</v>
+        <v>464502</v>
       </c>
       <c r="R120" t="n">
-        <v>6785298</v>
+        <v>6785318</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13173,7 +13173,7 @@
         <v>127423326</v>
       </c>
       <c r="B121" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>127425909</v>
       </c>
       <c r="B122" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13394,10 +13394,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127421841</v>
+        <v>127426763</v>
       </c>
       <c r="B123" t="n">
-        <v>8447</v>
+        <v>58031</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13405,34 +13405,39 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>464456</v>
+        <v>464578</v>
       </c>
       <c r="R123" t="n">
-        <v>6785336</v>
+        <v>6785262</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13464,7 +13469,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13474,7 +13479,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13501,10 +13506,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127426763</v>
+        <v>127421841</v>
       </c>
       <c r="B124" t="n">
-        <v>58027</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13512,39 +13517,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464578</v>
+        <v>464456</v>
       </c>
       <c r="R124" t="n">
-        <v>6785262</v>
+        <v>6785336</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13576,7 +13576,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13616,7 +13616,7 @@
         <v>127423422</v>
       </c>
       <c r="B125" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>127427379</v>
       </c>
       <c r="B126" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>127423221</v>
       </c>
       <c r="B127" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>127421737</v>
       </c>
       <c r="B128" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>127423379</v>
       </c>
       <c r="B129" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>127423538</v>
       </c>
       <c r="B130" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>127422760</v>
       </c>
       <c r="B131" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14367,10 +14367,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127423972</v>
+        <v>127422151</v>
       </c>
       <c r="B132" t="n">
-        <v>79632</v>
+        <v>57658</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14378,34 +14378,39 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464506</v>
+        <v>464471</v>
       </c>
       <c r="R132" t="n">
-        <v>6785318</v>
+        <v>6785300</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14477,7 +14482,7 @@
         <v>127423454</v>
       </c>
       <c r="B133" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14581,10 +14586,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127421996</v>
+        <v>127423972</v>
       </c>
       <c r="B134" t="n">
-        <v>57654</v>
+        <v>79636</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14592,39 +14597,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464445</v>
+        <v>464506</v>
       </c>
       <c r="R134" t="n">
-        <v>6785311</v>
+        <v>6785318</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14693,10 +14693,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127422151</v>
+        <v>127421996</v>
       </c>
       <c r="B135" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -14733,10 +14733,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464471</v>
+        <v>464445</v>
       </c>
       <c r="R135" t="n">
-        <v>6785300</v>
+        <v>6785311</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14808,7 +14808,7 @@
         <v>127422589</v>
       </c>
       <c r="B136" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>127422954</v>
       </c>
       <c r="B137" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>127423983</v>
       </c>
       <c r="B138" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>127423216</v>
       </c>
       <c r="B139" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15233,32 +15233,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127425011</v>
+        <v>127424838</v>
       </c>
       <c r="B140" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15268,10 +15268,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464526</v>
+        <v>464537</v>
       </c>
       <c r="R140" t="n">
-        <v>6785325</v>
+        <v>6785309</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15340,32 +15340,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127425810</v>
+        <v>127423228</v>
       </c>
       <c r="B141" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>464558</v>
+        <v>464502</v>
       </c>
       <c r="R141" t="n">
-        <v>6785308</v>
+        <v>6785318</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15447,10 +15447,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127424901</v>
+        <v>127425011</v>
       </c>
       <c r="B142" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15482,10 +15482,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464544</v>
+        <v>464526</v>
       </c>
       <c r="R142" t="n">
-        <v>6785309</v>
+        <v>6785325</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15554,32 +15554,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127424838</v>
+        <v>127425810</v>
       </c>
       <c r="B143" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15589,10 +15589,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>464537</v>
+        <v>464558</v>
       </c>
       <c r="R143" t="n">
-        <v>6785309</v>
+        <v>6785308</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15661,32 +15661,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127423228</v>
+        <v>127424901</v>
       </c>
       <c r="B144" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464502</v>
+        <v>464544</v>
       </c>
       <c r="R144" t="n">
-        <v>6785318</v>
+        <v>6785309</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15771,7 +15771,7 @@
         <v>127423546</v>
       </c>
       <c r="B145" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>127424833</v>
       </c>
       <c r="B146" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>127423429</v>
       </c>
       <c r="B147" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>127423346</v>
       </c>
       <c r="B148" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16196,10 +16196,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127422085</v>
+        <v>127421885</v>
       </c>
       <c r="B149" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16231,10 +16231,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464454</v>
+        <v>464445</v>
       </c>
       <c r="R149" t="n">
-        <v>6785288</v>
+        <v>6785311</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16303,10 +16303,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127421885</v>
+        <v>127422085</v>
       </c>
       <c r="B150" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16338,10 +16338,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>464445</v>
+        <v>464454</v>
       </c>
       <c r="R150" t="n">
-        <v>6785311</v>
+        <v>6785288</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16413,7 +16413,7 @@
         <v>127422583</v>
       </c>
       <c r="B151" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>127421603</v>
       </c>
       <c r="B152" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>127465306</v>
       </c>
       <c r="B153" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>127465699</v>
       </c>
       <c r="B154" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>127465669</v>
       </c>
       <c r="B155" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>127466199</v>
       </c>
       <c r="B156" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>127470562</v>
       </c>
       <c r="B157" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>127465578</v>
       </c>
       <c r="B158" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>127465540</v>
       </c>
       <c r="B159" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17344,32 +17344,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127469037</v>
+        <v>127465918</v>
       </c>
       <c r="B160" t="n">
-        <v>91780</v>
+        <v>75142</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17382,10 +17382,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>464491</v>
+        <v>464578</v>
       </c>
       <c r="R160" t="n">
-        <v>6785311</v>
+        <v>6785294</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17445,32 +17445,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127465918</v>
+        <v>127469037</v>
       </c>
       <c r="B161" t="n">
-        <v>75138</v>
+        <v>91784</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17483,10 +17483,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>464578</v>
+        <v>464491</v>
       </c>
       <c r="R161" t="n">
-        <v>6785294</v>
+        <v>6785311</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -11662,7 +11662,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127423519</v>
+        <v>127423611</v>
       </c>
       <c r="B107" t="n">
         <v>79018</v>
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464487</v>
+        <v>464488</v>
       </c>
       <c r="R107" t="n">
-        <v>6785354</v>
+        <v>6785340</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11769,10 +11769,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127423611</v>
+        <v>127427354</v>
       </c>
       <c r="B108" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11780,34 +11780,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464488</v>
+        <v>464643</v>
       </c>
       <c r="R108" t="n">
-        <v>6785340</v>
+        <v>6785243</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11839,7 +11844,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11849,7 +11854,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11876,32 +11881,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127423331</v>
+        <v>127423519</v>
       </c>
       <c r="B109" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11911,10 +11916,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>464480</v>
+        <v>464487</v>
       </c>
       <c r="R109" t="n">
-        <v>6785322</v>
+        <v>6785354</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11983,7 +11988,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127422104</v>
+        <v>127423331</v>
       </c>
       <c r="B110" t="n">
         <v>8450</v>
@@ -12018,10 +12023,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>464454</v>
+        <v>464480</v>
       </c>
       <c r="R110" t="n">
-        <v>6785288</v>
+        <v>6785322</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12090,50 +12095,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127427354</v>
+        <v>127422104</v>
       </c>
       <c r="B111" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464643</v>
+        <v>464454</v>
       </c>
       <c r="R111" t="n">
-        <v>6785243</v>
+        <v>6785288</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12165,7 +12165,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12416,10 +12416,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127423850</v>
+        <v>127421683</v>
       </c>
       <c r="B114" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12427,21 +12427,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12451,10 +12451,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464502</v>
+        <v>464444</v>
       </c>
       <c r="R114" t="n">
-        <v>6785318</v>
+        <v>6785295</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12523,10 +12523,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127421683</v>
+        <v>127423850</v>
       </c>
       <c r="B115" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12534,21 +12534,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12558,10 +12558,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464444</v>
+        <v>464502</v>
       </c>
       <c r="R115" t="n">
-        <v>6785295</v>
+        <v>6785318</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12737,45 +12737,50 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127422036</v>
+        <v>127424788</v>
       </c>
       <c r="B117" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464445</v>
+        <v>464526</v>
       </c>
       <c r="R117" t="n">
-        <v>6785311</v>
+        <v>6785298</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12844,7 +12849,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127422304</v>
+        <v>127422036</v>
       </c>
       <c r="B118" t="n">
         <v>8450</v>
@@ -12879,10 +12884,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464471</v>
+        <v>464445</v>
       </c>
       <c r="R118" t="n">
-        <v>6785300</v>
+        <v>6785311</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12951,50 +12956,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127424788</v>
+        <v>127422304</v>
       </c>
       <c r="B119" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464526</v>
+        <v>464471</v>
       </c>
       <c r="R119" t="n">
-        <v>6785298</v>
+        <v>6785300</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13934,45 +13934,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127421737</v>
+        <v>127423538</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>464429</v>
+        <v>464487</v>
       </c>
       <c r="R128" t="n">
-        <v>6785317</v>
+        <v>6785354</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14041,7 +14046,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127423379</v>
+        <v>127421737</v>
       </c>
       <c r="B129" t="n">
         <v>8450</v>
@@ -14076,10 +14081,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>464477</v>
+        <v>464429</v>
       </c>
       <c r="R129" t="n">
-        <v>6785333</v>
+        <v>6785317</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14148,50 +14153,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127423538</v>
+        <v>127423379</v>
       </c>
       <c r="B130" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>464487</v>
+        <v>464477</v>
       </c>
       <c r="R130" t="n">
-        <v>6785354</v>
+        <v>6785333</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14367,50 +14367,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127422151</v>
+        <v>127422589</v>
       </c>
       <c r="B132" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464471</v>
+        <v>464502</v>
       </c>
       <c r="R132" t="n">
-        <v>6785300</v>
+        <v>6785289</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14479,10 +14474,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127423454</v>
+        <v>127421996</v>
       </c>
       <c r="B133" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14490,34 +14485,39 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464472</v>
+        <v>464445</v>
       </c>
       <c r="R133" t="n">
-        <v>6785351</v>
+        <v>6785311</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14586,10 +14586,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127423972</v>
+        <v>127422151</v>
       </c>
       <c r="B134" t="n">
-        <v>79636</v>
+        <v>57658</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14597,34 +14597,39 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464506</v>
+        <v>464471</v>
       </c>
       <c r="R134" t="n">
-        <v>6785318</v>
+        <v>6785300</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14693,10 +14698,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127421996</v>
+        <v>127423972</v>
       </c>
       <c r="B135" t="n">
-        <v>57658</v>
+        <v>79636</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14704,39 +14709,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464445</v>
+        <v>464506</v>
       </c>
       <c r="R135" t="n">
-        <v>6785311</v>
+        <v>6785318</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14805,32 +14805,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127422589</v>
+        <v>127423454</v>
       </c>
       <c r="B136" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14840,10 +14840,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>464502</v>
+        <v>464472</v>
       </c>
       <c r="R136" t="n">
-        <v>6785289</v>
+        <v>6785351</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15233,32 +15233,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127424838</v>
+        <v>127425011</v>
       </c>
       <c r="B140" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15268,10 +15268,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464537</v>
+        <v>464526</v>
       </c>
       <c r="R140" t="n">
-        <v>6785309</v>
+        <v>6785325</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15340,32 +15340,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127423228</v>
+        <v>127425810</v>
       </c>
       <c r="B141" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>464502</v>
+        <v>464558</v>
       </c>
       <c r="R141" t="n">
-        <v>6785318</v>
+        <v>6785308</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15447,7 +15447,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127425011</v>
+        <v>127424901</v>
       </c>
       <c r="B142" t="n">
         <v>79018</v>
@@ -15482,10 +15482,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464526</v>
+        <v>464544</v>
       </c>
       <c r="R142" t="n">
-        <v>6785325</v>
+        <v>6785309</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15554,32 +15554,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127425810</v>
+        <v>127424838</v>
       </c>
       <c r="B143" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15589,10 +15589,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>464558</v>
+        <v>464537</v>
       </c>
       <c r="R143" t="n">
-        <v>6785308</v>
+        <v>6785309</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15661,32 +15661,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127424901</v>
+        <v>127423228</v>
       </c>
       <c r="B144" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464544</v>
+        <v>464502</v>
       </c>
       <c r="R144" t="n">
-        <v>6785309</v>
+        <v>6785318</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17037,37 +17037,42 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127470562</v>
+        <v>127465578</v>
       </c>
       <c r="B157" t="n">
-        <v>91784</v>
+        <v>57658</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -17075,10 +17080,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>464476</v>
+        <v>464659</v>
       </c>
       <c r="R157" t="n">
-        <v>6785297</v>
+        <v>6785196</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17119,7 +17124,6 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -17138,42 +17142,37 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127465578</v>
+        <v>127470562</v>
       </c>
       <c r="B158" t="n">
-        <v>57658</v>
+        <v>91784</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
@@ -17181,10 +17180,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>464659</v>
+        <v>464476</v>
       </c>
       <c r="R158" t="n">
-        <v>6785196</v>
+        <v>6785297</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17225,6 +17224,7 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -11448,7 +11448,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127422249</v>
+        <v>127422560</v>
       </c>
       <c r="B105" t="n">
         <v>79018</v>
@@ -11483,10 +11483,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464471</v>
+        <v>464493</v>
       </c>
       <c r="R105" t="n">
-        <v>6785300</v>
+        <v>6785289</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11555,7 +11555,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127422560</v>
+        <v>127422249</v>
       </c>
       <c r="B106" t="n">
         <v>79018</v>
@@ -11590,10 +11590,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464493</v>
+        <v>464471</v>
       </c>
       <c r="R106" t="n">
-        <v>6785289</v>
+        <v>6785300</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11662,7 +11662,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127423611</v>
+        <v>127423519</v>
       </c>
       <c r="B107" t="n">
         <v>79018</v>
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464488</v>
+        <v>464487</v>
       </c>
       <c r="R107" t="n">
-        <v>6785340</v>
+        <v>6785354</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11881,7 +11881,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127423519</v>
+        <v>127423611</v>
       </c>
       <c r="B109" t="n">
         <v>79018</v>
@@ -11916,10 +11916,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>464487</v>
+        <v>464488</v>
       </c>
       <c r="R109" t="n">
-        <v>6785354</v>
+        <v>6785340</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14367,45 +14367,50 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127422589</v>
+        <v>127421996</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464502</v>
+        <v>464445</v>
       </c>
       <c r="R132" t="n">
-        <v>6785289</v>
+        <v>6785311</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14474,7 +14479,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127421996</v>
+        <v>127422151</v>
       </c>
       <c r="B133" t="n">
         <v>57658</v>
@@ -14505,7 +14510,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -14514,10 +14519,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464445</v>
+        <v>464471</v>
       </c>
       <c r="R133" t="n">
-        <v>6785311</v>
+        <v>6785300</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14586,50 +14591,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127422151</v>
+        <v>127422589</v>
       </c>
       <c r="B134" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464471</v>
+        <v>464502</v>
       </c>
       <c r="R134" t="n">
-        <v>6785300</v>
+        <v>6785289</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15233,32 +15233,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127425011</v>
+        <v>127424838</v>
       </c>
       <c r="B140" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15268,10 +15268,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464526</v>
+        <v>464537</v>
       </c>
       <c r="R140" t="n">
-        <v>6785325</v>
+        <v>6785309</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15340,32 +15340,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127425810</v>
+        <v>127423228</v>
       </c>
       <c r="B141" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>464558</v>
+        <v>464502</v>
       </c>
       <c r="R141" t="n">
-        <v>6785308</v>
+        <v>6785318</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15447,7 +15447,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127424901</v>
+        <v>127425011</v>
       </c>
       <c r="B142" t="n">
         <v>79018</v>
@@ -15482,10 +15482,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464544</v>
+        <v>464526</v>
       </c>
       <c r="R142" t="n">
-        <v>6785309</v>
+        <v>6785325</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15554,32 +15554,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127424838</v>
+        <v>127425810</v>
       </c>
       <c r="B143" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15589,10 +15589,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>464537</v>
+        <v>464558</v>
       </c>
       <c r="R143" t="n">
-        <v>6785309</v>
+        <v>6785308</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15661,32 +15661,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127423228</v>
+        <v>127424901</v>
       </c>
       <c r="B144" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464502</v>
+        <v>464544</v>
       </c>
       <c r="R144" t="n">
-        <v>6785318</v>
+        <v>6785309</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16196,10 +16196,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127421885</v>
+        <v>127422583</v>
       </c>
       <c r="B149" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16207,34 +16207,39 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464445</v>
+        <v>464502</v>
       </c>
       <c r="R149" t="n">
-        <v>6785311</v>
+        <v>6785289</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16303,7 +16308,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127422085</v>
+        <v>127421885</v>
       </c>
       <c r="B150" t="n">
         <v>79018</v>
@@ -16338,10 +16343,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>464454</v>
+        <v>464445</v>
       </c>
       <c r="R150" t="n">
-        <v>6785288</v>
+        <v>6785311</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16410,10 +16415,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127422583</v>
+        <v>127422085</v>
       </c>
       <c r="B151" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16421,39 +16426,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>464502</v>
+        <v>464454</v>
       </c>
       <c r="R151" t="n">
-        <v>6785289</v>
+        <v>6785288</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY161"/>
+  <dimension ref="A1:AY160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11662,7 +11662,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127423519</v>
+        <v>127423611</v>
       </c>
       <c r="B107" t="n">
         <v>79018</v>
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464487</v>
+        <v>464488</v>
       </c>
       <c r="R107" t="n">
-        <v>6785354</v>
+        <v>6785340</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11881,7 +11881,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127423611</v>
+        <v>127423519</v>
       </c>
       <c r="B109" t="n">
         <v>79018</v>
@@ -11916,10 +11916,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>464488</v>
+        <v>464487</v>
       </c>
       <c r="R109" t="n">
-        <v>6785340</v>
+        <v>6785354</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13170,27 +13170,27 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127423326</v>
+        <v>127426763</v>
       </c>
       <c r="B121" t="n">
-        <v>57658</v>
+        <v>58031</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -13201,7 +13201,7 @@
       <c r="I121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13210,10 +13210,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464480</v>
+        <v>464578</v>
       </c>
       <c r="R121" t="n">
-        <v>6785322</v>
+        <v>6785262</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13245,7 +13245,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13255,7 +13255,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13282,7 +13282,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127425909</v>
+        <v>127423326</v>
       </c>
       <c r="B122" t="n">
         <v>57658</v>
@@ -13313,7 +13313,7 @@
       <c r="I122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -13322,10 +13322,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464566</v>
+        <v>464480</v>
       </c>
       <c r="R122" t="n">
-        <v>6785301</v>
+        <v>6785322</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13367,7 +13367,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13394,27 +13394,27 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127426763</v>
+        <v>127425909</v>
       </c>
       <c r="B123" t="n">
-        <v>58031</v>
+        <v>57658</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -13425,7 +13425,7 @@
       <c r="I123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -13434,10 +13434,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>464578</v>
+        <v>464566</v>
       </c>
       <c r="R123" t="n">
-        <v>6785262</v>
+        <v>6785301</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14367,50 +14367,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127421996</v>
+        <v>127422589</v>
       </c>
       <c r="B132" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464445</v>
+        <v>464502</v>
       </c>
       <c r="R132" t="n">
-        <v>6785311</v>
+        <v>6785289</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14479,7 +14474,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127422151</v>
+        <v>127421996</v>
       </c>
       <c r="B133" t="n">
         <v>57658</v>
@@ -14510,7 +14505,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -14519,10 +14514,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464471</v>
+        <v>464445</v>
       </c>
       <c r="R133" t="n">
-        <v>6785300</v>
+        <v>6785311</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14591,45 +14586,50 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127422589</v>
+        <v>127422151</v>
       </c>
       <c r="B134" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464502</v>
+        <v>464471</v>
       </c>
       <c r="R134" t="n">
-        <v>6785289</v>
+        <v>6785300</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16196,10 +16196,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127422583</v>
+        <v>127421885</v>
       </c>
       <c r="B149" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16207,39 +16207,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464502</v>
+        <v>464445</v>
       </c>
       <c r="R149" t="n">
-        <v>6785289</v>
+        <v>6785311</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16308,7 +16303,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127421885</v>
+        <v>127422085</v>
       </c>
       <c r="B150" t="n">
         <v>79018</v>
@@ -16343,10 +16338,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>464445</v>
+        <v>464454</v>
       </c>
       <c r="R150" t="n">
-        <v>6785311</v>
+        <v>6785288</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16415,10 +16410,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127422085</v>
+        <v>127422583</v>
       </c>
       <c r="B151" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16426,34 +16421,39 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>464454</v>
+        <v>464502</v>
       </c>
       <c r="R151" t="n">
-        <v>6785288</v>
+        <v>6785289</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16936,37 +16936,42 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127466199</v>
+        <v>127465578</v>
       </c>
       <c r="B156" t="n">
-        <v>91784</v>
+        <v>57658</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -16974,10 +16979,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>464572</v>
+        <v>464659</v>
       </c>
       <c r="R156" t="n">
-        <v>6785297</v>
+        <v>6785196</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17018,7 +17023,6 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -17037,10 +17041,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127465578</v>
+        <v>127465540</v>
       </c>
       <c r="B157" t="n">
-        <v>57658</v>
+        <v>75142</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17048,31 +17052,26 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -17124,6 +17123,7 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -17142,32 +17142,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127470562</v>
+        <v>127465918</v>
       </c>
       <c r="B158" t="n">
-        <v>91784</v>
+        <v>75142</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17180,10 +17180,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>464476</v>
+        <v>464578</v>
       </c>
       <c r="R158" t="n">
-        <v>6785297</v>
+        <v>6785294</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17243,32 +17243,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127465540</v>
+        <v>127675974</v>
       </c>
       <c r="B159" t="n">
-        <v>75142</v>
+        <v>91784</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17281,10 +17281,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>464659</v>
+        <v>464612</v>
       </c>
       <c r="R159" t="n">
-        <v>6785196</v>
+        <v>6785260</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17317,6 +17317,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17344,32 +17349,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127465918</v>
+        <v>127470562</v>
       </c>
       <c r="B160" t="n">
-        <v>75142</v>
+        <v>91784</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17382,10 +17387,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>464578</v>
+        <v>464476</v>
       </c>
       <c r="R160" t="n">
-        <v>6785294</v>
+        <v>6785297</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17420,6 +17425,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning</t>
+        </is>
+      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
@@ -17442,107 +17452,6 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>127469037</v>
-      </c>
-      <c r="B161" t="n">
-        <v>91784</v>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E161" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-      <c r="P161" t="inlineStr">
-        <is>
-          <t>Kölbron, Dlr</t>
-        </is>
-      </c>
-      <c r="Q161" t="n">
-        <v>464491</v>
-      </c>
-      <c r="R161" t="n">
-        <v>6785311</v>
-      </c>
-      <c r="S161" t="n">
-        <v>10</v>
-      </c>
-      <c r="T161" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U161" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="V161" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W161" t="inlineStr">
-        <is>
-          <t>Våmhus</t>
-        </is>
-      </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AD161" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE161" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF161" t="inlineStr"/>
-      <c r="AG161" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT161" t="inlineStr"/>
-      <c r="AW161" t="inlineStr">
-        <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AX161" t="inlineStr">
-        <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AY161" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -11448,7 +11448,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127422560</v>
+        <v>127422249</v>
       </c>
       <c r="B105" t="n">
         <v>79018</v>
@@ -11483,10 +11483,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464493</v>
+        <v>464471</v>
       </c>
       <c r="R105" t="n">
-        <v>6785289</v>
+        <v>6785300</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11555,7 +11555,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127422249</v>
+        <v>127422560</v>
       </c>
       <c r="B106" t="n">
         <v>79018</v>
@@ -11590,10 +11590,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464471</v>
+        <v>464493</v>
       </c>
       <c r="R106" t="n">
-        <v>6785300</v>
+        <v>6785289</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11662,7 +11662,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127423611</v>
+        <v>127423519</v>
       </c>
       <c r="B107" t="n">
         <v>79018</v>
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464488</v>
+        <v>464487</v>
       </c>
       <c r="R107" t="n">
-        <v>6785340</v>
+        <v>6785354</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11769,10 +11769,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127427354</v>
+        <v>127423611</v>
       </c>
       <c r="B108" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11780,39 +11780,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464643</v>
+        <v>464488</v>
       </c>
       <c r="R108" t="n">
-        <v>6785243</v>
+        <v>6785340</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11844,7 +11839,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11854,7 +11849,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11881,10 +11876,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127423519</v>
+        <v>127427354</v>
       </c>
       <c r="B109" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11892,34 +11887,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>464487</v>
+        <v>464643</v>
       </c>
       <c r="R109" t="n">
-        <v>6785354</v>
+        <v>6785243</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12416,10 +12416,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127421683</v>
+        <v>127423850</v>
       </c>
       <c r="B114" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12427,21 +12427,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12451,10 +12451,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464444</v>
+        <v>464502</v>
       </c>
       <c r="R114" t="n">
-        <v>6785295</v>
+        <v>6785318</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12523,10 +12523,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127423850</v>
+        <v>127421683</v>
       </c>
       <c r="B115" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12534,21 +12534,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12558,10 +12558,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464502</v>
+        <v>464444</v>
       </c>
       <c r="R115" t="n">
-        <v>6785318</v>
+        <v>6785295</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14367,32 +14367,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127422589</v>
+        <v>127423454</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14402,10 +14402,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464502</v>
+        <v>464472</v>
       </c>
       <c r="R132" t="n">
-        <v>6785289</v>
+        <v>6785351</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14474,10 +14474,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127421996</v>
+        <v>127423972</v>
       </c>
       <c r="B133" t="n">
-        <v>57658</v>
+        <v>79636</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14485,39 +14485,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464445</v>
+        <v>464506</v>
       </c>
       <c r="R133" t="n">
-        <v>6785311</v>
+        <v>6785318</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14586,7 +14581,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127422151</v>
+        <v>127421996</v>
       </c>
       <c r="B134" t="n">
         <v>57658</v>
@@ -14617,7 +14612,7 @@
       <c r="I134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -14626,10 +14621,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464471</v>
+        <v>464445</v>
       </c>
       <c r="R134" t="n">
-        <v>6785300</v>
+        <v>6785311</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14698,10 +14693,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127423972</v>
+        <v>127422151</v>
       </c>
       <c r="B135" t="n">
-        <v>79636</v>
+        <v>57658</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14709,34 +14704,39 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464506</v>
+        <v>464471</v>
       </c>
       <c r="R135" t="n">
-        <v>6785318</v>
+        <v>6785300</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14805,32 +14805,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127423454</v>
+        <v>127422589</v>
       </c>
       <c r="B136" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14840,10 +14840,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>464472</v>
+        <v>464502</v>
       </c>
       <c r="R136" t="n">
-        <v>6785351</v>
+        <v>6785289</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14912,10 +14912,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127422954</v>
+        <v>127423216</v>
       </c>
       <c r="B137" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14923,21 +14923,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14947,10 +14947,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464492</v>
+        <v>464502</v>
       </c>
       <c r="R137" t="n">
-        <v>6785316</v>
+        <v>6785318</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15019,7 +15019,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127423983</v>
+        <v>127422954</v>
       </c>
       <c r="B138" t="n">
         <v>79018</v>
@@ -15054,10 +15054,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>464506</v>
+        <v>464492</v>
       </c>
       <c r="R138" t="n">
-        <v>6785318</v>
+        <v>6785316</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15126,10 +15126,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127423216</v>
+        <v>127423983</v>
       </c>
       <c r="B139" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15137,21 +15137,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15161,7 +15161,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464502</v>
+        <v>464506</v>
       </c>
       <c r="R139" t="n">
         <v>6785318</v>
@@ -15233,32 +15233,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127424838</v>
+        <v>127425011</v>
       </c>
       <c r="B140" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15268,10 +15268,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464537</v>
+        <v>464526</v>
       </c>
       <c r="R140" t="n">
-        <v>6785309</v>
+        <v>6785325</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15340,32 +15340,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127423228</v>
+        <v>127425810</v>
       </c>
       <c r="B141" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>464502</v>
+        <v>464558</v>
       </c>
       <c r="R141" t="n">
-        <v>6785318</v>
+        <v>6785308</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15447,7 +15447,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127425011</v>
+        <v>127424901</v>
       </c>
       <c r="B142" t="n">
         <v>79018</v>
@@ -15482,10 +15482,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464526</v>
+        <v>464544</v>
       </c>
       <c r="R142" t="n">
-        <v>6785325</v>
+        <v>6785309</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15554,32 +15554,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127425810</v>
+        <v>127424838</v>
       </c>
       <c r="B143" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15589,10 +15589,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>464558</v>
+        <v>464537</v>
       </c>
       <c r="R143" t="n">
-        <v>6785308</v>
+        <v>6785309</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15661,32 +15661,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127424901</v>
+        <v>127423228</v>
       </c>
       <c r="B144" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464544</v>
+        <v>464502</v>
       </c>
       <c r="R144" t="n">
-        <v>6785309</v>
+        <v>6785318</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -13170,10 +13170,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127426763</v>
+        <v>127421841</v>
       </c>
       <c r="B121" t="n">
-        <v>58031</v>
+        <v>8450</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13181,39 +13181,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464578</v>
+        <v>464456</v>
       </c>
       <c r="R121" t="n">
-        <v>6785262</v>
+        <v>6785336</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13245,7 +13240,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13255,7 +13250,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13282,50 +13277,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127423326</v>
+        <v>127423422</v>
       </c>
       <c r="B122" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464480</v>
+        <v>464465</v>
       </c>
       <c r="R122" t="n">
-        <v>6785322</v>
+        <v>6785344</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13394,50 +13384,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127425909</v>
+        <v>127427379</v>
       </c>
       <c r="B123" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>464566</v>
+        <v>464643</v>
       </c>
       <c r="R123" t="n">
-        <v>6785301</v>
+        <v>6785243</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13506,45 +13491,50 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127421841</v>
+        <v>127423326</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464456</v>
+        <v>464480</v>
       </c>
       <c r="R124" t="n">
-        <v>6785336</v>
+        <v>6785322</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13613,45 +13603,50 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127423422</v>
+        <v>127425909</v>
       </c>
       <c r="B125" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>464465</v>
+        <v>464566</v>
       </c>
       <c r="R125" t="n">
-        <v>6785344</v>
+        <v>6785301</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13683,7 +13678,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13693,7 +13688,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13720,10 +13715,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127427379</v>
+        <v>127426763</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>58031</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13731,34 +13726,39 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464643</v>
+        <v>464578</v>
       </c>
       <c r="R126" t="n">
-        <v>6785243</v>
+        <v>6785262</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14367,10 +14367,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127423454</v>
+        <v>127423972</v>
       </c>
       <c r="B132" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14378,21 +14378,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14402,10 +14402,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464472</v>
+        <v>464506</v>
       </c>
       <c r="R132" t="n">
-        <v>6785351</v>
+        <v>6785318</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14474,32 +14474,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127423972</v>
+        <v>127422589</v>
       </c>
       <c r="B133" t="n">
-        <v>79636</v>
+        <v>8450</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14509,10 +14509,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464506</v>
+        <v>464502</v>
       </c>
       <c r="R133" t="n">
-        <v>6785318</v>
+        <v>6785289</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14581,10 +14581,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127421996</v>
+        <v>127423454</v>
       </c>
       <c r="B134" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14592,39 +14592,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464445</v>
+        <v>464472</v>
       </c>
       <c r="R134" t="n">
-        <v>6785311</v>
+        <v>6785351</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14693,7 +14688,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127422151</v>
+        <v>127421996</v>
       </c>
       <c r="B135" t="n">
         <v>57658</v>
@@ -14724,7 +14719,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -14733,10 +14728,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464471</v>
+        <v>464445</v>
       </c>
       <c r="R135" t="n">
-        <v>6785300</v>
+        <v>6785311</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14805,45 +14800,50 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127422589</v>
+        <v>127422151</v>
       </c>
       <c r="B136" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>464502</v>
+        <v>464471</v>
       </c>
       <c r="R136" t="n">
-        <v>6785289</v>
+        <v>6785300</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14912,10 +14912,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127423216</v>
+        <v>127422954</v>
       </c>
       <c r="B137" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14923,21 +14923,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14947,10 +14947,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464502</v>
+        <v>464492</v>
       </c>
       <c r="R137" t="n">
-        <v>6785318</v>
+        <v>6785316</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15019,7 +15019,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127422954</v>
+        <v>127423983</v>
       </c>
       <c r="B138" t="n">
         <v>79018</v>
@@ -15054,10 +15054,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>464492</v>
+        <v>464506</v>
       </c>
       <c r="R138" t="n">
-        <v>6785316</v>
+        <v>6785318</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15126,10 +15126,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127423983</v>
+        <v>127423216</v>
       </c>
       <c r="B139" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15137,21 +15137,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15161,7 +15161,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464506</v>
+        <v>464502</v>
       </c>
       <c r="R139" t="n">
         <v>6785318</v>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -11244,7 +11244,7 @@
         <v>127156818</v>
       </c>
       <c r="B103" t="n">
-        <v>91784</v>
+        <v>91786</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>127020226</v>
       </c>
       <c r="B104" t="n">
-        <v>91791</v>
+        <v>91793</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11448,10 +11448,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127422249</v>
+        <v>127422560</v>
       </c>
       <c r="B105" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11483,10 +11483,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464471</v>
+        <v>464493</v>
       </c>
       <c r="R105" t="n">
-        <v>6785300</v>
+        <v>6785289</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11555,10 +11555,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127422560</v>
+        <v>127422249</v>
       </c>
       <c r="B106" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11590,10 +11590,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464493</v>
+        <v>464471</v>
       </c>
       <c r="R106" t="n">
-        <v>6785289</v>
+        <v>6785300</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11665,7 +11665,7 @@
         <v>127423519</v>
       </c>
       <c r="B107" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>127423611</v>
       </c>
       <c r="B108" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11876,50 +11876,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127427354</v>
+        <v>127423331</v>
       </c>
       <c r="B109" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>464643</v>
+        <v>464480</v>
       </c>
       <c r="R109" t="n">
-        <v>6785243</v>
+        <v>6785322</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11951,7 +11946,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11961,7 +11956,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11988,7 +11983,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127423331</v>
+        <v>127422104</v>
       </c>
       <c r="B110" t="n">
         <v>8450</v>
@@ -12023,10 +12018,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>464480</v>
+        <v>464454</v>
       </c>
       <c r="R110" t="n">
-        <v>6785322</v>
+        <v>6785288</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12095,45 +12090,50 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127422104</v>
+        <v>127427354</v>
       </c>
       <c r="B111" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464454</v>
+        <v>464643</v>
       </c>
       <c r="R111" t="n">
-        <v>6785288</v>
+        <v>6785243</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12165,7 +12165,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12202,10 +12202,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127421835</v>
+        <v>127421683</v>
       </c>
       <c r="B112" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12213,21 +12213,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12237,10 +12237,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464456</v>
+        <v>464444</v>
       </c>
       <c r="R112" t="n">
-        <v>6785336</v>
+        <v>6785295</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12312,7 +12312,7 @@
         <v>127421762</v>
       </c>
       <c r="B113" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>127423850</v>
       </c>
       <c r="B114" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12523,10 +12523,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127421683</v>
+        <v>127421835</v>
       </c>
       <c r="B115" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12534,21 +12534,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12558,10 +12558,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464444</v>
+        <v>464456</v>
       </c>
       <c r="R115" t="n">
-        <v>6785295</v>
+        <v>6785336</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12633,7 +12633,7 @@
         <v>127425834</v>
       </c>
       <c r="B116" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12737,10 +12737,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127424788</v>
+        <v>127423223</v>
       </c>
       <c r="B117" t="n">
-        <v>57658</v>
+        <v>79609</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12748,39 +12748,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464526</v>
+        <v>464502</v>
       </c>
       <c r="R117" t="n">
-        <v>6785298</v>
+        <v>6785318</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12849,45 +12844,50 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127422036</v>
+        <v>127424788</v>
       </c>
       <c r="B118" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464445</v>
+        <v>464526</v>
       </c>
       <c r="R118" t="n">
-        <v>6785311</v>
+        <v>6785298</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12956,7 +12956,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127422304</v>
+        <v>127422036</v>
       </c>
       <c r="B119" t="n">
         <v>8450</v>
@@ -12991,10 +12991,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464471</v>
+        <v>464445</v>
       </c>
       <c r="R119" t="n">
-        <v>6785300</v>
+        <v>6785311</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13063,32 +13063,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127423223</v>
+        <v>127422304</v>
       </c>
       <c r="B120" t="n">
-        <v>79607</v>
+        <v>8450</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13098,10 +13098,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464502</v>
+        <v>464471</v>
       </c>
       <c r="R120" t="n">
-        <v>6785318</v>
+        <v>6785300</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13170,10 +13170,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127421841</v>
+        <v>127426763</v>
       </c>
       <c r="B121" t="n">
-        <v>8450</v>
+        <v>58033</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13181,34 +13181,39 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464456</v>
+        <v>464578</v>
       </c>
       <c r="R121" t="n">
-        <v>6785336</v>
+        <v>6785262</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13240,7 +13245,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13250,7 +13255,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13277,7 +13282,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127423422</v>
+        <v>127421841</v>
       </c>
       <c r="B122" t="n">
         <v>8450</v>
@@ -13312,10 +13317,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464465</v>
+        <v>464456</v>
       </c>
       <c r="R122" t="n">
-        <v>6785344</v>
+        <v>6785336</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13384,7 +13389,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127427379</v>
+        <v>127423422</v>
       </c>
       <c r="B123" t="n">
         <v>8450</v>
@@ -13419,10 +13424,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>464643</v>
+        <v>464465</v>
       </c>
       <c r="R123" t="n">
-        <v>6785243</v>
+        <v>6785344</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13454,7 +13459,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13464,7 +13469,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13491,50 +13496,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127423326</v>
+        <v>127427379</v>
       </c>
       <c r="B124" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464480</v>
+        <v>464643</v>
       </c>
       <c r="R124" t="n">
-        <v>6785322</v>
+        <v>6785243</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13606,7 +13606,7 @@
         <v>127425909</v>
       </c>
       <c r="B125" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13715,27 +13715,27 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127426763</v>
+        <v>127423326</v>
       </c>
       <c r="B126" t="n">
-        <v>58031</v>
+        <v>57660</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -13746,7 +13746,7 @@
       <c r="I126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -13755,10 +13755,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464578</v>
+        <v>464480</v>
       </c>
       <c r="R126" t="n">
-        <v>6785262</v>
+        <v>6785322</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13830,7 +13830,7 @@
         <v>127423221</v>
       </c>
       <c r="B127" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>127423538</v>
       </c>
       <c r="B128" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127421737</v>
+        <v>127423379</v>
       </c>
       <c r="B129" t="n">
         <v>8450</v>
@@ -14081,10 +14081,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>464429</v>
+        <v>464477</v>
       </c>
       <c r="R129" t="n">
-        <v>6785317</v>
+        <v>6785333</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14153,7 +14153,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127423379</v>
+        <v>127421737</v>
       </c>
       <c r="B130" t="n">
         <v>8450</v>
@@ -14188,10 +14188,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>464477</v>
+        <v>464429</v>
       </c>
       <c r="R130" t="n">
-        <v>6785333</v>
+        <v>6785317</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14263,7 +14263,7 @@
         <v>127422760</v>
       </c>
       <c r="B131" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14367,32 +14367,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127423972</v>
+        <v>127422589</v>
       </c>
       <c r="B132" t="n">
-        <v>79636</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14402,10 +14402,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464506</v>
+        <v>464502</v>
       </c>
       <c r="R132" t="n">
-        <v>6785318</v>
+        <v>6785289</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14474,32 +14474,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127422589</v>
+        <v>127423972</v>
       </c>
       <c r="B133" t="n">
-        <v>8450</v>
+        <v>79638</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14509,10 +14509,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464502</v>
+        <v>464506</v>
       </c>
       <c r="R133" t="n">
-        <v>6785289</v>
+        <v>6785318</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14584,7 +14584,7 @@
         <v>127423454</v>
       </c>
       <c r="B134" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14688,10 +14688,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127421996</v>
+        <v>127422151</v>
       </c>
       <c r="B135" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -14728,10 +14728,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464445</v>
+        <v>464471</v>
       </c>
       <c r="R135" t="n">
-        <v>6785311</v>
+        <v>6785300</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14800,10 +14800,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127422151</v>
+        <v>127421996</v>
       </c>
       <c r="B136" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
       <c r="I136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -14840,10 +14840,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>464471</v>
+        <v>464445</v>
       </c>
       <c r="R136" t="n">
-        <v>6785300</v>
+        <v>6785311</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14912,10 +14912,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127422954</v>
+        <v>127423216</v>
       </c>
       <c r="B137" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14923,21 +14923,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14947,10 +14947,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464492</v>
+        <v>464502</v>
       </c>
       <c r="R137" t="n">
-        <v>6785316</v>
+        <v>6785318</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15022,7 +15022,7 @@
         <v>127423983</v>
       </c>
       <c r="B138" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15126,10 +15126,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127423216</v>
+        <v>127422954</v>
       </c>
       <c r="B139" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15137,21 +15137,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15161,10 +15161,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464502</v>
+        <v>464492</v>
       </c>
       <c r="R139" t="n">
-        <v>6785318</v>
+        <v>6785316</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15233,32 +15233,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127425011</v>
+        <v>127424838</v>
       </c>
       <c r="B140" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15268,10 +15268,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464526</v>
+        <v>464537</v>
       </c>
       <c r="R140" t="n">
-        <v>6785325</v>
+        <v>6785309</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15340,32 +15340,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127425810</v>
+        <v>127423228</v>
       </c>
       <c r="B141" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>464558</v>
+        <v>464502</v>
       </c>
       <c r="R141" t="n">
-        <v>6785308</v>
+        <v>6785318</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15450,7 +15450,7 @@
         <v>127424901</v>
       </c>
       <c r="B142" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15554,32 +15554,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127424838</v>
+        <v>127425810</v>
       </c>
       <c r="B143" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15589,10 +15589,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>464537</v>
+        <v>464558</v>
       </c>
       <c r="R143" t="n">
-        <v>6785309</v>
+        <v>6785308</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15661,32 +15661,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127423228</v>
+        <v>127425011</v>
       </c>
       <c r="B144" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464502</v>
+        <v>464526</v>
       </c>
       <c r="R144" t="n">
-        <v>6785318</v>
+        <v>6785325</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15878,7 +15878,7 @@
         <v>127424833</v>
       </c>
       <c r="B146" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>127423429</v>
       </c>
       <c r="B147" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>127423346</v>
       </c>
       <c r="B148" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16196,10 +16196,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127421885</v>
+        <v>127422085</v>
       </c>
       <c r="B149" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16231,10 +16231,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464445</v>
+        <v>464454</v>
       </c>
       <c r="R149" t="n">
-        <v>6785311</v>
+        <v>6785288</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16303,10 +16303,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127422085</v>
+        <v>127421885</v>
       </c>
       <c r="B150" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16338,10 +16338,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>464454</v>
+        <v>464445</v>
       </c>
       <c r="R150" t="n">
-        <v>6785288</v>
+        <v>6785311</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16413,7 +16413,7 @@
         <v>127422583</v>
       </c>
       <c r="B151" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>127421603</v>
       </c>
       <c r="B152" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>127465306</v>
       </c>
       <c r="B153" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>127465699</v>
       </c>
       <c r="B154" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>127465669</v>
       </c>
       <c r="B155" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>127465578</v>
       </c>
       <c r="B156" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>127465540</v>
       </c>
       <c r="B157" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>127465918</v>
       </c>
       <c r="B158" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>127675974</v>
       </c>
       <c r="B159" t="n">
-        <v>91784</v>
+        <v>91786</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>127470562</v>
       </c>
       <c r="B160" t="n">
-        <v>91784</v>
+        <v>91786</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -11448,7 +11448,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127422560</v>
+        <v>127422249</v>
       </c>
       <c r="B105" t="n">
         <v>79020</v>
@@ -11483,10 +11483,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464493</v>
+        <v>464471</v>
       </c>
       <c r="R105" t="n">
-        <v>6785289</v>
+        <v>6785300</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11555,7 +11555,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127422249</v>
+        <v>127422560</v>
       </c>
       <c r="B106" t="n">
         <v>79020</v>
@@ -11590,10 +11590,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464471</v>
+        <v>464493</v>
       </c>
       <c r="R106" t="n">
-        <v>6785300</v>
+        <v>6785289</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11662,10 +11662,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127423519</v>
+        <v>127427354</v>
       </c>
       <c r="B107" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11673,34 +11673,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464487</v>
+        <v>464643</v>
       </c>
       <c r="R107" t="n">
-        <v>6785354</v>
+        <v>6785243</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11732,7 +11737,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11742,7 +11747,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11769,32 +11774,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127423611</v>
+        <v>127423331</v>
       </c>
       <c r="B108" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11804,10 +11809,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464488</v>
+        <v>464480</v>
       </c>
       <c r="R108" t="n">
-        <v>6785340</v>
+        <v>6785322</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11876,7 +11881,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127423331</v>
+        <v>127422104</v>
       </c>
       <c r="B109" t="n">
         <v>8450</v>
@@ -11911,10 +11916,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>464480</v>
+        <v>464454</v>
       </c>
       <c r="R109" t="n">
-        <v>6785322</v>
+        <v>6785288</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11983,32 +11988,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127422104</v>
+        <v>127423519</v>
       </c>
       <c r="B110" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12018,10 +12023,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>464454</v>
+        <v>464487</v>
       </c>
       <c r="R110" t="n">
-        <v>6785288</v>
+        <v>6785354</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12090,10 +12095,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127427354</v>
+        <v>127423611</v>
       </c>
       <c r="B111" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12101,39 +12106,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464643</v>
+        <v>464488</v>
       </c>
       <c r="R111" t="n">
-        <v>6785243</v>
+        <v>6785340</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12165,7 +12165,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12202,10 +12202,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127421683</v>
+        <v>127421835</v>
       </c>
       <c r="B112" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12213,21 +12213,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12237,10 +12237,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464444</v>
+        <v>464456</v>
       </c>
       <c r="R112" t="n">
-        <v>6785295</v>
+        <v>6785336</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12523,10 +12523,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127421835</v>
+        <v>127421683</v>
       </c>
       <c r="B115" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12534,21 +12534,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12558,10 +12558,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464456</v>
+        <v>464444</v>
       </c>
       <c r="R115" t="n">
-        <v>6785336</v>
+        <v>6785295</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12737,10 +12737,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127423223</v>
+        <v>127424788</v>
       </c>
       <c r="B117" t="n">
-        <v>79609</v>
+        <v>57660</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12748,34 +12748,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464502</v>
+        <v>464526</v>
       </c>
       <c r="R117" t="n">
-        <v>6785318</v>
+        <v>6785298</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12844,10 +12849,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127424788</v>
+        <v>127423223</v>
       </c>
       <c r="B118" t="n">
-        <v>57660</v>
+        <v>79609</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12855,39 +12860,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464526</v>
+        <v>464502</v>
       </c>
       <c r="R118" t="n">
-        <v>6785298</v>
+        <v>6785318</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13170,27 +13170,27 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127426763</v>
+        <v>127423326</v>
       </c>
       <c r="B121" t="n">
-        <v>58033</v>
+        <v>57660</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -13201,7 +13201,7 @@
       <c r="I121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13210,10 +13210,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464578</v>
+        <v>464480</v>
       </c>
       <c r="R121" t="n">
-        <v>6785262</v>
+        <v>6785322</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13245,7 +13245,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13255,7 +13255,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13282,45 +13282,50 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127421841</v>
+        <v>127425909</v>
       </c>
       <c r="B122" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464456</v>
+        <v>464566</v>
       </c>
       <c r="R122" t="n">
-        <v>6785336</v>
+        <v>6785301</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13352,7 +13357,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13362,7 +13367,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13389,10 +13394,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127423422</v>
+        <v>127426763</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>58033</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13400,34 +13405,39 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>464465</v>
+        <v>464578</v>
       </c>
       <c r="R123" t="n">
-        <v>6785344</v>
+        <v>6785262</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13459,7 +13469,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13469,7 +13479,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13496,7 +13506,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127427379</v>
+        <v>127421841</v>
       </c>
       <c r="B124" t="n">
         <v>8450</v>
@@ -13531,10 +13541,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464643</v>
+        <v>464456</v>
       </c>
       <c r="R124" t="n">
-        <v>6785243</v>
+        <v>6785336</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13566,7 +13576,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13576,7 +13586,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13603,50 +13613,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127425909</v>
+        <v>127423422</v>
       </c>
       <c r="B125" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>464566</v>
+        <v>464465</v>
       </c>
       <c r="R125" t="n">
-        <v>6785301</v>
+        <v>6785344</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13678,7 +13683,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13688,7 +13693,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13715,50 +13720,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127423326</v>
+        <v>127427379</v>
       </c>
       <c r="B126" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464480</v>
+        <v>464643</v>
       </c>
       <c r="R126" t="n">
-        <v>6785322</v>
+        <v>6785243</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14046,7 +14046,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127423379</v>
+        <v>127421737</v>
       </c>
       <c r="B129" t="n">
         <v>8450</v>
@@ -14081,10 +14081,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>464477</v>
+        <v>464429</v>
       </c>
       <c r="R129" t="n">
-        <v>6785333</v>
+        <v>6785317</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14153,7 +14153,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127421737</v>
+        <v>127423379</v>
       </c>
       <c r="B130" t="n">
         <v>8450</v>
@@ -14188,10 +14188,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>464429</v>
+        <v>464477</v>
       </c>
       <c r="R130" t="n">
-        <v>6785317</v>
+        <v>6785333</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14367,32 +14367,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127422589</v>
+        <v>127423454</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14402,10 +14402,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464502</v>
+        <v>464472</v>
       </c>
       <c r="R132" t="n">
-        <v>6785289</v>
+        <v>6785351</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14474,10 +14474,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127423972</v>
+        <v>127421996</v>
       </c>
       <c r="B133" t="n">
-        <v>79638</v>
+        <v>57660</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14485,34 +14485,39 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464506</v>
+        <v>464445</v>
       </c>
       <c r="R133" t="n">
-        <v>6785318</v>
+        <v>6785311</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14581,10 +14586,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127423454</v>
+        <v>127422151</v>
       </c>
       <c r="B134" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14592,34 +14597,39 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464472</v>
+        <v>464471</v>
       </c>
       <c r="R134" t="n">
-        <v>6785351</v>
+        <v>6785300</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14688,10 +14698,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127422151</v>
+        <v>127423972</v>
       </c>
       <c r="B135" t="n">
-        <v>57660</v>
+        <v>79638</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14699,39 +14709,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464471</v>
+        <v>464506</v>
       </c>
       <c r="R135" t="n">
-        <v>6785300</v>
+        <v>6785318</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14800,50 +14805,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127421996</v>
+        <v>127422589</v>
       </c>
       <c r="B136" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>464445</v>
+        <v>464502</v>
       </c>
       <c r="R136" t="n">
-        <v>6785311</v>
+        <v>6785289</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14912,10 +14912,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127423216</v>
+        <v>127422954</v>
       </c>
       <c r="B137" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14923,21 +14923,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14947,10 +14947,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464502</v>
+        <v>464492</v>
       </c>
       <c r="R137" t="n">
-        <v>6785318</v>
+        <v>6785316</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15126,10 +15126,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127422954</v>
+        <v>127423216</v>
       </c>
       <c r="B139" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15137,21 +15137,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15161,10 +15161,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464492</v>
+        <v>464502</v>
       </c>
       <c r="R139" t="n">
-        <v>6785316</v>
+        <v>6785318</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15233,32 +15233,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127424838</v>
+        <v>127425011</v>
       </c>
       <c r="B140" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15268,10 +15268,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464537</v>
+        <v>464526</v>
       </c>
       <c r="R140" t="n">
-        <v>6785309</v>
+        <v>6785325</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15340,32 +15340,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127423228</v>
+        <v>127425810</v>
       </c>
       <c r="B141" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>464502</v>
+        <v>464558</v>
       </c>
       <c r="R141" t="n">
-        <v>6785318</v>
+        <v>6785308</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15554,32 +15554,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127425810</v>
+        <v>127424838</v>
       </c>
       <c r="B143" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15589,10 +15589,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>464558</v>
+        <v>464537</v>
       </c>
       <c r="R143" t="n">
-        <v>6785308</v>
+        <v>6785309</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15661,32 +15661,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127425011</v>
+        <v>127423228</v>
       </c>
       <c r="B144" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464526</v>
+        <v>464502</v>
       </c>
       <c r="R144" t="n">
-        <v>6785325</v>
+        <v>6785318</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16196,10 +16196,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127422085</v>
+        <v>127422583</v>
       </c>
       <c r="B149" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16207,34 +16207,39 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464454</v>
+        <v>464502</v>
       </c>
       <c r="R149" t="n">
-        <v>6785288</v>
+        <v>6785289</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16410,10 +16415,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127422583</v>
+        <v>127422085</v>
       </c>
       <c r="B151" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16421,39 +16426,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>464502</v>
+        <v>464454</v>
       </c>
       <c r="R151" t="n">
-        <v>6785289</v>
+        <v>6785288</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -11662,10 +11662,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127427354</v>
+        <v>127423519</v>
       </c>
       <c r="B107" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11673,39 +11673,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464643</v>
+        <v>464487</v>
       </c>
       <c r="R107" t="n">
-        <v>6785243</v>
+        <v>6785354</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11737,7 +11732,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11747,7 +11742,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11774,32 +11769,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127423331</v>
+        <v>127423611</v>
       </c>
       <c r="B108" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11809,10 +11804,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464480</v>
+        <v>464488</v>
       </c>
       <c r="R108" t="n">
-        <v>6785322</v>
+        <v>6785340</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11881,45 +11876,50 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127422104</v>
+        <v>127427354</v>
       </c>
       <c r="B109" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>464454</v>
+        <v>464643</v>
       </c>
       <c r="R109" t="n">
-        <v>6785288</v>
+        <v>6785243</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11988,32 +11988,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127423519</v>
+        <v>127423331</v>
       </c>
       <c r="B110" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12023,10 +12023,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>464487</v>
+        <v>464480</v>
       </c>
       <c r="R110" t="n">
-        <v>6785354</v>
+        <v>6785322</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12095,32 +12095,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127423611</v>
+        <v>127422104</v>
       </c>
       <c r="B111" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12130,10 +12130,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464488</v>
+        <v>464454</v>
       </c>
       <c r="R111" t="n">
-        <v>6785340</v>
+        <v>6785288</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12737,50 +12737,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127424788</v>
+        <v>127422036</v>
       </c>
       <c r="B117" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464526</v>
+        <v>464445</v>
       </c>
       <c r="R117" t="n">
-        <v>6785298</v>
+        <v>6785311</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12849,32 +12844,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127423223</v>
+        <v>127422304</v>
       </c>
       <c r="B118" t="n">
-        <v>79609</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12884,10 +12879,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464502</v>
+        <v>464471</v>
       </c>
       <c r="R118" t="n">
-        <v>6785318</v>
+        <v>6785300</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12956,45 +12951,50 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127422036</v>
+        <v>127424788</v>
       </c>
       <c r="B119" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464445</v>
+        <v>464526</v>
       </c>
       <c r="R119" t="n">
-        <v>6785311</v>
+        <v>6785298</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13063,32 +13063,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127422304</v>
+        <v>127423223</v>
       </c>
       <c r="B120" t="n">
-        <v>8450</v>
+        <v>79609</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13098,10 +13098,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464471</v>
+        <v>464502</v>
       </c>
       <c r="R120" t="n">
-        <v>6785300</v>
+        <v>6785318</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13170,50 +13170,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127423326</v>
+        <v>127421841</v>
       </c>
       <c r="B121" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464480</v>
+        <v>464456</v>
       </c>
       <c r="R121" t="n">
-        <v>6785322</v>
+        <v>6785336</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13282,50 +13277,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127425909</v>
+        <v>127423422</v>
       </c>
       <c r="B122" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464566</v>
+        <v>464465</v>
       </c>
       <c r="R122" t="n">
-        <v>6785301</v>
+        <v>6785344</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13357,7 +13347,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13367,7 +13357,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13394,10 +13384,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127426763</v>
+        <v>127427379</v>
       </c>
       <c r="B123" t="n">
-        <v>58033</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13405,39 +13395,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>464578</v>
+        <v>464643</v>
       </c>
       <c r="R123" t="n">
-        <v>6785262</v>
+        <v>6785243</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13506,45 +13491,50 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127421841</v>
+        <v>127423326</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464456</v>
+        <v>464480</v>
       </c>
       <c r="R124" t="n">
-        <v>6785336</v>
+        <v>6785322</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13613,45 +13603,50 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127423422</v>
+        <v>127425909</v>
       </c>
       <c r="B125" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>464465</v>
+        <v>464566</v>
       </c>
       <c r="R125" t="n">
-        <v>6785344</v>
+        <v>6785301</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13683,7 +13678,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13693,7 +13688,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13720,10 +13715,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127427379</v>
+        <v>127426763</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>58033</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13731,34 +13726,39 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464643</v>
+        <v>464578</v>
       </c>
       <c r="R126" t="n">
-        <v>6785243</v>
+        <v>6785262</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14912,10 +14912,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127422954</v>
+        <v>127423216</v>
       </c>
       <c r="B137" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14923,21 +14923,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14947,10 +14947,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464492</v>
+        <v>464502</v>
       </c>
       <c r="R137" t="n">
-        <v>6785316</v>
+        <v>6785318</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15019,7 +15019,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127423983</v>
+        <v>127422954</v>
       </c>
       <c r="B138" t="n">
         <v>79020</v>
@@ -15054,10 +15054,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>464506</v>
+        <v>464492</v>
       </c>
       <c r="R138" t="n">
-        <v>6785318</v>
+        <v>6785316</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15126,10 +15126,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127423216</v>
+        <v>127423983</v>
       </c>
       <c r="B139" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15137,21 +15137,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15161,7 +15161,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464502</v>
+        <v>464506</v>
       </c>
       <c r="R139" t="n">
         <v>6785318</v>
@@ -16196,10 +16196,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127422583</v>
+        <v>127421885</v>
       </c>
       <c r="B149" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16207,39 +16207,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464502</v>
+        <v>464445</v>
       </c>
       <c r="R149" t="n">
-        <v>6785289</v>
+        <v>6785311</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16308,7 +16303,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127421885</v>
+        <v>127422085</v>
       </c>
       <c r="B150" t="n">
         <v>79020</v>
@@ -16343,10 +16338,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>464445</v>
+        <v>464454</v>
       </c>
       <c r="R150" t="n">
-        <v>6785311</v>
+        <v>6785288</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16415,10 +16410,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127422085</v>
+        <v>127422583</v>
       </c>
       <c r="B151" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16426,34 +16421,39 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>464454</v>
+        <v>464502</v>
       </c>
       <c r="R151" t="n">
-        <v>6785288</v>
+        <v>6785289</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -11448,7 +11448,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127422249</v>
+        <v>127422560</v>
       </c>
       <c r="B105" t="n">
         <v>79020</v>
@@ -11483,10 +11483,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464471</v>
+        <v>464493</v>
       </c>
       <c r="R105" t="n">
-        <v>6785300</v>
+        <v>6785289</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11555,7 +11555,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127422560</v>
+        <v>127422249</v>
       </c>
       <c r="B106" t="n">
         <v>79020</v>
@@ -11590,10 +11590,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464493</v>
+        <v>464471</v>
       </c>
       <c r="R106" t="n">
-        <v>6785289</v>
+        <v>6785300</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12737,45 +12737,50 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127422036</v>
+        <v>127424788</v>
       </c>
       <c r="B117" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464445</v>
+        <v>464526</v>
       </c>
       <c r="R117" t="n">
-        <v>6785311</v>
+        <v>6785298</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12844,7 +12849,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127422304</v>
+        <v>127422036</v>
       </c>
       <c r="B118" t="n">
         <v>8450</v>
@@ -12879,10 +12884,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464471</v>
+        <v>464445</v>
       </c>
       <c r="R118" t="n">
-        <v>6785300</v>
+        <v>6785311</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12951,50 +12956,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127424788</v>
+        <v>127422304</v>
       </c>
       <c r="B119" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464526</v>
+        <v>464471</v>
       </c>
       <c r="R119" t="n">
-        <v>6785298</v>
+        <v>6785300</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13170,45 +13170,50 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127421841</v>
+        <v>127423326</v>
       </c>
       <c r="B121" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464456</v>
+        <v>464480</v>
       </c>
       <c r="R121" t="n">
-        <v>6785336</v>
+        <v>6785322</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13277,45 +13282,50 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127423422</v>
+        <v>127425909</v>
       </c>
       <c r="B122" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464465</v>
+        <v>464566</v>
       </c>
       <c r="R122" t="n">
-        <v>6785344</v>
+        <v>6785301</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13347,7 +13357,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13357,7 +13367,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13384,10 +13394,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127427379</v>
+        <v>127426763</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>58033</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13395,34 +13405,39 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>464643</v>
+        <v>464578</v>
       </c>
       <c r="R123" t="n">
-        <v>6785243</v>
+        <v>6785262</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13491,50 +13506,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127423326</v>
+        <v>127421841</v>
       </c>
       <c r="B124" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464480</v>
+        <v>464456</v>
       </c>
       <c r="R124" t="n">
-        <v>6785322</v>
+        <v>6785336</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13603,50 +13613,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127425909</v>
+        <v>127423422</v>
       </c>
       <c r="B125" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>464566</v>
+        <v>464465</v>
       </c>
       <c r="R125" t="n">
-        <v>6785301</v>
+        <v>6785344</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13678,7 +13683,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13688,7 +13693,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13715,10 +13720,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127426763</v>
+        <v>127427379</v>
       </c>
       <c r="B126" t="n">
-        <v>58033</v>
+        <v>8450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13726,39 +13731,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464578</v>
+        <v>464643</v>
       </c>
       <c r="R126" t="n">
-        <v>6785262</v>
+        <v>6785243</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14367,10 +14367,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127423454</v>
+        <v>127421996</v>
       </c>
       <c r="B132" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14378,34 +14378,39 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464472</v>
+        <v>464445</v>
       </c>
       <c r="R132" t="n">
-        <v>6785351</v>
+        <v>6785311</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14474,7 +14479,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127421996</v>
+        <v>127422151</v>
       </c>
       <c r="B133" t="n">
         <v>57660</v>
@@ -14505,7 +14510,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -14514,10 +14519,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464445</v>
+        <v>464471</v>
       </c>
       <c r="R133" t="n">
-        <v>6785311</v>
+        <v>6785300</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14586,10 +14591,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127422151</v>
+        <v>127423454</v>
       </c>
       <c r="B134" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14597,39 +14602,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464471</v>
+        <v>464472</v>
       </c>
       <c r="R134" t="n">
-        <v>6785300</v>
+        <v>6785351</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15340,7 +15340,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127425810</v>
+        <v>127424901</v>
       </c>
       <c r="B141" t="n">
         <v>79020</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>464558</v>
+        <v>464544</v>
       </c>
       <c r="R141" t="n">
-        <v>6785308</v>
+        <v>6785309</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15447,32 +15447,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127424901</v>
+        <v>127424838</v>
       </c>
       <c r="B142" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15482,7 +15482,7 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464544</v>
+        <v>464537</v>
       </c>
       <c r="R142" t="n">
         <v>6785309</v>
@@ -15554,7 +15554,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127424838</v>
+        <v>127423228</v>
       </c>
       <c r="B143" t="n">
         <v>8450</v>
@@ -15589,10 +15589,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>464537</v>
+        <v>464502</v>
       </c>
       <c r="R143" t="n">
-        <v>6785309</v>
+        <v>6785318</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15661,32 +15661,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127423228</v>
+        <v>127425810</v>
       </c>
       <c r="B144" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464502</v>
+        <v>464558</v>
       </c>
       <c r="R144" t="n">
-        <v>6785318</v>
+        <v>6785308</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD144" t="b">

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -11244,7 +11244,7 @@
         <v>127156818</v>
       </c>
       <c r="B103" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>127020226</v>
       </c>
       <c r="B104" t="n">
-        <v>91793</v>
+        <v>91799</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127422560</v>
+        <v>127422249</v>
       </c>
       <c r="B105" t="n">
         <v>79020</v>
@@ -11483,10 +11483,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464493</v>
+        <v>464471</v>
       </c>
       <c r="R105" t="n">
-        <v>6785289</v>
+        <v>6785300</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11555,7 +11555,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127422249</v>
+        <v>127422560</v>
       </c>
       <c r="B106" t="n">
         <v>79020</v>
@@ -11590,10 +11590,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464471</v>
+        <v>464493</v>
       </c>
       <c r="R106" t="n">
-        <v>6785300</v>
+        <v>6785289</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11662,32 +11662,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127423519</v>
+        <v>127423331</v>
       </c>
       <c r="B107" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464487</v>
+        <v>464480</v>
       </c>
       <c r="R107" t="n">
-        <v>6785354</v>
+        <v>6785322</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11769,32 +11769,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127423611</v>
+        <v>127422104</v>
       </c>
       <c r="B108" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11804,10 +11804,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464488</v>
+        <v>464454</v>
       </c>
       <c r="R108" t="n">
-        <v>6785340</v>
+        <v>6785288</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11988,32 +11988,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127423331</v>
+        <v>127423519</v>
       </c>
       <c r="B110" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12023,10 +12023,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>464480</v>
+        <v>464487</v>
       </c>
       <c r="R110" t="n">
-        <v>6785322</v>
+        <v>6785354</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12095,32 +12095,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127422104</v>
+        <v>127423611</v>
       </c>
       <c r="B111" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12130,10 +12130,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464454</v>
+        <v>464488</v>
       </c>
       <c r="R111" t="n">
-        <v>6785288</v>
+        <v>6785340</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12309,10 +12309,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127421762</v>
+        <v>127421683</v>
       </c>
       <c r="B113" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12320,21 +12320,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12344,10 +12344,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464429</v>
+        <v>464444</v>
       </c>
       <c r="R113" t="n">
-        <v>6785317</v>
+        <v>6785295</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12416,7 +12416,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127423850</v>
+        <v>127421762</v>
       </c>
       <c r="B114" t="n">
         <v>79020</v>
@@ -12451,10 +12451,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464502</v>
+        <v>464429</v>
       </c>
       <c r="R114" t="n">
-        <v>6785318</v>
+        <v>6785317</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12523,10 +12523,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127421683</v>
+        <v>127423850</v>
       </c>
       <c r="B115" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12534,21 +12534,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12558,10 +12558,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464444</v>
+        <v>464502</v>
       </c>
       <c r="R115" t="n">
-        <v>6785295</v>
+        <v>6785318</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12849,32 +12849,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127422036</v>
+        <v>127423223</v>
       </c>
       <c r="B118" t="n">
-        <v>8450</v>
+        <v>79609</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12884,10 +12884,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464445</v>
+        <v>464502</v>
       </c>
       <c r="R118" t="n">
-        <v>6785311</v>
+        <v>6785318</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12956,7 +12956,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127422304</v>
+        <v>127422036</v>
       </c>
       <c r="B119" t="n">
         <v>8450</v>
@@ -12991,10 +12991,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464471</v>
+        <v>464445</v>
       </c>
       <c r="R119" t="n">
-        <v>6785300</v>
+        <v>6785311</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13063,32 +13063,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127423223</v>
+        <v>127422304</v>
       </c>
       <c r="B120" t="n">
-        <v>79609</v>
+        <v>8450</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13098,10 +13098,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464502</v>
+        <v>464471</v>
       </c>
       <c r="R120" t="n">
-        <v>6785318</v>
+        <v>6785300</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13170,50 +13170,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127423326</v>
+        <v>127421841</v>
       </c>
       <c r="B121" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464480</v>
+        <v>464456</v>
       </c>
       <c r="R121" t="n">
-        <v>6785322</v>
+        <v>6785336</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13282,50 +13277,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127425909</v>
+        <v>127423422</v>
       </c>
       <c r="B122" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464566</v>
+        <v>464465</v>
       </c>
       <c r="R122" t="n">
-        <v>6785301</v>
+        <v>6785344</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13357,7 +13347,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13367,7 +13357,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13394,10 +13384,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127426763</v>
+        <v>127427379</v>
       </c>
       <c r="B123" t="n">
-        <v>58033</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13405,39 +13395,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>464578</v>
+        <v>464643</v>
       </c>
       <c r="R123" t="n">
-        <v>6785262</v>
+        <v>6785243</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13506,45 +13491,50 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127421841</v>
+        <v>127423326</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464456</v>
+        <v>464480</v>
       </c>
       <c r="R124" t="n">
-        <v>6785336</v>
+        <v>6785322</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13613,45 +13603,50 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127423422</v>
+        <v>127425909</v>
       </c>
       <c r="B125" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>464465</v>
+        <v>464566</v>
       </c>
       <c r="R125" t="n">
-        <v>6785344</v>
+        <v>6785301</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13683,7 +13678,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13693,7 +13688,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13720,10 +13715,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127427379</v>
+        <v>127426763</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>58033</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13731,34 +13726,39 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464643</v>
+        <v>464578</v>
       </c>
       <c r="R126" t="n">
-        <v>6785243</v>
+        <v>6785262</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14367,10 +14367,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127421996</v>
+        <v>127423972</v>
       </c>
       <c r="B132" t="n">
-        <v>57660</v>
+        <v>79638</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14378,39 +14378,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464445</v>
+        <v>464506</v>
       </c>
       <c r="R132" t="n">
-        <v>6785311</v>
+        <v>6785318</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14479,50 +14474,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127422151</v>
+        <v>127422589</v>
       </c>
       <c r="B133" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464471</v>
+        <v>464502</v>
       </c>
       <c r="R133" t="n">
-        <v>6785300</v>
+        <v>6785289</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14591,10 +14581,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127423454</v>
+        <v>127422151</v>
       </c>
       <c r="B134" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14602,34 +14592,39 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464472</v>
+        <v>464471</v>
       </c>
       <c r="R134" t="n">
-        <v>6785351</v>
+        <v>6785300</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14698,10 +14693,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127423972</v>
+        <v>127421996</v>
       </c>
       <c r="B135" t="n">
-        <v>79638</v>
+        <v>57660</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14709,34 +14704,39 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464506</v>
+        <v>464445</v>
       </c>
       <c r="R135" t="n">
-        <v>6785318</v>
+        <v>6785311</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14805,32 +14805,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127422589</v>
+        <v>127423454</v>
       </c>
       <c r="B136" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14840,10 +14840,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>464502</v>
+        <v>464472</v>
       </c>
       <c r="R136" t="n">
-        <v>6785289</v>
+        <v>6785351</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14912,10 +14912,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127423216</v>
+        <v>127422954</v>
       </c>
       <c r="B137" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14923,21 +14923,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14947,10 +14947,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464502</v>
+        <v>464492</v>
       </c>
       <c r="R137" t="n">
-        <v>6785318</v>
+        <v>6785316</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15019,7 +15019,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127422954</v>
+        <v>127423983</v>
       </c>
       <c r="B138" t="n">
         <v>79020</v>
@@ -15054,10 +15054,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>464492</v>
+        <v>464506</v>
       </c>
       <c r="R138" t="n">
-        <v>6785316</v>
+        <v>6785318</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15126,10 +15126,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127423983</v>
+        <v>127423216</v>
       </c>
       <c r="B139" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15137,21 +15137,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15161,7 +15161,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464506</v>
+        <v>464502</v>
       </c>
       <c r="R139" t="n">
         <v>6785318</v>
@@ -15233,7 +15233,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127425011</v>
+        <v>127425810</v>
       </c>
       <c r="B140" t="n">
         <v>79020</v>
@@ -15268,10 +15268,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464526</v>
+        <v>464558</v>
       </c>
       <c r="R140" t="n">
-        <v>6785325</v>
+        <v>6785308</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15313,7 +15313,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15447,32 +15447,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127424838</v>
+        <v>127425011</v>
       </c>
       <c r="B142" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15482,10 +15482,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464537</v>
+        <v>464526</v>
       </c>
       <c r="R142" t="n">
-        <v>6785309</v>
+        <v>6785325</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15554,7 +15554,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127423228</v>
+        <v>127424838</v>
       </c>
       <c r="B143" t="n">
         <v>8450</v>
@@ -15589,10 +15589,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>464502</v>
+        <v>464537</v>
       </c>
       <c r="R143" t="n">
-        <v>6785318</v>
+        <v>6785309</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15661,32 +15661,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127425810</v>
+        <v>127423228</v>
       </c>
       <c r="B144" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464558</v>
+        <v>464502</v>
       </c>
       <c r="R144" t="n">
-        <v>6785308</v>
+        <v>6785318</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16196,10 +16196,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127421885</v>
+        <v>127422583</v>
       </c>
       <c r="B149" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16207,34 +16207,39 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464445</v>
+        <v>464502</v>
       </c>
       <c r="R149" t="n">
-        <v>6785311</v>
+        <v>6785289</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16410,10 +16415,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127422583</v>
+        <v>127421885</v>
       </c>
       <c r="B151" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16421,39 +16426,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>464502</v>
+        <v>464445</v>
       </c>
       <c r="R151" t="n">
-        <v>6785289</v>
+        <v>6785311</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17246,7 +17246,7 @@
         <v>127675974</v>
       </c>
       <c r="B159" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>127470562</v>
       </c>
       <c r="B160" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -11244,7 +11244,7 @@
         <v>127156818</v>
       </c>
       <c r="B103" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>127020226</v>
       </c>
       <c r="B104" t="n">
-        <v>91799</v>
+        <v>91802</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>127422249</v>
       </c>
       <c r="B105" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>127422560</v>
       </c>
       <c r="B106" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11662,32 +11662,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127423331</v>
+        <v>127423519</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464480</v>
+        <v>464487</v>
       </c>
       <c r="R107" t="n">
-        <v>6785322</v>
+        <v>6785354</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11769,32 +11769,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127422104</v>
+        <v>127423611</v>
       </c>
       <c r="B108" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11804,10 +11804,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464454</v>
+        <v>464488</v>
       </c>
       <c r="R108" t="n">
-        <v>6785288</v>
+        <v>6785340</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11879,7 +11879,7 @@
         <v>127427354</v>
       </c>
       <c r="B109" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11988,32 +11988,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127423519</v>
+        <v>127423331</v>
       </c>
       <c r="B110" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12023,10 +12023,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>464487</v>
+        <v>464480</v>
       </c>
       <c r="R110" t="n">
-        <v>6785354</v>
+        <v>6785322</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12095,32 +12095,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127423611</v>
+        <v>127422104</v>
       </c>
       <c r="B111" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12130,10 +12130,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464488</v>
+        <v>464454</v>
       </c>
       <c r="R111" t="n">
-        <v>6785340</v>
+        <v>6785288</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12202,10 +12202,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127421835</v>
+        <v>127421683</v>
       </c>
       <c r="B112" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12213,21 +12213,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12237,10 +12237,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464456</v>
+        <v>464444</v>
       </c>
       <c r="R112" t="n">
-        <v>6785336</v>
+        <v>6785295</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12309,10 +12309,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127421683</v>
+        <v>127421835</v>
       </c>
       <c r="B113" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12320,21 +12320,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12344,10 +12344,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464444</v>
+        <v>464456</v>
       </c>
       <c r="R113" t="n">
-        <v>6785295</v>
+        <v>6785336</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12419,7 +12419,7 @@
         <v>127421762</v>
       </c>
       <c r="B114" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>127423850</v>
       </c>
       <c r="B115" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>127425834</v>
       </c>
       <c r="B116" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12737,50 +12737,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127424788</v>
+        <v>127422036</v>
       </c>
       <c r="B117" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464526</v>
+        <v>464445</v>
       </c>
       <c r="R117" t="n">
-        <v>6785298</v>
+        <v>6785311</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12849,32 +12844,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127423223</v>
+        <v>127422304</v>
       </c>
       <c r="B118" t="n">
-        <v>79609</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12884,10 +12879,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464502</v>
+        <v>464471</v>
       </c>
       <c r="R118" t="n">
-        <v>6785318</v>
+        <v>6785300</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12956,32 +12951,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127422036</v>
+        <v>127423223</v>
       </c>
       <c r="B119" t="n">
-        <v>8450</v>
+        <v>79612</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12991,10 +12986,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464445</v>
+        <v>464502</v>
       </c>
       <c r="R119" t="n">
-        <v>6785311</v>
+        <v>6785318</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13063,45 +13058,50 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127422304</v>
+        <v>127424788</v>
       </c>
       <c r="B120" t="n">
-        <v>8450</v>
+        <v>57663</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464471</v>
+        <v>464526</v>
       </c>
       <c r="R120" t="n">
-        <v>6785300</v>
+        <v>6785298</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13170,45 +13170,50 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127421841</v>
+        <v>127423326</v>
       </c>
       <c r="B121" t="n">
-        <v>8450</v>
+        <v>57663</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464456</v>
+        <v>464480</v>
       </c>
       <c r="R121" t="n">
-        <v>6785336</v>
+        <v>6785322</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13277,45 +13282,50 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127423422</v>
+        <v>127425909</v>
       </c>
       <c r="B122" t="n">
-        <v>8450</v>
+        <v>57663</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464465</v>
+        <v>464566</v>
       </c>
       <c r="R122" t="n">
-        <v>6785344</v>
+        <v>6785301</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13347,7 +13357,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13357,7 +13367,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13384,10 +13394,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127427379</v>
+        <v>127426763</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>58036</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13395,34 +13405,39 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>464643</v>
+        <v>464578</v>
       </c>
       <c r="R123" t="n">
-        <v>6785243</v>
+        <v>6785262</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13491,50 +13506,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127423326</v>
+        <v>127421841</v>
       </c>
       <c r="B124" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464480</v>
+        <v>464456</v>
       </c>
       <c r="R124" t="n">
-        <v>6785322</v>
+        <v>6785336</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13603,50 +13613,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127425909</v>
+        <v>127423422</v>
       </c>
       <c r="B125" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>464566</v>
+        <v>464465</v>
       </c>
       <c r="R125" t="n">
-        <v>6785301</v>
+        <v>6785344</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13678,7 +13683,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13688,7 +13693,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13715,10 +13720,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127426763</v>
+        <v>127427379</v>
       </c>
       <c r="B126" t="n">
-        <v>58033</v>
+        <v>8450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13726,39 +13731,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464578</v>
+        <v>464643</v>
       </c>
       <c r="R126" t="n">
-        <v>6785262</v>
+        <v>6785243</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13830,7 +13830,7 @@
         <v>127423221</v>
       </c>
       <c r="B127" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13934,50 +13934,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127423538</v>
+        <v>127423379</v>
       </c>
       <c r="B128" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>464487</v>
+        <v>464477</v>
       </c>
       <c r="R128" t="n">
-        <v>6785354</v>
+        <v>6785333</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14046,45 +14041,50 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127421737</v>
+        <v>127423538</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>57663</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>464429</v>
+        <v>464487</v>
       </c>
       <c r="R129" t="n">
-        <v>6785317</v>
+        <v>6785354</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14153,7 +14153,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127423379</v>
+        <v>127421737</v>
       </c>
       <c r="B130" t="n">
         <v>8450</v>
@@ -14188,10 +14188,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>464477</v>
+        <v>464429</v>
       </c>
       <c r="R130" t="n">
-        <v>6785333</v>
+        <v>6785317</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14263,7 +14263,7 @@
         <v>127422760</v>
       </c>
       <c r="B131" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14367,32 +14367,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127423972</v>
+        <v>127422589</v>
       </c>
       <c r="B132" t="n">
-        <v>79638</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14402,10 +14402,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464506</v>
+        <v>464502</v>
       </c>
       <c r="R132" t="n">
-        <v>6785318</v>
+        <v>6785289</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14474,32 +14474,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127422589</v>
+        <v>127423972</v>
       </c>
       <c r="B133" t="n">
-        <v>8450</v>
+        <v>79641</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14509,10 +14509,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464502</v>
+        <v>464506</v>
       </c>
       <c r="R133" t="n">
-        <v>6785289</v>
+        <v>6785318</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14581,10 +14581,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127422151</v>
+        <v>127423454</v>
       </c>
       <c r="B134" t="n">
-        <v>57660</v>
+        <v>79023</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14592,39 +14592,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464471</v>
+        <v>464472</v>
       </c>
       <c r="R134" t="n">
-        <v>6785300</v>
+        <v>6785351</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14696,7 +14691,7 @@
         <v>127421996</v>
       </c>
       <c r="B135" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14805,10 +14800,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127423454</v>
+        <v>127422151</v>
       </c>
       <c r="B136" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14816,34 +14811,39 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>464472</v>
+        <v>464471</v>
       </c>
       <c r="R136" t="n">
-        <v>6785351</v>
+        <v>6785300</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14912,10 +14912,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127422954</v>
+        <v>127423983</v>
       </c>
       <c r="B137" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14947,10 +14947,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464492</v>
+        <v>464506</v>
       </c>
       <c r="R137" t="n">
-        <v>6785316</v>
+        <v>6785318</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15019,10 +15019,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127423983</v>
+        <v>127422954</v>
       </c>
       <c r="B138" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15054,10 +15054,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>464506</v>
+        <v>464492</v>
       </c>
       <c r="R138" t="n">
-        <v>6785318</v>
+        <v>6785316</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15129,7 +15129,7 @@
         <v>127423216</v>
       </c>
       <c r="B139" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15233,32 +15233,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127425810</v>
+        <v>127424838</v>
       </c>
       <c r="B140" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15268,10 +15268,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464558</v>
+        <v>464537</v>
       </c>
       <c r="R140" t="n">
-        <v>6785308</v>
+        <v>6785309</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15313,7 +15313,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15340,32 +15340,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127424901</v>
+        <v>127423228</v>
       </c>
       <c r="B141" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>464544</v>
+        <v>464502</v>
       </c>
       <c r="R141" t="n">
-        <v>6785309</v>
+        <v>6785318</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15450,7 +15450,7 @@
         <v>127425011</v>
       </c>
       <c r="B142" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15554,32 +15554,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127424838</v>
+        <v>127425810</v>
       </c>
       <c r="B143" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15589,10 +15589,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>464537</v>
+        <v>464558</v>
       </c>
       <c r="R143" t="n">
-        <v>6785309</v>
+        <v>6785308</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15661,32 +15661,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127423228</v>
+        <v>127424901</v>
       </c>
       <c r="B144" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464502</v>
+        <v>464544</v>
       </c>
       <c r="R144" t="n">
-        <v>6785318</v>
+        <v>6785309</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15878,7 +15878,7 @@
         <v>127424833</v>
       </c>
       <c r="B146" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>127423429</v>
       </c>
       <c r="B147" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>127423346</v>
       </c>
       <c r="B148" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>127422583</v>
       </c>
       <c r="B149" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16308,10 +16308,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127422085</v>
+        <v>127421885</v>
       </c>
       <c r="B150" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16343,10 +16343,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>464454</v>
+        <v>464445</v>
       </c>
       <c r="R150" t="n">
-        <v>6785288</v>
+        <v>6785311</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16415,10 +16415,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127421885</v>
+        <v>127422085</v>
       </c>
       <c r="B151" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16450,10 +16450,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>464445</v>
+        <v>464454</v>
       </c>
       <c r="R151" t="n">
-        <v>6785311</v>
+        <v>6785288</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16525,7 +16525,7 @@
         <v>127421603</v>
       </c>
       <c r="B152" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>127465306</v>
       </c>
       <c r="B153" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>127465699</v>
       </c>
       <c r="B154" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>127465669</v>
       </c>
       <c r="B155" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>127465578</v>
       </c>
       <c r="B156" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>127465540</v>
       </c>
       <c r="B157" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>127465918</v>
       </c>
       <c r="B158" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>127675974</v>
       </c>
       <c r="B159" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>127470562</v>
       </c>
       <c r="B160" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -11244,7 +11244,7 @@
         <v>127156818</v>
       </c>
       <c r="B103" t="n">
-        <v>91795</v>
+        <v>91803</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>127020226</v>
       </c>
       <c r="B104" t="n">
-        <v>91802</v>
+        <v>91810</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11448,10 +11448,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127422249</v>
+        <v>127422560</v>
       </c>
       <c r="B105" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11483,10 +11483,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464471</v>
+        <v>464493</v>
       </c>
       <c r="R105" t="n">
-        <v>6785300</v>
+        <v>6785289</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11555,10 +11555,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127422560</v>
+        <v>127422249</v>
       </c>
       <c r="B106" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11590,10 +11590,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464493</v>
+        <v>464471</v>
       </c>
       <c r="R106" t="n">
-        <v>6785289</v>
+        <v>6785300</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11665,7 +11665,7 @@
         <v>127423519</v>
       </c>
       <c r="B107" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>127423611</v>
       </c>
       <c r="B108" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>127427354</v>
       </c>
       <c r="B109" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12202,10 +12202,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127421683</v>
+        <v>127421762</v>
       </c>
       <c r="B112" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12213,21 +12213,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12237,10 +12237,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464444</v>
+        <v>464429</v>
       </c>
       <c r="R112" t="n">
-        <v>6785295</v>
+        <v>6785317</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12309,10 +12309,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127421835</v>
+        <v>127421683</v>
       </c>
       <c r="B113" t="n">
-        <v>79023</v>
+        <v>79647</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12320,21 +12320,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12344,10 +12344,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464456</v>
+        <v>464444</v>
       </c>
       <c r="R113" t="n">
-        <v>6785336</v>
+        <v>6785295</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12416,10 +12416,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127421762</v>
+        <v>127423850</v>
       </c>
       <c r="B114" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12451,10 +12451,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464429</v>
+        <v>464502</v>
       </c>
       <c r="R114" t="n">
-        <v>6785317</v>
+        <v>6785318</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12523,10 +12523,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127423850</v>
+        <v>127421835</v>
       </c>
       <c r="B115" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12558,10 +12558,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464502</v>
+        <v>464456</v>
       </c>
       <c r="R115" t="n">
-        <v>6785318</v>
+        <v>6785336</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12633,7 +12633,7 @@
         <v>127425834</v>
       </c>
       <c r="B116" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12737,32 +12737,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127422036</v>
+        <v>127423223</v>
       </c>
       <c r="B117" t="n">
-        <v>8450</v>
+        <v>79618</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12772,10 +12772,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464445</v>
+        <v>464502</v>
       </c>
       <c r="R117" t="n">
-        <v>6785311</v>
+        <v>6785318</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12844,45 +12844,50 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127422304</v>
+        <v>127424788</v>
       </c>
       <c r="B118" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464471</v>
+        <v>464526</v>
       </c>
       <c r="R118" t="n">
-        <v>6785300</v>
+        <v>6785298</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12951,32 +12956,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127423223</v>
+        <v>127422036</v>
       </c>
       <c r="B119" t="n">
-        <v>79612</v>
+        <v>8450</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12986,10 +12991,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464502</v>
+        <v>464445</v>
       </c>
       <c r="R119" t="n">
-        <v>6785318</v>
+        <v>6785311</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13058,50 +13063,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127424788</v>
+        <v>127422304</v>
       </c>
       <c r="B120" t="n">
-        <v>57663</v>
+        <v>8450</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464526</v>
+        <v>464471</v>
       </c>
       <c r="R120" t="n">
-        <v>6785298</v>
+        <v>6785300</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13173,7 +13173,7 @@
         <v>127423326</v>
       </c>
       <c r="B121" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>127425909</v>
       </c>
       <c r="B122" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>127426763</v>
       </c>
       <c r="B123" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>127423221</v>
       </c>
       <c r="B127" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13934,45 +13934,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127423379</v>
+        <v>127423538</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>464477</v>
+        <v>464487</v>
       </c>
       <c r="R128" t="n">
-        <v>6785333</v>
+        <v>6785354</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14041,50 +14046,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127423538</v>
+        <v>127421737</v>
       </c>
       <c r="B129" t="n">
-        <v>57663</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>464487</v>
+        <v>464429</v>
       </c>
       <c r="R129" t="n">
-        <v>6785354</v>
+        <v>6785317</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14153,7 +14153,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127421737</v>
+        <v>127423379</v>
       </c>
       <c r="B130" t="n">
         <v>8450</v>
@@ -14188,10 +14188,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>464429</v>
+        <v>464477</v>
       </c>
       <c r="R130" t="n">
-        <v>6785317</v>
+        <v>6785333</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14263,7 +14263,7 @@
         <v>127422760</v>
       </c>
       <c r="B131" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14367,32 +14367,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127422589</v>
+        <v>127423972</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>79647</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14402,10 +14402,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464502</v>
+        <v>464506</v>
       </c>
       <c r="R132" t="n">
-        <v>6785289</v>
+        <v>6785318</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14474,10 +14474,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127423972</v>
+        <v>127423454</v>
       </c>
       <c r="B133" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14485,21 +14485,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14509,10 +14509,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464506</v>
+        <v>464472</v>
       </c>
       <c r="R133" t="n">
-        <v>6785318</v>
+        <v>6785351</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14581,10 +14581,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127423454</v>
+        <v>127421996</v>
       </c>
       <c r="B134" t="n">
-        <v>79023</v>
+        <v>57669</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14592,34 +14592,39 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464472</v>
+        <v>464445</v>
       </c>
       <c r="R134" t="n">
-        <v>6785351</v>
+        <v>6785311</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14688,10 +14693,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127421996</v>
+        <v>127422151</v>
       </c>
       <c r="B135" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14719,7 +14724,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -14728,10 +14733,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464445</v>
+        <v>464471</v>
       </c>
       <c r="R135" t="n">
-        <v>6785311</v>
+        <v>6785300</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14800,50 +14805,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127422151</v>
+        <v>127422589</v>
       </c>
       <c r="B136" t="n">
-        <v>57663</v>
+        <v>8450</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>464471</v>
+        <v>464502</v>
       </c>
       <c r="R136" t="n">
-        <v>6785300</v>
+        <v>6785289</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14915,7 +14915,7 @@
         <v>127423983</v>
       </c>
       <c r="B137" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>127422954</v>
       </c>
       <c r="B138" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>127423216</v>
       </c>
       <c r="B139" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15233,32 +15233,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127424838</v>
+        <v>127425011</v>
       </c>
       <c r="B140" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15268,10 +15268,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464537</v>
+        <v>464526</v>
       </c>
       <c r="R140" t="n">
-        <v>6785309</v>
+        <v>6785325</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15340,32 +15340,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127423228</v>
+        <v>127425810</v>
       </c>
       <c r="B141" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>464502</v>
+        <v>464558</v>
       </c>
       <c r="R141" t="n">
-        <v>6785318</v>
+        <v>6785308</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15447,10 +15447,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127425011</v>
+        <v>127424901</v>
       </c>
       <c r="B142" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15482,10 +15482,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464526</v>
+        <v>464544</v>
       </c>
       <c r="R142" t="n">
-        <v>6785325</v>
+        <v>6785309</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15554,32 +15554,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127425810</v>
+        <v>127424838</v>
       </c>
       <c r="B143" t="n">
-        <v>79023</v>
+        <v>8450</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15589,10 +15589,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>464558</v>
+        <v>464537</v>
       </c>
       <c r="R143" t="n">
-        <v>6785308</v>
+        <v>6785309</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15661,32 +15661,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127424901</v>
+        <v>127423228</v>
       </c>
       <c r="B144" t="n">
-        <v>79023</v>
+        <v>8450</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464544</v>
+        <v>464502</v>
       </c>
       <c r="R144" t="n">
-        <v>6785309</v>
+        <v>6785318</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15878,7 +15878,7 @@
         <v>127424833</v>
       </c>
       <c r="B146" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>127423429</v>
       </c>
       <c r="B147" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>127423346</v>
       </c>
       <c r="B148" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16196,10 +16196,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127422583</v>
+        <v>127422085</v>
       </c>
       <c r="B149" t="n">
-        <v>57663</v>
+        <v>79029</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16207,39 +16207,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464502</v>
+        <v>464454</v>
       </c>
       <c r="R149" t="n">
-        <v>6785289</v>
+        <v>6785288</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16311,7 +16306,7 @@
         <v>127421885</v>
       </c>
       <c r="B150" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16415,10 +16410,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127422085</v>
+        <v>127422583</v>
       </c>
       <c r="B151" t="n">
-        <v>79023</v>
+        <v>57669</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16426,34 +16421,39 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>464454</v>
+        <v>464502</v>
       </c>
       <c r="R151" t="n">
-        <v>6785288</v>
+        <v>6785289</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16525,7 +16525,7 @@
         <v>127421603</v>
       </c>
       <c r="B152" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>127465306</v>
       </c>
       <c r="B153" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>127465699</v>
       </c>
       <c r="B154" t="n">
-        <v>75147</v>
+        <v>75153</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>127465669</v>
       </c>
       <c r="B155" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>127465578</v>
       </c>
       <c r="B156" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>127465540</v>
       </c>
       <c r="B157" t="n">
-        <v>75147</v>
+        <v>75153</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>127465918</v>
       </c>
       <c r="B158" t="n">
-        <v>75147</v>
+        <v>75153</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>127675974</v>
       </c>
       <c r="B159" t="n">
-        <v>91795</v>
+        <v>91803</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>127470562</v>
       </c>
       <c r="B160" t="n">
-        <v>91795</v>
+        <v>91803</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -11244,7 +11244,7 @@
         <v>127156818</v>
       </c>
       <c r="B103" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>127020226</v>
       </c>
       <c r="B104" t="n">
-        <v>91810</v>
+        <v>91811</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127422560</v>
+        <v>127422249</v>
       </c>
       <c r="B105" t="n">
         <v>79029</v>
@@ -11483,10 +11483,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464493</v>
+        <v>464471</v>
       </c>
       <c r="R105" t="n">
-        <v>6785289</v>
+        <v>6785300</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11555,7 +11555,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127422249</v>
+        <v>127422560</v>
       </c>
       <c r="B106" t="n">
         <v>79029</v>
@@ -11590,10 +11590,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464471</v>
+        <v>464493</v>
       </c>
       <c r="R106" t="n">
-        <v>6785300</v>
+        <v>6785289</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12202,7 +12202,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127421762</v>
+        <v>127421835</v>
       </c>
       <c r="B112" t="n">
         <v>79029</v>
@@ -12237,10 +12237,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464429</v>
+        <v>464456</v>
       </c>
       <c r="R112" t="n">
-        <v>6785317</v>
+        <v>6785336</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12309,10 +12309,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127421683</v>
+        <v>127421762</v>
       </c>
       <c r="B113" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12320,21 +12320,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12344,10 +12344,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464444</v>
+        <v>464429</v>
       </c>
       <c r="R113" t="n">
-        <v>6785295</v>
+        <v>6785317</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12416,10 +12416,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127423850</v>
+        <v>127421683</v>
       </c>
       <c r="B114" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12427,21 +12427,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12451,10 +12451,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464502</v>
+        <v>464444</v>
       </c>
       <c r="R114" t="n">
-        <v>6785318</v>
+        <v>6785295</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12523,7 +12523,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127421835</v>
+        <v>127423850</v>
       </c>
       <c r="B115" t="n">
         <v>79029</v>
@@ -12558,10 +12558,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464456</v>
+        <v>464502</v>
       </c>
       <c r="R115" t="n">
-        <v>6785336</v>
+        <v>6785318</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12737,10 +12737,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127423223</v>
+        <v>127424788</v>
       </c>
       <c r="B117" t="n">
-        <v>79618</v>
+        <v>57669</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12748,34 +12748,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464502</v>
+        <v>464526</v>
       </c>
       <c r="R117" t="n">
-        <v>6785318</v>
+        <v>6785298</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12844,50 +12849,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127424788</v>
+        <v>127422036</v>
       </c>
       <c r="B118" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464526</v>
+        <v>464445</v>
       </c>
       <c r="R118" t="n">
-        <v>6785298</v>
+        <v>6785311</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12956,7 +12956,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127422036</v>
+        <v>127422304</v>
       </c>
       <c r="B119" t="n">
         <v>8450</v>
@@ -12991,10 +12991,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464445</v>
+        <v>464471</v>
       </c>
       <c r="R119" t="n">
-        <v>6785311</v>
+        <v>6785300</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13063,32 +13063,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127422304</v>
+        <v>127423223</v>
       </c>
       <c r="B120" t="n">
-        <v>8450</v>
+        <v>79618</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13098,10 +13098,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464471</v>
+        <v>464502</v>
       </c>
       <c r="R120" t="n">
-        <v>6785300</v>
+        <v>6785318</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13170,50 +13170,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127423326</v>
+        <v>127421841</v>
       </c>
       <c r="B121" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464480</v>
+        <v>464456</v>
       </c>
       <c r="R121" t="n">
-        <v>6785322</v>
+        <v>6785336</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13282,50 +13277,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127425909</v>
+        <v>127423422</v>
       </c>
       <c r="B122" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464566</v>
+        <v>464465</v>
       </c>
       <c r="R122" t="n">
-        <v>6785301</v>
+        <v>6785344</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13357,7 +13347,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13367,7 +13357,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13394,10 +13384,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127426763</v>
+        <v>127427379</v>
       </c>
       <c r="B123" t="n">
-        <v>58042</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13405,39 +13395,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>464578</v>
+        <v>464643</v>
       </c>
       <c r="R123" t="n">
-        <v>6785262</v>
+        <v>6785243</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13506,45 +13491,50 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127421841</v>
+        <v>127423326</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464456</v>
+        <v>464480</v>
       </c>
       <c r="R124" t="n">
-        <v>6785336</v>
+        <v>6785322</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13613,45 +13603,50 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127423422</v>
+        <v>127425909</v>
       </c>
       <c r="B125" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>464465</v>
+        <v>464566</v>
       </c>
       <c r="R125" t="n">
-        <v>6785344</v>
+        <v>6785301</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13683,7 +13678,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13693,7 +13688,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13720,10 +13715,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127427379</v>
+        <v>127426763</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>58042</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13731,34 +13726,39 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464643</v>
+        <v>464578</v>
       </c>
       <c r="R126" t="n">
-        <v>6785243</v>
+        <v>6785262</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14367,10 +14367,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127423972</v>
+        <v>127422151</v>
       </c>
       <c r="B132" t="n">
-        <v>79647</v>
+        <v>57669</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14378,34 +14378,39 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464506</v>
+        <v>464471</v>
       </c>
       <c r="R132" t="n">
-        <v>6785318</v>
+        <v>6785300</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14474,10 +14479,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127423454</v>
+        <v>127421996</v>
       </c>
       <c r="B133" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14485,34 +14490,39 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464472</v>
+        <v>464445</v>
       </c>
       <c r="R133" t="n">
-        <v>6785351</v>
+        <v>6785311</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14581,10 +14591,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127421996</v>
+        <v>127423972</v>
       </c>
       <c r="B134" t="n">
-        <v>57669</v>
+        <v>79647</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14592,39 +14602,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464445</v>
+        <v>464506</v>
       </c>
       <c r="R134" t="n">
-        <v>6785311</v>
+        <v>6785318</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14693,10 +14698,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127422151</v>
+        <v>127423454</v>
       </c>
       <c r="B135" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14704,39 +14709,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464471</v>
+        <v>464472</v>
       </c>
       <c r="R135" t="n">
-        <v>6785300</v>
+        <v>6785351</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14912,7 +14912,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127423983</v>
+        <v>127422954</v>
       </c>
       <c r="B137" t="n">
         <v>79029</v>
@@ -14947,10 +14947,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464506</v>
+        <v>464492</v>
       </c>
       <c r="R137" t="n">
-        <v>6785318</v>
+        <v>6785316</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15019,7 +15019,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127422954</v>
+        <v>127423983</v>
       </c>
       <c r="B138" t="n">
         <v>79029</v>
@@ -15054,10 +15054,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>464492</v>
+        <v>464506</v>
       </c>
       <c r="R138" t="n">
-        <v>6785316</v>
+        <v>6785318</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16196,10 +16196,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127422085</v>
+        <v>127422583</v>
       </c>
       <c r="B149" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16207,34 +16207,39 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464454</v>
+        <v>464502</v>
       </c>
       <c r="R149" t="n">
-        <v>6785288</v>
+        <v>6785289</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16410,10 +16415,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127422583</v>
+        <v>127422085</v>
       </c>
       <c r="B151" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16421,39 +16426,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>464502</v>
+        <v>464454</v>
       </c>
       <c r="R151" t="n">
-        <v>6785289</v>
+        <v>6785288</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17246,7 +17246,7 @@
         <v>127675974</v>
       </c>
       <c r="B159" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>127470562</v>
       </c>
       <c r="B160" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -11448,7 +11448,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127422249</v>
+        <v>127422560</v>
       </c>
       <c r="B105" t="n">
         <v>79029</v>
@@ -11483,10 +11483,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464471</v>
+        <v>464493</v>
       </c>
       <c r="R105" t="n">
-        <v>6785300</v>
+        <v>6785289</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11555,7 +11555,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127422560</v>
+        <v>127422249</v>
       </c>
       <c r="B106" t="n">
         <v>79029</v>
@@ -11590,10 +11590,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464493</v>
+        <v>464471</v>
       </c>
       <c r="R106" t="n">
-        <v>6785289</v>
+        <v>6785300</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12202,10 +12202,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127421835</v>
+        <v>127421683</v>
       </c>
       <c r="B112" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12213,21 +12213,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12237,10 +12237,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464456</v>
+        <v>464444</v>
       </c>
       <c r="R112" t="n">
-        <v>6785336</v>
+        <v>6785295</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12416,10 +12416,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127421683</v>
+        <v>127423850</v>
       </c>
       <c r="B114" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12427,21 +12427,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12451,10 +12451,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464444</v>
+        <v>464502</v>
       </c>
       <c r="R114" t="n">
-        <v>6785295</v>
+        <v>6785318</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12523,7 +12523,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127423850</v>
+        <v>127421835</v>
       </c>
       <c r="B115" t="n">
         <v>79029</v>
@@ -12558,10 +12558,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464502</v>
+        <v>464456</v>
       </c>
       <c r="R115" t="n">
-        <v>6785318</v>
+        <v>6785336</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13170,45 +13170,50 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127421841</v>
+        <v>127423326</v>
       </c>
       <c r="B121" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464456</v>
+        <v>464480</v>
       </c>
       <c r="R121" t="n">
-        <v>6785336</v>
+        <v>6785322</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13277,45 +13282,50 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127423422</v>
+        <v>127425909</v>
       </c>
       <c r="B122" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464465</v>
+        <v>464566</v>
       </c>
       <c r="R122" t="n">
-        <v>6785344</v>
+        <v>6785301</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13347,7 +13357,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13357,7 +13367,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13384,10 +13394,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127427379</v>
+        <v>127426763</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>58042</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13395,34 +13405,39 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>464643</v>
+        <v>464578</v>
       </c>
       <c r="R123" t="n">
-        <v>6785243</v>
+        <v>6785262</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13491,50 +13506,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127423326</v>
+        <v>127423422</v>
       </c>
       <c r="B124" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464480</v>
+        <v>464465</v>
       </c>
       <c r="R124" t="n">
-        <v>6785322</v>
+        <v>6785344</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13603,50 +13613,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127425909</v>
+        <v>127421841</v>
       </c>
       <c r="B125" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>464566</v>
+        <v>464456</v>
       </c>
       <c r="R125" t="n">
-        <v>6785301</v>
+        <v>6785336</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13678,7 +13683,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13688,7 +13693,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13715,10 +13720,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127426763</v>
+        <v>127427379</v>
       </c>
       <c r="B126" t="n">
-        <v>58042</v>
+        <v>8450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13726,39 +13731,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464578</v>
+        <v>464643</v>
       </c>
       <c r="R126" t="n">
-        <v>6785262</v>
+        <v>6785243</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14046,7 +14046,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127421737</v>
+        <v>127423379</v>
       </c>
       <c r="B129" t="n">
         <v>8450</v>
@@ -14081,10 +14081,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>464429</v>
+        <v>464477</v>
       </c>
       <c r="R129" t="n">
-        <v>6785317</v>
+        <v>6785333</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14153,7 +14153,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127423379</v>
+        <v>127421737</v>
       </c>
       <c r="B130" t="n">
         <v>8450</v>
@@ -14188,10 +14188,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>464477</v>
+        <v>464429</v>
       </c>
       <c r="R130" t="n">
-        <v>6785333</v>
+        <v>6785317</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14367,10 +14367,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127422151</v>
+        <v>127423454</v>
       </c>
       <c r="B132" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14378,39 +14378,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464471</v>
+        <v>464472</v>
       </c>
       <c r="R132" t="n">
-        <v>6785300</v>
+        <v>6785351</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14479,10 +14474,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127421996</v>
+        <v>127423972</v>
       </c>
       <c r="B133" t="n">
-        <v>57669</v>
+        <v>79647</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14490,39 +14485,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464445</v>
+        <v>464506</v>
       </c>
       <c r="R133" t="n">
-        <v>6785311</v>
+        <v>6785318</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14591,10 +14581,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127423972</v>
+        <v>127422151</v>
       </c>
       <c r="B134" t="n">
-        <v>79647</v>
+        <v>57669</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14602,34 +14592,39 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464506</v>
+        <v>464471</v>
       </c>
       <c r="R134" t="n">
-        <v>6785318</v>
+        <v>6785300</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14698,10 +14693,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127423454</v>
+        <v>127421996</v>
       </c>
       <c r="B135" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14709,34 +14704,39 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464472</v>
+        <v>464445</v>
       </c>
       <c r="R135" t="n">
-        <v>6785351</v>
+        <v>6785311</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14912,7 +14912,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127422954</v>
+        <v>127423983</v>
       </c>
       <c r="B137" t="n">
         <v>79029</v>
@@ -14947,10 +14947,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464492</v>
+        <v>464506</v>
       </c>
       <c r="R137" t="n">
-        <v>6785316</v>
+        <v>6785318</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15019,7 +15019,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127423983</v>
+        <v>127422954</v>
       </c>
       <c r="B138" t="n">
         <v>79029</v>
@@ -15054,10 +15054,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>464506</v>
+        <v>464492</v>
       </c>
       <c r="R138" t="n">
-        <v>6785318</v>
+        <v>6785316</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15233,7 +15233,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127425011</v>
+        <v>127424901</v>
       </c>
       <c r="B140" t="n">
         <v>79029</v>
@@ -15268,10 +15268,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464526</v>
+        <v>464544</v>
       </c>
       <c r="R140" t="n">
-        <v>6785325</v>
+        <v>6785309</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15447,7 +15447,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127424901</v>
+        <v>127425011</v>
       </c>
       <c r="B142" t="n">
         <v>79029</v>
@@ -15482,10 +15482,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464544</v>
+        <v>464526</v>
       </c>
       <c r="R142" t="n">
-        <v>6785309</v>
+        <v>6785325</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16196,10 +16196,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127422583</v>
+        <v>127422085</v>
       </c>
       <c r="B149" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16207,39 +16207,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464502</v>
+        <v>464454</v>
       </c>
       <c r="R149" t="n">
-        <v>6785289</v>
+        <v>6785288</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16415,10 +16410,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127422085</v>
+        <v>127422583</v>
       </c>
       <c r="B151" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16426,34 +16421,39 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>464454</v>
+        <v>464502</v>
       </c>
       <c r="R151" t="n">
-        <v>6785288</v>
+        <v>6785289</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -11448,7 +11448,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127422560</v>
+        <v>127422249</v>
       </c>
       <c r="B105" t="n">
         <v>79029</v>
@@ -11483,10 +11483,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464493</v>
+        <v>464471</v>
       </c>
       <c r="R105" t="n">
-        <v>6785289</v>
+        <v>6785300</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11555,7 +11555,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127422249</v>
+        <v>127422560</v>
       </c>
       <c r="B106" t="n">
         <v>79029</v>
@@ -11590,10 +11590,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464471</v>
+        <v>464493</v>
       </c>
       <c r="R106" t="n">
-        <v>6785300</v>
+        <v>6785289</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12202,10 +12202,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127421683</v>
+        <v>127421835</v>
       </c>
       <c r="B112" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12213,21 +12213,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12237,10 +12237,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464444</v>
+        <v>464456</v>
       </c>
       <c r="R112" t="n">
-        <v>6785295</v>
+        <v>6785336</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12416,10 +12416,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127423850</v>
+        <v>127421683</v>
       </c>
       <c r="B114" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12427,21 +12427,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12451,10 +12451,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464502</v>
+        <v>464444</v>
       </c>
       <c r="R114" t="n">
-        <v>6785318</v>
+        <v>6785295</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12523,7 +12523,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127421835</v>
+        <v>127423850</v>
       </c>
       <c r="B115" t="n">
         <v>79029</v>
@@ -12558,10 +12558,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464456</v>
+        <v>464502</v>
       </c>
       <c r="R115" t="n">
-        <v>6785336</v>
+        <v>6785318</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13170,50 +13170,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127423326</v>
+        <v>127421841</v>
       </c>
       <c r="B121" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464480</v>
+        <v>464456</v>
       </c>
       <c r="R121" t="n">
-        <v>6785322</v>
+        <v>6785336</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13282,50 +13277,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127425909</v>
+        <v>127423422</v>
       </c>
       <c r="B122" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464566</v>
+        <v>464465</v>
       </c>
       <c r="R122" t="n">
-        <v>6785301</v>
+        <v>6785344</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13357,7 +13347,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13367,7 +13357,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13394,10 +13384,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127426763</v>
+        <v>127427379</v>
       </c>
       <c r="B123" t="n">
-        <v>58042</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13405,39 +13395,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>464578</v>
+        <v>464643</v>
       </c>
       <c r="R123" t="n">
-        <v>6785262</v>
+        <v>6785243</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13506,45 +13491,50 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127423422</v>
+        <v>127423326</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464465</v>
+        <v>464480</v>
       </c>
       <c r="R124" t="n">
-        <v>6785344</v>
+        <v>6785322</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13613,45 +13603,50 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127421841</v>
+        <v>127425909</v>
       </c>
       <c r="B125" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>464456</v>
+        <v>464566</v>
       </c>
       <c r="R125" t="n">
-        <v>6785336</v>
+        <v>6785301</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13683,7 +13678,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13693,7 +13688,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13720,10 +13715,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127427379</v>
+        <v>127426763</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>58042</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13731,34 +13726,39 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464643</v>
+        <v>464578</v>
       </c>
       <c r="R126" t="n">
-        <v>6785243</v>
+        <v>6785262</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13934,50 +13934,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127423538</v>
+        <v>127423379</v>
       </c>
       <c r="B128" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>464487</v>
+        <v>464477</v>
       </c>
       <c r="R128" t="n">
-        <v>6785354</v>
+        <v>6785333</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14046,45 +14041,50 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127423379</v>
+        <v>127423538</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>464477</v>
+        <v>464487</v>
       </c>
       <c r="R129" t="n">
-        <v>6785333</v>
+        <v>6785354</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14367,10 +14367,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127423454</v>
+        <v>127423972</v>
       </c>
       <c r="B132" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14378,21 +14378,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14402,10 +14402,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464472</v>
+        <v>464506</v>
       </c>
       <c r="R132" t="n">
-        <v>6785351</v>
+        <v>6785318</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14474,10 +14474,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127423972</v>
+        <v>127423454</v>
       </c>
       <c r="B133" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14485,21 +14485,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14509,10 +14509,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464506</v>
+        <v>464472</v>
       </c>
       <c r="R133" t="n">
-        <v>6785318</v>
+        <v>6785351</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14581,50 +14581,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127422151</v>
+        <v>127422589</v>
       </c>
       <c r="B134" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464471</v>
+        <v>464502</v>
       </c>
       <c r="R134" t="n">
-        <v>6785300</v>
+        <v>6785289</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14805,45 +14800,50 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127422589</v>
+        <v>127422151</v>
       </c>
       <c r="B136" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>464502</v>
+        <v>464471</v>
       </c>
       <c r="R136" t="n">
-        <v>6785289</v>
+        <v>6785300</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14912,10 +14912,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127423983</v>
+        <v>127423216</v>
       </c>
       <c r="B137" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14923,21 +14923,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14947,7 +14947,7 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464506</v>
+        <v>464502</v>
       </c>
       <c r="R137" t="n">
         <v>6785318</v>
@@ -15126,10 +15126,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127423216</v>
+        <v>127423983</v>
       </c>
       <c r="B139" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15137,21 +15137,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15161,7 +15161,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464502</v>
+        <v>464506</v>
       </c>
       <c r="R139" t="n">
         <v>6785318</v>
@@ -15233,7 +15233,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127424901</v>
+        <v>127425011</v>
       </c>
       <c r="B140" t="n">
         <v>79029</v>
@@ -15268,10 +15268,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464544</v>
+        <v>464526</v>
       </c>
       <c r="R140" t="n">
-        <v>6785309</v>
+        <v>6785325</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15447,7 +15447,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127425011</v>
+        <v>127424901</v>
       </c>
       <c r="B142" t="n">
         <v>79029</v>
@@ -15482,10 +15482,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464526</v>
+        <v>464544</v>
       </c>
       <c r="R142" t="n">
-        <v>6785325</v>
+        <v>6785309</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16196,10 +16196,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127422085</v>
+        <v>127422583</v>
       </c>
       <c r="B149" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16207,34 +16207,39 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464454</v>
+        <v>464502</v>
       </c>
       <c r="R149" t="n">
-        <v>6785288</v>
+        <v>6785289</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16410,10 +16415,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127422583</v>
+        <v>127422085</v>
       </c>
       <c r="B151" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16421,39 +16426,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>464502</v>
+        <v>464454</v>
       </c>
       <c r="R151" t="n">
-        <v>6785289</v>
+        <v>6785288</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17246,7 +17246,7 @@
         <v>127675974</v>
       </c>
       <c r="B159" t="n">
-        <v>91804</v>
+        <v>91805</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>127470562</v>
       </c>
       <c r="B160" t="n">
-        <v>91804</v>
+        <v>91805</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -11448,7 +11448,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127422249</v>
+        <v>127422560</v>
       </c>
       <c r="B105" t="n">
         <v>79029</v>
@@ -11483,10 +11483,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464471</v>
+        <v>464493</v>
       </c>
       <c r="R105" t="n">
-        <v>6785300</v>
+        <v>6785289</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11555,7 +11555,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127422560</v>
+        <v>127422249</v>
       </c>
       <c r="B106" t="n">
         <v>79029</v>
@@ -11590,10 +11590,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464493</v>
+        <v>464471</v>
       </c>
       <c r="R106" t="n">
-        <v>6785289</v>
+        <v>6785300</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12202,10 +12202,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127421835</v>
+        <v>127421683</v>
       </c>
       <c r="B112" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12213,21 +12213,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12237,10 +12237,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464456</v>
+        <v>464444</v>
       </c>
       <c r="R112" t="n">
-        <v>6785336</v>
+        <v>6785295</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12416,10 +12416,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127421683</v>
+        <v>127423850</v>
       </c>
       <c r="B114" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12427,21 +12427,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12451,10 +12451,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464444</v>
+        <v>464502</v>
       </c>
       <c r="R114" t="n">
-        <v>6785295</v>
+        <v>6785318</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12523,7 +12523,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127423850</v>
+        <v>127421835</v>
       </c>
       <c r="B115" t="n">
         <v>79029</v>
@@ -12558,10 +12558,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464502</v>
+        <v>464456</v>
       </c>
       <c r="R115" t="n">
-        <v>6785318</v>
+        <v>6785336</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13170,45 +13170,50 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127421841</v>
+        <v>127423326</v>
       </c>
       <c r="B121" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464456</v>
+        <v>464480</v>
       </c>
       <c r="R121" t="n">
-        <v>6785336</v>
+        <v>6785322</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13277,45 +13282,50 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127423422</v>
+        <v>127425909</v>
       </c>
       <c r="B122" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464465</v>
+        <v>464566</v>
       </c>
       <c r="R122" t="n">
-        <v>6785344</v>
+        <v>6785301</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13347,7 +13357,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13357,7 +13367,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13384,7 +13394,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127427379</v>
+        <v>127421841</v>
       </c>
       <c r="B123" t="n">
         <v>8450</v>
@@ -13419,10 +13429,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>464643</v>
+        <v>464456</v>
       </c>
       <c r="R123" t="n">
-        <v>6785243</v>
+        <v>6785336</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13454,7 +13464,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13464,7 +13474,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13491,50 +13501,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127423326</v>
+        <v>127423422</v>
       </c>
       <c r="B124" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464480</v>
+        <v>464465</v>
       </c>
       <c r="R124" t="n">
-        <v>6785322</v>
+        <v>6785344</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13603,50 +13608,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127425909</v>
+        <v>127427379</v>
       </c>
       <c r="B125" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>464566</v>
+        <v>464643</v>
       </c>
       <c r="R125" t="n">
-        <v>6785301</v>
+        <v>6785243</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13934,7 +13934,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127423379</v>
+        <v>127421737</v>
       </c>
       <c r="B128" t="n">
         <v>8450</v>
@@ -13969,10 +13969,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>464477</v>
+        <v>464429</v>
       </c>
       <c r="R128" t="n">
-        <v>6785333</v>
+        <v>6785317</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14041,50 +14041,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127423538</v>
+        <v>127423379</v>
       </c>
       <c r="B129" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>464487</v>
+        <v>464477</v>
       </c>
       <c r="R129" t="n">
-        <v>6785354</v>
+        <v>6785333</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14153,45 +14148,50 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127421737</v>
+        <v>127423538</v>
       </c>
       <c r="B130" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>464429</v>
+        <v>464487</v>
       </c>
       <c r="R130" t="n">
-        <v>6785317</v>
+        <v>6785354</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14367,10 +14367,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127423972</v>
+        <v>127421996</v>
       </c>
       <c r="B132" t="n">
-        <v>79647</v>
+        <v>57669</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14378,34 +14378,39 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464506</v>
+        <v>464445</v>
       </c>
       <c r="R132" t="n">
-        <v>6785318</v>
+        <v>6785311</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14474,10 +14479,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127423454</v>
+        <v>127422151</v>
       </c>
       <c r="B133" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14485,34 +14490,39 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464472</v>
+        <v>464471</v>
       </c>
       <c r="R133" t="n">
-        <v>6785351</v>
+        <v>6785300</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14688,10 +14698,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127421996</v>
+        <v>127423972</v>
       </c>
       <c r="B135" t="n">
-        <v>57669</v>
+        <v>79647</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14699,39 +14709,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464445</v>
+        <v>464506</v>
       </c>
       <c r="R135" t="n">
-        <v>6785311</v>
+        <v>6785318</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14800,10 +14805,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127422151</v>
+        <v>127423454</v>
       </c>
       <c r="B136" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14811,39 +14816,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>464471</v>
+        <v>464472</v>
       </c>
       <c r="R136" t="n">
-        <v>6785300</v>
+        <v>6785351</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14912,10 +14912,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127423216</v>
+        <v>127423983</v>
       </c>
       <c r="B137" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14923,21 +14923,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14947,7 +14947,7 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464502</v>
+        <v>464506</v>
       </c>
       <c r="R137" t="n">
         <v>6785318</v>
@@ -15126,10 +15126,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127423983</v>
+        <v>127423216</v>
       </c>
       <c r="B139" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15137,21 +15137,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15161,7 +15161,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464506</v>
+        <v>464502</v>
       </c>
       <c r="R139" t="n">
         <v>6785318</v>
@@ -15233,7 +15233,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127425011</v>
+        <v>127424901</v>
       </c>
       <c r="B140" t="n">
         <v>79029</v>
@@ -15268,10 +15268,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464526</v>
+        <v>464544</v>
       </c>
       <c r="R140" t="n">
-        <v>6785325</v>
+        <v>6785309</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15447,7 +15447,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127424901</v>
+        <v>127425011</v>
       </c>
       <c r="B142" t="n">
         <v>79029</v>
@@ -15482,10 +15482,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464544</v>
+        <v>464526</v>
       </c>
       <c r="R142" t="n">
-        <v>6785309</v>
+        <v>6785325</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16196,10 +16196,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127422583</v>
+        <v>127422085</v>
       </c>
       <c r="B149" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16207,39 +16207,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464502</v>
+        <v>464454</v>
       </c>
       <c r="R149" t="n">
-        <v>6785289</v>
+        <v>6785288</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16415,10 +16410,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127422085</v>
+        <v>127422583</v>
       </c>
       <c r="B151" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16426,34 +16421,39 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>464454</v>
+        <v>464502</v>
       </c>
       <c r="R151" t="n">
-        <v>6785288</v>
+        <v>6785289</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17246,7 +17246,7 @@
         <v>127675974</v>
       </c>
       <c r="B159" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>127470562</v>
       </c>
       <c r="B160" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -11448,7 +11448,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127422560</v>
+        <v>127422249</v>
       </c>
       <c r="B105" t="n">
         <v>79029</v>
@@ -11483,10 +11483,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464493</v>
+        <v>464471</v>
       </c>
       <c r="R105" t="n">
-        <v>6785289</v>
+        <v>6785300</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11555,7 +11555,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127422249</v>
+        <v>127422560</v>
       </c>
       <c r="B106" t="n">
         <v>79029</v>
@@ -11590,10 +11590,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464471</v>
+        <v>464493</v>
       </c>
       <c r="R106" t="n">
-        <v>6785300</v>
+        <v>6785289</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11662,7 +11662,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127423519</v>
+        <v>127423611</v>
       </c>
       <c r="B107" t="n">
         <v>79029</v>
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464487</v>
+        <v>464488</v>
       </c>
       <c r="R107" t="n">
-        <v>6785354</v>
+        <v>6785340</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11769,7 +11769,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127423611</v>
+        <v>127423519</v>
       </c>
       <c r="B108" t="n">
         <v>79029</v>
@@ -11804,10 +11804,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464488</v>
+        <v>464487</v>
       </c>
       <c r="R108" t="n">
-        <v>6785340</v>
+        <v>6785354</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12309,7 +12309,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127421762</v>
+        <v>127421789</v>
       </c>
       <c r="B113" t="n">
         <v>79029</v>
@@ -12416,7 +12416,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127423850</v>
+        <v>127421835</v>
       </c>
       <c r="B114" t="n">
         <v>79029</v>
@@ -12451,10 +12451,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464502</v>
+        <v>464456</v>
       </c>
       <c r="R114" t="n">
-        <v>6785318</v>
+        <v>6785336</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12523,7 +12523,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127421835</v>
+        <v>127423850</v>
       </c>
       <c r="B115" t="n">
         <v>79029</v>
@@ -12558,10 +12558,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464456</v>
+        <v>464502</v>
       </c>
       <c r="R115" t="n">
-        <v>6785336</v>
+        <v>6785318</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12737,50 +12737,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127424788</v>
+        <v>127422036</v>
       </c>
       <c r="B117" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464526</v>
+        <v>464445</v>
       </c>
       <c r="R117" t="n">
-        <v>6785298</v>
+        <v>6785311</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12849,7 +12844,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127422036</v>
+        <v>127422304</v>
       </c>
       <c r="B118" t="n">
         <v>8450</v>
@@ -12884,10 +12879,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464445</v>
+        <v>464471</v>
       </c>
       <c r="R118" t="n">
-        <v>6785311</v>
+        <v>6785300</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12956,45 +12951,50 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127422304</v>
+        <v>127424788</v>
       </c>
       <c r="B119" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464471</v>
+        <v>464526</v>
       </c>
       <c r="R119" t="n">
-        <v>6785300</v>
+        <v>6785298</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13170,50 +13170,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127423326</v>
+        <v>127427379</v>
       </c>
       <c r="B121" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464480</v>
+        <v>464643</v>
       </c>
       <c r="R121" t="n">
-        <v>6785322</v>
+        <v>6785243</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13245,7 +13240,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13255,7 +13250,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13282,7 +13277,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127425909</v>
+        <v>127423326</v>
       </c>
       <c r="B122" t="n">
         <v>57669</v>
@@ -13313,7 +13308,7 @@
       <c r="I122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -13322,10 +13317,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464566</v>
+        <v>464480</v>
       </c>
       <c r="R122" t="n">
-        <v>6785301</v>
+        <v>6785322</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13357,7 +13352,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13367,7 +13362,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13394,45 +13389,50 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127421841</v>
+        <v>127425909</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>464456</v>
+        <v>464566</v>
       </c>
       <c r="R123" t="n">
-        <v>6785336</v>
+        <v>6785301</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13464,7 +13464,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13501,10 +13501,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127423422</v>
+        <v>127426763</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>58042</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13512,34 +13512,39 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464465</v>
+        <v>464578</v>
       </c>
       <c r="R124" t="n">
-        <v>6785344</v>
+        <v>6785262</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13571,7 +13576,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13581,7 +13586,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13608,7 +13613,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127427379</v>
+        <v>127423422</v>
       </c>
       <c r="B125" t="n">
         <v>8450</v>
@@ -13643,10 +13648,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>464643</v>
+        <v>464465</v>
       </c>
       <c r="R125" t="n">
-        <v>6785243</v>
+        <v>6785344</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13678,7 +13683,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13688,7 +13693,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13715,10 +13720,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127426763</v>
+        <v>127421841</v>
       </c>
       <c r="B126" t="n">
-        <v>58042</v>
+        <v>8450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13726,39 +13731,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464578</v>
+        <v>464456</v>
       </c>
       <c r="R126" t="n">
-        <v>6785262</v>
+        <v>6785336</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13934,45 +13934,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127421737</v>
+        <v>127423538</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>464429</v>
+        <v>464487</v>
       </c>
       <c r="R128" t="n">
-        <v>6785317</v>
+        <v>6785354</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14148,50 +14153,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127423538</v>
+        <v>127421737</v>
       </c>
       <c r="B130" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>464487</v>
+        <v>464429</v>
       </c>
       <c r="R130" t="n">
-        <v>6785354</v>
+        <v>6785317</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14912,10 +14912,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127423983</v>
+        <v>127423216</v>
       </c>
       <c r="B137" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14923,21 +14923,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14947,7 +14947,7 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464506</v>
+        <v>464502</v>
       </c>
       <c r="R137" t="n">
         <v>6785318</v>
@@ -15126,10 +15126,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127423216</v>
+        <v>127423983</v>
       </c>
       <c r="B139" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15137,21 +15137,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15161,7 +15161,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464502</v>
+        <v>464506</v>
       </c>
       <c r="R139" t="n">
         <v>6785318</v>
@@ -15233,32 +15233,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127424901</v>
+        <v>127423228</v>
       </c>
       <c r="B140" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15268,10 +15268,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464544</v>
+        <v>464502</v>
       </c>
       <c r="R140" t="n">
-        <v>6785309</v>
+        <v>6785318</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15340,32 +15340,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127425810</v>
+        <v>127424838</v>
       </c>
       <c r="B141" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>464558</v>
+        <v>464537</v>
       </c>
       <c r="R141" t="n">
-        <v>6785308</v>
+        <v>6785309</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15554,32 +15554,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127424838</v>
+        <v>127425810</v>
       </c>
       <c r="B143" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15589,10 +15589,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>464537</v>
+        <v>464558</v>
       </c>
       <c r="R143" t="n">
-        <v>6785309</v>
+        <v>6785308</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15661,32 +15661,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127423228</v>
+        <v>127424901</v>
       </c>
       <c r="B144" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464502</v>
+        <v>464544</v>
       </c>
       <c r="R144" t="n">
-        <v>6785318</v>
+        <v>6785309</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16196,7 +16196,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127422085</v>
+        <v>127421885</v>
       </c>
       <c r="B149" t="n">
         <v>79029</v>
@@ -16231,10 +16231,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464454</v>
+        <v>464445</v>
       </c>
       <c r="R149" t="n">
-        <v>6785288</v>
+        <v>6785311</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16303,7 +16303,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127421885</v>
+        <v>127422085</v>
       </c>
       <c r="B150" t="n">
         <v>79029</v>
@@ -16338,10 +16338,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>464445</v>
+        <v>464454</v>
       </c>
       <c r="R150" t="n">
-        <v>6785311</v>
+        <v>6785288</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -12737,7 +12737,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127422036</v>
+        <v>127422304</v>
       </c>
       <c r="B117" t="n">
         <v>8450</v>
@@ -12772,10 +12772,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464445</v>
+        <v>464471</v>
       </c>
       <c r="R117" t="n">
-        <v>6785311</v>
+        <v>6785300</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12844,7 +12844,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127422304</v>
+        <v>127422036</v>
       </c>
       <c r="B118" t="n">
         <v>8450</v>
@@ -12879,10 +12879,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464471</v>
+        <v>464445</v>
       </c>
       <c r="R118" t="n">
-        <v>6785300</v>
+        <v>6785311</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12951,10 +12951,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127424788</v>
+        <v>127423223</v>
       </c>
       <c r="B119" t="n">
-        <v>57669</v>
+        <v>79618</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12962,39 +12962,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464526</v>
+        <v>464502</v>
       </c>
       <c r="R119" t="n">
-        <v>6785298</v>
+        <v>6785318</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13063,10 +13058,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127423223</v>
+        <v>127424788</v>
       </c>
       <c r="B120" t="n">
-        <v>79618</v>
+        <v>57669</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13074,34 +13069,39 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464502</v>
+        <v>464526</v>
       </c>
       <c r="R120" t="n">
-        <v>6785318</v>
+        <v>6785298</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13170,45 +13170,50 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127427379</v>
+        <v>127423326</v>
       </c>
       <c r="B121" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464643</v>
+        <v>464480</v>
       </c>
       <c r="R121" t="n">
-        <v>6785243</v>
+        <v>6785322</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13240,7 +13245,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13250,7 +13255,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13277,7 +13282,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127423326</v>
+        <v>127425909</v>
       </c>
       <c r="B122" t="n">
         <v>57669</v>
@@ -13308,7 +13313,7 @@
       <c r="I122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -13317,10 +13322,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464480</v>
+        <v>464566</v>
       </c>
       <c r="R122" t="n">
-        <v>6785322</v>
+        <v>6785301</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13352,7 +13357,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13362,7 +13367,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13389,27 +13394,27 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127425909</v>
+        <v>127426763</v>
       </c>
       <c r="B123" t="n">
-        <v>57669</v>
+        <v>58042</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -13420,7 +13425,7 @@
       <c r="I123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -13429,10 +13434,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>464566</v>
+        <v>464578</v>
       </c>
       <c r="R123" t="n">
-        <v>6785301</v>
+        <v>6785262</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13501,10 +13506,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127426763</v>
+        <v>127427379</v>
       </c>
       <c r="B124" t="n">
-        <v>58042</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13512,39 +13517,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>464578</v>
+        <v>464643</v>
       </c>
       <c r="R124" t="n">
-        <v>6785262</v>
+        <v>6785243</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14367,10 +14367,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127421996</v>
+        <v>127423972</v>
       </c>
       <c r="B132" t="n">
-        <v>57669</v>
+        <v>79647</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14378,39 +14378,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>464445</v>
+        <v>464506</v>
       </c>
       <c r="R132" t="n">
-        <v>6785311</v>
+        <v>6785318</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14479,10 +14474,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127422151</v>
+        <v>127423454</v>
       </c>
       <c r="B133" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14490,39 +14485,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464471</v>
+        <v>464472</v>
       </c>
       <c r="R133" t="n">
-        <v>6785300</v>
+        <v>6785351</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14591,45 +14581,50 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127422589</v>
+        <v>127421996</v>
       </c>
       <c r="B134" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464502</v>
+        <v>464445</v>
       </c>
       <c r="R134" t="n">
-        <v>6785289</v>
+        <v>6785311</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14698,10 +14693,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127423972</v>
+        <v>127422151</v>
       </c>
       <c r="B135" t="n">
-        <v>79647</v>
+        <v>57669</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14709,34 +14704,39 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Kölbron, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464506</v>
+        <v>464471</v>
       </c>
       <c r="R135" t="n">
-        <v>6785318</v>
+        <v>6785300</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14805,32 +14805,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127423454</v>
+        <v>127422589</v>
       </c>
       <c r="B136" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14840,10 +14840,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>464472</v>
+        <v>464502</v>
       </c>
       <c r="R136" t="n">
-        <v>6785351</v>
+        <v>6785289</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14912,10 +14912,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127423216</v>
+        <v>127422954</v>
       </c>
       <c r="B137" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14923,21 +14923,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14947,10 +14947,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464502</v>
+        <v>464492</v>
       </c>
       <c r="R137" t="n">
-        <v>6785318</v>
+        <v>6785316</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15019,7 +15019,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127422954</v>
+        <v>127423983</v>
       </c>
       <c r="B138" t="n">
         <v>79029</v>
@@ -15054,10 +15054,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>464492</v>
+        <v>464506</v>
       </c>
       <c r="R138" t="n">
-        <v>6785316</v>
+        <v>6785318</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15126,10 +15126,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127423983</v>
+        <v>127423216</v>
       </c>
       <c r="B139" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15137,21 +15137,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15161,7 +15161,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464506</v>
+        <v>464502</v>
       </c>
       <c r="R139" t="n">
         <v>6785318</v>

--- a/artfynd/A 34018-2021 artfynd.xlsx
+++ b/artfynd/A 34018-2021 artfynd.xlsx
@@ -17246,7 +17246,7 @@
         <v>127675974</v>
       </c>
       <c r="B159" t="n">
-        <v>91806</v>
+        <v>91814</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>127470562</v>
       </c>
       <c r="B160" t="n">
-        <v>91806</v>
+        <v>91814</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
